--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -7,8 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sprint Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Raw Worklogs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Overview_Weekly" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Overview_Sprint" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fact_Timelogs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dim_Sprints" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dim_Issues" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Dim_Authors" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,30 +418,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sprint</t>
+          <t>calendar_week</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Worklog Author</t>
+          <t>worklog_author</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Hours Logged</t>
+          <t>total_hours</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -446,13 +450,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -461,13 +465,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -476,13 +480,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -491,13 +495,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -506,13 +510,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -521,13 +525,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -536,13 +540,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -551,13 +555,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -566,36 +570,141 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Klas Widebeck</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Seleman Hassan</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C14" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Anton Hedlund</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Einar Eriksson Wahlin</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Klas Widebeck</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Seleman Hassan</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>6</v>
       </c>
     </row>
@@ -610,65 +719,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sprint</t>
+          <t>sprint_by_date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Worklog Author</t>
+          <t>worklog_author</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Hours Logged</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Issue</t>
+          <t>total_hours</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SCRUM-55</t>
-        </is>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -677,92 +766,52 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SCRUM-75</t>
-        </is>
+        <v>9.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SCRUM-75</t>
-        </is>
+        <v>10.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SCRUM-75</t>
-        </is>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>SCRUM-75</t>
-        </is>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -773,21 +822,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SCRUM-17</t>
-        </is>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -798,795 +837,4657 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Seleman Hassan</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>worklog_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>calendar_week</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sprint_by_date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>worklog_author</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>author_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>issue_key</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>hours_logged</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10322</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-28 11:00:24</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Anton Hedlund</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SCRUM-75</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10323</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-28 11:00:25</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>5</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SCRUM-75</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10324</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-28 11:00:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Seleman Hassan</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SCRUM-75</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10325</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-28 11:00:28</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SCRUM-75</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10176</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-24 11:13:09</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Einar Eriksson Wahlin</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SCRUM-64</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10177</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-24 11:13:09</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SCRUM-64</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10178</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-24 11:13:15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SCRUM-64</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>10179</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-24 11:13:10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Seleman Hassan</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SCRUM-17</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SCRUM-64</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>5</v>
+          <t>2026-09-24 11:14:22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Klas Widebeck</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SCRUM-64</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>10319</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:53:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Einar Eriksson Wahlin</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Anton Hedlund</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SCRUM-64</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>SCRUM-64</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>10072</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:00:01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Sai Suchith Kurra</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SCRUM-64</t>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SCRUM-58</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>10073</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:00:04</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Calvin Koch</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SCRUM-64</t>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Einar Eriksson Wahlin</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SCRUM-58</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>10074</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:29:25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Seleman Hassan</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SCRUM-64</t>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Anton Hedlund</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SCRUM-58</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>10075</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:00:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Klas Widebeck</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SCRUM-64</t>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SCRUM-58</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': [{'type': 'paragraph', 'content': [{'type': 'text', 'text': 'Team Meeting'}], 'attrs': {'localId': 'e10b569c8156'}}]}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>10076</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:00:29</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Anton Hedlund</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>SCRUM-64</t>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Seleman Hassan</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SCRUM-58</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>10317</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:00:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Einar Eriksson Wahlin</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>SCRUM-54</t>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Klas Widebeck</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SCRUM-58</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>10326</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:37:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Anton Hedlund</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>SCRUM-54</t>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SCRUM-55</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>10110</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-23 10:41:54</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Klas Widebeck</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Einar Eriksson Wahlin</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>SCRUM-54</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>10143</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-23 20:15:50</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Calvin Koch</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>SCRUM-58</t>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Anton Hedlund</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>SCRUM-54</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>10318</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-23 11:08:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Einar Eriksson Wahlin</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>SCRUM-58</t>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Klas Widebeck</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SCRUM-54</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>10320</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-21 11:53:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Anton Hedlund</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>SCRUM-58</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Seleman Hassan</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SCRUM-50</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-16 07:44:48</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Sai Suchith Kurra</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>SCRUM-58</t>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SCRUM-48</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-16 07:54:24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Seleman Hassan</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>SCRUM-58</t>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SCRUM-48</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>10002</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-16 05:54:42</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Klas Widebeck</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>SCRUM-58</t>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Einar Eriksson Wahlin</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SCRUM-48</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>10003</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-16 08:14:29</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Anton Hedlund</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>SCRUM-35</t>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Seleman Hassan</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SCRUM-48</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>10004</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-16 08:18:46</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Anton Hedlund</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>SCRUM-34</t>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SCRUM-48</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>10037</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-16 08:00:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Anton Hedlund</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Klas Widebeck</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SCRUM-48</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>1</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>SCRUM-33</t>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>10070</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-21 08:29:54</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Sai Suchith Kurra</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>SCRUM-10</t>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SCRUM-47</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>10215</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:17:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Sai Suchith Kurra</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SCRUM-38</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>1</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>SCRUM-38</t>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>2</v>
+          <t>2026-09-27 17:42:22</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Anton Hedlund</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SCRUM-35</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0.5</v>
+          <t>2026-09-25 15:00:19</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Anton Hedlund</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SCRUM-34</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>10248</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:15:02</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Calvin Koch</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>3</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>SCRUM-47</t>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Anton Hedlund</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SCRUM-33</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>2026-09-11 09:14:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>Sai Suchith Kurra</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>SCRUM-48</t>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SCRUM-27</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>10315</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-28 08:36:42</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Calvin Koch</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>SCRUM-48</t>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Einar Eriksson Wahlin</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SCRUM-17</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>10316</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-27 19:00:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Einar Eriksson Wahlin</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>SCRUM-48</t>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Klas Widebeck</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SCRUM-17</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>5</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>10321</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-28 06:56:33</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Seleman Hassan</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>SCRUM-48</t>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SCRUM-17</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
+          <t>2026-09-11 09:42:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>SCRUM-12</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>10071</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:14:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>SCRUM-10</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>{'type': 'doc', 'version': 1, 'content': [{'type': 'paragraph', 'content': [{'type': 'text', 'text': 'The issue has been resolved. '}], 'attrs': {'localId': '250995940946'}}]}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sprint_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sprint_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>theoretical_start_date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>theoretical_end_date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>effective_start_date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>effective_end_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-08-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-06 23:59:59</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:33:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:59:59</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:33:25</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09-28 16:33:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>future</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-09-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-11 23:59:59</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-28 16:33:25</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-10-11 23:59:59</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>issue_key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>issue_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>timespent_hours</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>created</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SCRUM-78</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Risk analysis and planning</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:38:45</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:40:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SCRUM-77</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>List of potential risks</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:37:59</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:40:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SCRUM-76</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:37:40</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:42:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SCRUM-75</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sprint 3 planning meeting</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:49:06</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SCRUM-74</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Look through options for time tracking</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:40:35</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:40:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SCRUM-73</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Prepare for Project Management and Tech Lead meeting</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:32:10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:40:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SCRUM-72</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Design Level 4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:07:23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:07:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SCRUM-71</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Attend Technical Lead meeting 3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:05:18</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:39:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SCRUM-70</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Attend Project Management meeting 3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:05:17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:39:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SCRUM-69</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Submit A3, Artefacts</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:03:04</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:43:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SCRUM-68</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Initial planning of sprint 3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:00:17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:08:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SCRUM-67</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Submit D5, Integration and Project Completion Plan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:59:53</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:02:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SCRUM-66</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Submit D4, Risk Assesment Plan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:59:26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:42:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SCRUM-65</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>User Requirements</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:55:24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:56:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SCRUM-64</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Group Meeting 24.09.2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:48:35</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:53:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SCRUM-63</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Project Handover Code Cleanup</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:08:11</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:08:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SCRUM-62</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:06:13</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SCRUM-61</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Course</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:05:17</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SCRUM-60</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Level 4 Game Logic</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:03:04</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:03:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:02:30</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SCRUM-58</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Group Meeting 21.09.2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>9</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:29:42</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:36:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SCRUM-57</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>add more user stories</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:16:53</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:41:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SCRUM-56</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Adjusting user requirements and adding more user stories</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:16:48</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:58:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SCRUM-55</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Reorganise the files and folders in the github repo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:15:32</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:38:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SCRUM-54</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Update D2, Requirements Specification</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-20 18:22:35</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:38:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SCRUM-53</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Update D1, Group Agreement</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-20 18:15:13</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:36:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SCRUM-52</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Brainstorming drafts of level 4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-16 11:04:20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:33:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SCRUM-50</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Change the en/ett button in level 3 to a field you can fill out</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:51:26</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:54:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SCRUM-49</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fix issue with language change not affecting instructions</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:46:54</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:23:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SCRUM-48</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sprint planning meeting</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:43:45</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:06:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SCRUM-47</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fix issue with the educational information page</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:39:28</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:14:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SCRUM-46</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Look through the existing code</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:26:40</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:34:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SCRUM-45</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Write Submission</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:29:10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:29:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SCRUM-44</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Write Submission</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:28:48</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:29:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SCRUM-43</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Write Submission</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:28:35</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:28:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SCRUM-42</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Write Submission</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:28:17</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:28:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SCRUM-41</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Write Submission</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:28:07</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:30:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SCRUM-40</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>Attend Meeting</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:26:58</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:27:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SCRUM-39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Attend Meeting</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:26:47</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:27:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SCRUM-38</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Attend Meeting</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:26:32</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SCRUM-37</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Attend Meeting</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:26:05</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:26:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SCRUM-36</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Submit A2, Artefacts</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-14 17:45:50</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:34:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SCRUM-35</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ethical Considerations</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:26:10</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-09-27 22:42:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SCRUM-34</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Functional Requirements 2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:25:56</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:15:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SCRUM-33</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Functional Requirements 1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:25:41</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:15:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SCRUM-32</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Components</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:25:35</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:03:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SCRUM-31</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Definitions</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:25:28</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:57:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SCRUM-30</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Scope Statement</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:25:21</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:03:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SCRUM-29</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>User Requirements 2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:14:13</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:17:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SCRUM-28</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>User Requirements 1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:14:02</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:17:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SCRUM-27</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>User Classes</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:13:58</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:14:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SCRUM-26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Layout and Ethical Concerns</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:13:52</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:17:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SCRUM-20</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Attend Meeting</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:07:22</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:08:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SCRUM-19</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Attend Technical Meeting</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:06:09</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:07:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SCRUM-18</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Attend Project Management Meeting</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:05:54</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:06:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SCRUM-17</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Submit D3, Requirements Specification</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-14 11:38:16</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:56:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SCRUM-16</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Scope Statement</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-14 11:34:01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SCRUM-15</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Client Meeting (online)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-14 11:32:26</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:27:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SCRUM-14</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Submit A1, Artefacts</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:36:46</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-09-14 18:29:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SCRUM-13</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Submit D2, Requirements Elicitation</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:34:14</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:20:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SCRUM-12</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Submit D1, Group Agreement</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:31:35</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SCRUM-11</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Revisit the group agreement</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:43:07</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:05:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SCRUM-10</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Fix issue with level 1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:57:26</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:18:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SCRUM-9</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Fix duplicate word issue in level 2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:54:17</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:37:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Fix case-sensitivity issue</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:52:58</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:39:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SCRUM-4</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Subtask 2.1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:12:55</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:12:55</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>account_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>firstname</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>lastname</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Calvin</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Anton Hedlund</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Anton</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Hedlund</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>SCRUM-48</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Klas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Widebeck</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Seleman Hassan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Seleman</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Hassan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Einar Eriksson Wahlin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Einar</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Eriksson Wahlin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Suchith Sai Kurra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Suchith</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sai Kurra</t>
         </is>
       </c>
     </row>

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -719,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.25</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="4">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="5">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -841,7 +841,82 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.5</v>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Anton Hedlund</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Einar Eriksson Wahlin</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Klas Widebeck</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Seleman Hassan</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -933,7 +1008,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -954,11 +1029,7 @@
       <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -983,7 +1054,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1004,11 +1075,7 @@
       <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1033,7 +1100,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1054,11 +1121,7 @@
       <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1083,7 +1146,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1104,11 +1167,7 @@
       <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1154,11 +1213,7 @@
       <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1204,11 +1259,7 @@
       <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1254,11 +1305,7 @@
       <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1304,11 +1351,7 @@
       <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1354,11 +1397,7 @@
       <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1404,11 +1443,7 @@
       <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1454,11 +1489,7 @@
       <c r="I12" t="n">
         <v>1.5</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1504,11 +1535,7 @@
       <c r="I13" t="n">
         <v>1.5</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1554,11 +1581,7 @@
       <c r="I14" t="n">
         <v>1.5</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1606,7 +1629,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>{'type': 'doc', 'version': 1, 'content': [{'type': 'paragraph', 'content': [{'type': 'text', 'text': 'Team Meeting'}], 'attrs': {'localId': 'e10b569c8156'}}]}</t>
+          <t>Team Meeting</t>
         </is>
       </c>
     </row>
@@ -1654,11 +1677,7 @@
       <c r="I16" t="n">
         <v>1.5</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1704,11 +1723,7 @@
       <c r="I17" t="n">
         <v>1.5</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1754,11 +1769,7 @@
       <c r="I18" t="n">
         <v>3</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1804,11 +1815,7 @@
       <c r="I19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1854,11 +1861,7 @@
       <c r="I20" t="n">
         <v>0.5</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1904,11 +1907,7 @@
       <c r="I21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2000,11 +1999,7 @@
       <c r="I23" t="n">
         <v>1</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2050,11 +2045,7 @@
       <c r="I24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2100,11 +2091,7 @@
       <c r="I25" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2150,11 +2137,7 @@
       <c r="I26" t="n">
         <v>1</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2200,11 +2183,7 @@
       <c r="I27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2250,11 +2229,7 @@
       <c r="I28" t="n">
         <v>1</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2300,11 +2275,7 @@
       <c r="I29" t="n">
         <v>3</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2329,7 +2300,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2350,11 +2321,7 @@
       <c r="I30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2400,11 +2367,7 @@
       <c r="I31" t="n">
         <v>3</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2450,11 +2413,7 @@
       <c r="I32" t="n">
         <v>0.25</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2500,11 +2459,7 @@
       <c r="I33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2550,11 +2505,7 @@
       <c r="I34" t="n">
         <v>2</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2579,7 +2530,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2600,11 +2551,7 @@
       <c r="I35" t="n">
         <v>2.5</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2650,11 +2597,7 @@
       <c r="I36" t="n">
         <v>5</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2679,7 +2622,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2700,11 +2643,7 @@
       <c r="I37" t="n">
         <v>5</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2750,11 +2689,7 @@
       <c r="I38" t="n">
         <v>0.5</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>{'type': 'doc', 'version': 1, 'content': []}</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2802,7 +2737,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>{'type': 'doc', 'version': 1, 'content': [{'type': 'paragraph', 'content': [{'type': 'text', 'text': 'The issue has been resolved. '}], 'attrs': {'localId': '250995940946'}}]}</t>
+          <t>The issue has been resolved.</t>
         </is>
       </c>
     </row>
@@ -2873,22 +2808,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-24 00:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-06 23:59:59</t>
+          <t>2026-09-13 23:59:59</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-30 22:00:00</t>
+          <t>2026-08-31 00:00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:33:24</t>
+          <t>2026-09-13 23:59:59</t>
         </is>
       </c>
     </row>
@@ -2918,12 +2853,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:33:25</t>
+          <t>2026-09-14 00:00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-28 16:33:24</t>
+          <t>2026-09-27 23:59:59</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2888,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-28 16:33:25</t>
+          <t>2026-09-28 00:00:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -2908,7 +2908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2947,6 +2947,11 @@
           <t>updated</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>issue_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2982,6 +2987,11 @@
           <t>2026-09-28 13:40:32</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3017,6 +3027,11 @@
           <t>2026-09-28 13:40:14</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3052,6 +3067,11 @@
           <t>2026-09-28 13:42:36</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3087,6 +3107,11 @@
           <t>2026-09-28 14:00:39</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3122,6 +3147,11 @@
           <t>2026-09-25 10:40:35</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3157,6 +3187,11 @@
           <t>2026-09-28 13:40:03</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3192,6 +3227,11 @@
           <t>2026-09-23 14:07:33</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3227,6 +3267,11 @@
           <t>2026-09-28 13:39:58</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3262,6 +3307,11 @@
           <t>2026-09-28 13:39:56</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3297,6 +3347,11 @@
           <t>2026-09-28 13:43:04</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3332,6 +3387,11 @@
           <t>2026-09-23 14:08:42</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3367,6 +3427,11 @@
           <t>2026-09-23 14:02:47</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3402,6 +3467,11 @@
           <t>2026-09-28 13:42:01</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3437,6 +3507,11 @@
           <t>2026-09-23 13:56:06</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3472,6 +3547,11 @@
           <t>2026-09-28 13:53:59</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3507,6 +3587,11 @@
           <t>2026-09-21 16:08:12</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3542,6 +3627,11 @@
           <t>2026-09-21 16:10:11</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3577,6 +3667,11 @@
           <t>2026-09-21 16:09:47</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3612,6 +3707,11 @@
           <t>2026-09-21 16:03:56</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3647,6 +3747,11 @@
           <t>2026-09-21 16:09:57</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3682,6 +3787,11 @@
           <t>2026-09-28 13:36:42</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3717,6 +3827,11 @@
           <t>2026-09-23 13:41:49</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3752,6 +3867,11 @@
           <t>2026-09-23 22:58:08</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3787,6 +3907,11 @@
           <t>2026-09-28 14:38:13</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3822,6 +3947,11 @@
           <t>2026-09-28 13:38:30</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3857,6 +3987,11 @@
           <t>2026-09-24 13:36:15</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3892,6 +4027,11 @@
           <t>2026-09-24 13:33:59</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3927,6 +4067,11 @@
           <t>2026-09-28 13:54:24</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3962,6 +4107,11 @@
           <t>2026-09-28 13:23:24</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3997,6 +4147,11 @@
           <t>2026-09-21 16:06:21</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4032,6 +4187,11 @@
           <t>2026-09-24 14:14:59</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4067,6 +4227,11 @@
           <t>2026-09-28 13:34:18</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4102,6 +4267,11 @@
           <t>2026-09-14 18:29:18</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4137,6 +4307,11 @@
           <t>2026-09-14 18:29:01</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4172,6 +4347,11 @@
           <t>2026-09-14 18:28:42</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4207,6 +4387,11 @@
           <t>2026-09-14 18:28:28</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4242,6 +4427,11 @@
           <t>2026-09-14 18:30:21</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4277,6 +4467,11 @@
           <t>2026-09-14 18:27:10</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4312,6 +4507,11 @@
           <t>2026-09-14 18:27:07</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4347,6 +4547,11 @@
           <t>2026-09-25 12:17:19</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4382,6 +4587,11 @@
           <t>2026-09-14 18:26:25</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4417,6 +4627,11 @@
           <t>2026-09-28 13:34:01</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4452,6 +4667,11 @@
           <t>2026-09-27 22:42:27</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4487,6 +4707,11 @@
           <t>2026-09-25 17:15:26</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4522,6 +4747,11 @@
           <t>2026-09-25 17:15:07</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4557,6 +4787,11 @@
           <t>2026-09-24 14:03:01</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4592,6 +4827,11 @@
           <t>2026-09-24 13:57:18</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4627,6 +4867,11 @@
           <t>2026-09-24 14:03:33</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4662,6 +4907,11 @@
           <t>2026-09-14 14:17:18</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4697,6 +4947,11 @@
           <t>2026-09-14 14:17:06</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4732,6 +4987,11 @@
           <t>2026-09-25 12:14:32</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4767,6 +5027,11 @@
           <t>2026-09-14 14:17:08</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4802,6 +5067,11 @@
           <t>2026-09-14 14:08:16</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4837,6 +5107,11 @@
           <t>2026-09-14 14:07:44</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4872,6 +5147,11 @@
           <t>2026-09-14 14:06:21</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4907,6 +5187,11 @@
           <t>2026-09-28 13:56:48</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4942,6 +5227,11 @@
           <t>2026-09-14 14:17:00</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4977,6 +5267,11 @@
           <t>2026-09-14 18:27:18</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5012,6 +5307,11 @@
           <t>2026-09-14 18:29:29</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5047,6 +5347,11 @@
           <t>2026-09-14 14:20:24</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5082,6 +5387,11 @@
           <t>2026-09-25 12:12:32</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5117,6 +5427,11 @@
           <t>2026-09-21 16:05:23</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5152,6 +5467,11 @@
           <t>2026-09-25 12:18:34</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5187,6 +5507,11 @@
           <t>2026-09-28 13:37:53</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5222,6 +5547,11 @@
           <t>2026-09-28 13:39:15</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5255,6 +5585,11 @@
       <c r="G67" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-4</t>
         </is>
       </c>
     </row>

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="17">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="8">
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
@@ -930,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,68 +1912,68 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-21 11:53:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-21 11:53:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1983,33 +1983,33 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2050,12 +2050,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2096,12 +2096,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2142,12 +2142,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2188,12 +2188,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2234,22 +2234,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2259,43 +2259,43 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2305,43 +2305,43 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2351,38 +2351,38 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2407,23 +2407,23 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2453,140 +2453,140 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2595,44 +2595,44 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-28 06:56:33</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2648,94 +2648,232 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-28 06:56:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>10359</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:23:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-W39</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>SCRUM-17</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10361</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-28 19:57:36</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>SCRUM-15</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10213</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:42:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>SCRUM-12</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>10071</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>2026-09-18 09:14:00</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2026-W38</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Sai Suchith Kurra</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>SCRUM-10</t>
         </is>
       </c>
-      <c r="I39" t="n">
+      <c r="I42" t="n">
         <v>2.5</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>The issue has been resolved.</t>
         </is>
@@ -3935,7 +4073,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3944,7 +4082,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-28 13:38:30</t>
+          <t>2026-09-28 22:24:30</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -5175,7 +5313,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5184,7 +5322,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-28 13:56:48</t>
+          <t>2026-09-28 22:23:47</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5255,7 +5393,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5264,7 +5402,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:18</t>
+          <t>2026-09-28 22:27:42</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,26 +446,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="4">
@@ -476,11 +476,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -491,11 +491,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -506,7 +506,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -521,11 +521,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -536,26 +536,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -566,11 +566,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.5</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="11">
@@ -581,11 +581,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
@@ -596,11 +596,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13">
@@ -611,7 +611,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -626,26 +626,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="16">
@@ -656,11 +656,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -671,11 +671,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -686,11 +686,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
@@ -701,10 +701,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Klas Widebeck</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Seleman Hassan</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C20" t="n">
         <v>6</v>
       </c>
     </row>
@@ -719,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -747,26 +762,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="4">
@@ -777,11 +792,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.5</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="5">
@@ -792,11 +807,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="6">
@@ -807,11 +822,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
@@ -822,11 +837,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -837,26 +852,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="10">
@@ -867,11 +882,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -882,11 +897,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -897,11 +912,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -912,10 +927,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Klas Widebeck</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Seleman Hassan</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C14" t="n">
         <v>6</v>
       </c>
     </row>
@@ -930,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,42 +1202,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-09-10 19:30:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1218,7 +1248,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1243,12 +1273,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1264,12 +1294,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1289,12 +1319,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1310,12 +1340,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1335,12 +1365,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1356,12 +1386,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1381,12 +1411,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1402,12 +1432,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1427,12 +1457,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1448,17 +1478,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1473,33 +1503,33 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1519,12 +1549,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1540,12 +1570,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1565,12 +1595,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1586,12 +1616,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1611,12 +1641,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1627,21 +1657,17 @@
       <c r="I15" t="n">
         <v>1.5</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1661,12 +1687,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1677,17 +1703,21 @@
       <c r="I16" t="n">
         <v>1.5</v>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1707,12 +1737,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1728,22 +1758,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1753,43 +1783,43 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1799,33 +1829,33 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1845,12 +1875,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1859,19 +1889,19 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1891,12 +1921,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1912,37 +1942,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1951,75 +1981,75 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-21 11:53:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-21 11:53:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2029,33 +2059,33 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2075,12 +2105,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2096,12 +2126,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2121,12 +2151,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2142,12 +2172,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2167,12 +2197,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2188,12 +2218,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2213,12 +2243,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2234,12 +2264,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2259,12 +2289,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2280,22 +2310,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2305,43 +2335,43 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2351,43 +2381,43 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2397,38 +2427,38 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2453,23 +2483,23 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2499,140 +2529,140 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2641,44 +2671,44 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-28 06:56:33</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2694,37 +2724,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-28 06:56:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2733,147 +2763,285 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-28 19:57:36</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>10361</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-07 19:57:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>SCRUM-15</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10213</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:42:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>SCRUM-12</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>10362</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:29:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>SCRUM-12</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>10071</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>2026-09-18 09:14:00</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>2026-W38</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Sai Suchith Kurra</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>SCRUM-10</t>
         </is>
       </c>
-      <c r="I42" t="n">
+      <c r="I45" t="n">
         <v>2.5</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>The issue has been resolved.</t>
         </is>
@@ -3273,7 +3441,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3282,7 +3450,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-25 10:40:35</t>
+          <t>2026-09-28 22:30:53</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5353,7 +5521,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5362,7 +5530,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:00</t>
+          <t>2026-09-28 22:35:13</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5402,7 +5570,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:42</t>
+          <t>2026-09-28 22:28:42</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5513,7 +5681,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5522,7 +5690,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-25 12:12:32</t>
+          <t>2026-09-28 22:30:22</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,10 +716,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Seleman Hassan</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>6</v>
       </c>
     </row>
@@ -734,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -942,10 +957,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Seleman Hassan</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -960,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1202,42 +1232,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1248,42 +1278,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-09-10 19:30:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1294,7 +1324,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1319,12 +1349,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1340,12 +1370,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1365,12 +1395,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1386,12 +1416,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1411,12 +1441,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1432,12 +1462,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1457,12 +1487,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1478,12 +1508,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1503,12 +1533,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1524,17 +1554,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1549,33 +1579,33 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1595,12 +1625,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1616,12 +1646,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1641,12 +1671,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1662,12 +1692,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1687,12 +1717,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1703,21 +1733,17 @@
       <c r="I16" t="n">
         <v>1.5</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1737,12 +1763,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1753,17 +1779,21 @@
       <c r="I17" t="n">
         <v>1.5</v>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1783,12 +1813,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1804,22 +1834,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1829,43 +1859,43 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1875,33 +1905,33 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1921,12 +1951,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1935,19 +1965,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1967,12 +1997,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1988,37 +2018,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2027,75 +2057,75 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-21 11:53:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-21 11:53:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2105,33 +2135,33 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2151,12 +2181,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2172,12 +2202,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2197,12 +2227,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2218,12 +2248,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2243,12 +2273,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2264,12 +2294,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2289,12 +2319,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2310,12 +2340,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2335,12 +2365,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2356,22 +2386,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2381,43 +2411,43 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2427,43 +2457,43 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2473,38 +2503,38 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2529,23 +2559,23 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2575,140 +2605,140 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2717,44 +2747,44 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-28 06:56:33</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2770,37 +2800,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-28 06:56:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2809,24 +2839,24 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2841,48 +2871,48 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2897,28 +2927,28 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2933,17 +2963,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2954,17 +2984,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2979,12 +3009,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2993,55 +3023,101 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>10362</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:29:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>SCRUM-12</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>10071</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>2026-09-18 09:14:00</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>2026-W38</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Sai Suchith Kurra</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>SCRUM-10</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="I46" t="n">
         <v>2.5</v>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>The issue has been resolved.</t>
         </is>
@@ -3401,7 +3477,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3410,7 +3486,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-28 14:00:39</t>
+          <t>2026-09-28 22:36:57</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,11 +446,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -461,71 +461,71 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -536,11 +536,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -551,71 +551,71 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -626,11 +626,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="15">
@@ -641,71 +641,71 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="20">
@@ -716,7 +716,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -731,11 +731,71 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Einar Eriksson Wahlin</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Klas Widebeck</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Seleman Hassan</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>6</v>
+      <c r="C25" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +946,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="10">
@@ -976,7 +1036,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2805,22 +2865,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-28 06:56:33</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5566,7 +5626,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-28 22:23:47</t>
+          <t>2026-09-28 22:43:58</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3044,12 +3044,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3069,38 +3069,38 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3129,55 +3129,147 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>10362</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:29:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>SCRUM-12</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>10366</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-10 20:22:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>SCRUM-11</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>10071</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>2026-09-18 09:14:00</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2026-W38</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Sai Suchith Kurra</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>SCRUM-10</t>
         </is>
       </c>
-      <c r="I46" t="n">
+      <c r="I48" t="n">
         <v>2.5</v>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>The issue has been resolved.</t>
         </is>
@@ -5777,7 +5869,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5786,7 +5878,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-14 14:20:24</t>
+          <t>2026-09-28 22:55:02</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5857,7 +5949,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5866,7 +5958,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-21 16:05:23</t>
+          <t>2026-09-28 22:52:55</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="6">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:24</t>
+          <t>2026-09-28 17:56:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1133,33 +1133,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:25</t>
+          <t>2026-09-28 11:00:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1200,12 +1200,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:30</t>
+          <t>2026-09-28 11:00:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1246,12 +1246,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:28</t>
+          <t>2026-09-28 11:00:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1292,12 +1292,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:00</t>
+          <t>2026-09-28 11:00:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1338,42 +1338,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1384,42 +1384,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-09-10 19:30:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1430,7 +1430,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1476,12 +1476,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1522,12 +1522,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1568,12 +1568,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1614,12 +1614,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1660,17 +1660,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1685,33 +1685,33 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1731,12 +1731,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1752,12 +1752,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1798,12 +1798,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1839,21 +1839,17 @@
       <c r="I17" t="n">
         <v>1.5</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1873,12 +1869,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1889,17 +1885,21 @@
       <c r="I18" t="n">
         <v>1.5</v>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1940,22 +1940,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1965,43 +1965,43 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2011,33 +2011,33 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2071,19 +2071,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2124,37 +2124,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2163,75 +2163,75 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-21 11:53:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-21 11:53:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2241,33 +2241,33 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2308,12 +2308,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2354,12 +2354,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2400,12 +2400,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2425,12 +2425,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2446,12 +2446,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2492,22 +2492,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2517,43 +2517,43 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2563,43 +2563,43 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2609,38 +2609,38 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2665,23 +2665,23 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,140 +2711,140 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2853,24 +2853,24 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2906,12 +2906,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2945,24 +2945,24 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2977,48 +2977,48 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3033,28 +3033,28 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3079,23 +3079,23 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3115,38 +3115,38 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3175,19 +3175,19 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-10 19:29:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3217,63 +3217,155 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>10366</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-10 20:22:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SCRUM-11</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>10071</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>2026-09-18 09:14:00</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>2026-W38</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Sai Suchith Kurra</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>SCRUM-10</t>
         </is>
       </c>
-      <c r="I48" t="n">
+      <c r="I49" t="n">
         <v>2.5</v>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>The issue has been resolved.</t>
         </is>
       </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3442,7 +3534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3490,17 +3582,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCRUM-78</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Risk analysis and planning</t>
+          <t>Worklog Report Solution</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3509,33 +3601,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-28 13:38:45</t>
+          <t>2026-09-28 22:55:55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:32</t>
+          <t>2026-09-28 22:56:19</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCRUM-77</t>
+          <t>SCRUM-78</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>List of potential risks</t>
+          <t>Risk analysis and planning</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3553,29 +3645,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:59</t>
+          <t>2026-09-28 13:38:45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:14</t>
+          <t>2026-09-28 13:40:32</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCRUM-76</t>
+          <t>SCRUM-77</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>List of potential risks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3593,34 +3685,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:40</t>
+          <t>2026-09-28 13:37:59</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42:36</t>
+          <t>2026-09-28 13:40:14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-76</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sprint 3 planning meeting</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3629,33 +3721,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-25 10:49:06</t>
+          <t>2026-09-28 13:37:40</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-28 22:36:57</t>
+          <t>2026-09-28 13:42:36</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Look through options for time tracking</t>
+          <t>Sprint 3 planning meeting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3669,33 +3761,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-25 10:40:35</t>
+          <t>2026-09-25 10:49:06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-28 22:30:53</t>
+          <t>2026-09-28 22:36:57</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCRUM-73</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prepare for Project Management and Tech Lead meeting</t>
+          <t>Look through options for time tracking</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3709,33 +3801,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-25 10:32:10</t>
+          <t>2026-09-25 10:40:35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:03</t>
+          <t>2026-09-28 22:30:53</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCRUM-72</t>
+          <t>SCRUM-73</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Design Level 4</t>
+          <t>Prepare for Project Management and Tech Lead meeting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3753,29 +3845,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:23</t>
+          <t>2026-09-25 10:32:10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:33</t>
+          <t>2026-09-28 13:40:03</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCRUM-71</t>
+          <t>SCRUM-72</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Attend Technical Lead meeting 3</t>
+          <t>Design Level 4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3793,29 +3885,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:18</t>
+          <t>2026-09-23 14:07:23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-28 13:39:58</t>
+          <t>2026-09-23 14:07:33</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-71</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Attend Project Management meeting 3</t>
+          <t>Attend Technical Lead meeting 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3833,29 +3925,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:17</t>
+          <t>2026-09-23 14:05:18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-28 13:39:56</t>
+          <t>2026-09-28 13:39:58</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCRUM-69</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Submit A3, Artefacts</t>
+          <t>Attend Project Management meeting 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3873,29 +3965,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-23 14:03:04</t>
+          <t>2026-09-23 14:05:17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-28 13:43:04</t>
+          <t>2026-09-28 13:39:56</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCRUM-68</t>
+          <t>SCRUM-69</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Initial planning of sprint 3</t>
+          <t>Submit A3, Artefacts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3905,7 +3997,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3913,29 +4005,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-23 14:00:17</t>
+          <t>2026-09-23 14:03:04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-23 14:08:42</t>
+          <t>2026-09-28 13:43:04</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-68</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Submit D5, Integration and Project Completion Plan</t>
+          <t>Initial planning of sprint 3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3945,7 +4037,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -3953,29 +4045,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:53</t>
+          <t>2026-09-23 14:00:17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-23 14:02:47</t>
+          <t>2026-09-23 14:08:42</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SCRUM-66</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Submit D4, Risk Assesment Plan</t>
+          <t>Submit D5, Integration and Project Completion Plan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3993,34 +4085,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:26</t>
+          <t>2026-09-23 13:59:53</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42:01</t>
+          <t>2026-09-23 14:02:47</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SCRUM-65</t>
+          <t>SCRUM-66</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>User Requirements</t>
+          <t>Submit D4, Risk Assesment Plan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4033,109 +4125,109 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-23 13:55:24</t>
+          <t>2026-09-23 13:59:26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-23 13:56:06</t>
+          <t>2026-09-28 13:42:01</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-65</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Group Meeting 24.09.2026</t>
+          <t>User Requirements</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-23 13:48:35</t>
+          <t>2026-09-23 13:55:24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-28 13:53:59</t>
+          <t>2026-09-23 13:56:06</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SCRUM-63</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Project Handover Code Cleanup</t>
+          <t>Group Meeting 24.09.2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:11</t>
+          <t>2026-09-23 13:48:35</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:12</t>
+          <t>2026-09-28 13:53:59</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SCRUM-62</t>
+          <t>SCRUM-63</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>Project Handover Code Cleanup</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4153,29 +4245,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:13</t>
+          <t>2026-09-21 16:08:11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-21 16:10:11</t>
+          <t>2026-09-21 16:08:12</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SCRUM-61</t>
+          <t>SCRUM-62</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Meetings</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4193,34 +4285,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-21 16:05:17</t>
+          <t>2026-09-21 16:06:13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:47</t>
+          <t>2026-09-21 16:10:11</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SCRUM-60</t>
+          <t>SCRUM-61</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Level 4 Game Logic</t>
+          <t>Course</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4233,34 +4325,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:04</t>
+          <t>2026-09-21 16:05:17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:56</t>
+          <t>2026-09-21 16:09:47</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SCRUM-59</t>
+          <t>SCRUM-60</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 4 Game Logic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4273,74 +4365,74 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-21 16:02:30</t>
+          <t>2026-09-21 16:03:04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:57</t>
+          <t>2026-09-21 16:03:56</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Group Meeting 21.09.2026</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-21 14:29:42</t>
+          <t>2026-09-21 16:02:30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-28 13:36:42</t>
+          <t>2026-09-21 16:09:57</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SCRUM-57</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>add more user stories</t>
+          <t>Group Meeting 21.09.2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4349,33 +4441,33 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:53</t>
+          <t>2026-09-21 14:29:42</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:49</t>
+          <t>2026-09-28 13:36:42</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SCRUM-56</t>
+          <t>SCRUM-57</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Adjusting user requirements and adding more user stories</t>
+          <t>add more user stories</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4393,69 +4485,69 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:48</t>
+          <t>2026-09-21 14:16:53</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-23 22:58:08</t>
+          <t>2026-09-23 13:41:49</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Reorganise the files and folders in the github repo</t>
+          <t>Adjusting user requirements and adding more user stories</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-21 13:15:32</t>
+          <t>2026-09-21 14:16:48</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-28 14:38:13</t>
+          <t>2026-09-23 22:58:08</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Update D2, Requirements Specification</t>
+          <t>Reorganise the files and folders in the github repo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4465,37 +4557,37 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-20 18:22:35</t>
+          <t>2026-09-21 13:15:32</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-28 22:24:30</t>
+          <t>2026-09-28 14:38:13</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SCRUM-53</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Update D1, Group Agreement</t>
+          <t>Update D2, Requirements Specification</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4509,33 +4601,33 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-20 18:15:13</t>
+          <t>2026-09-20 18:22:35</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-24 13:36:15</t>
+          <t>2026-09-28 22:24:30</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SCRUM-52</t>
+          <t>SCRUM-53</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Brainstorming drafts of level 4</t>
+          <t>Update D1, Group Agreement</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4553,29 +4645,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-16 11:04:20</t>
+          <t>2026-09-20 18:15:13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-24 13:33:59</t>
+          <t>2026-09-24 13:36:15</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Change the en/ett button in level 3 to a field you can fill out</t>
+          <t>Brainstorming drafts of level 4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4585,42 +4677,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-16 10:51:26</t>
+          <t>2026-09-16 11:04:20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-28 13:54:24</t>
+          <t>2026-09-24 13:33:59</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fix issue with language change not affecting instructions</t>
+          <t>Change the en/ett button in level 3 to a field you can fill out</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4629,163 +4721,163 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-16 10:46:54</t>
+          <t>2026-09-16 10:51:26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-28 13:23:24</t>
+          <t>2026-09-28 13:54:24</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sprint planning meeting</t>
+          <t>Fix issue with language change not affecting instructions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-16 10:43:45</t>
+          <t>2026-09-16 10:46:54</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:21</t>
+          <t>2026-09-28 13:23:24</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fix issue with the educational information page</t>
+          <t>Sprint planning meeting</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39:28</t>
+          <t>2026-09-16 10:43:45</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-24 14:14:59</t>
+          <t>2026-09-21 16:06:21</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Look through the existing code</t>
+          <t>Fix issue with the educational information page</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-16 10:26:40</t>
+          <t>2026-09-16 10:39:28</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-28 13:34:18</t>
+          <t>2026-09-24 14:14:59</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SCRUM-45</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Write Submission</t>
+          <t>Look through the existing code</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4793,24 +4885,24 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:10</t>
+          <t>2026-09-16 10:26:40</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:18</t>
+          <t>2026-09-28 13:34:18</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SCRUM-44</t>
+          <t>SCRUM-45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4833,24 +4925,24 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:48</t>
+          <t>2026-09-14 18:29:10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:01</t>
+          <t>2026-09-14 18:29:18</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SCRUM-43</t>
+          <t>SCRUM-44</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4873,24 +4965,24 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:35</t>
+          <t>2026-09-14 18:28:48</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:42</t>
+          <t>2026-09-14 18:29:01</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SCRUM-42</t>
+          <t>SCRUM-43</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4913,24 +5005,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:17</t>
+          <t>2026-09-14 18:28:35</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:28</t>
+          <t>2026-09-14 18:28:42</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SCRUM-41</t>
+          <t>SCRUM-42</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4953,29 +5045,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:07</t>
+          <t>2026-09-14 18:28:17</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-14 18:30:21</t>
+          <t>2026-09-14 18:28:28</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SCRUM-40</t>
+          <t>SCRUM-41</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Write Submission</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4993,24 +5085,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:58</t>
+          <t>2026-09-14 18:28:07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:10</t>
+          <t>2026-09-14 18:30:21</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SCRUM-39</t>
+          <t>SCRUM-40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5033,24 +5125,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:47</t>
+          <t>2026-09-14 18:26:58</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:07</t>
+          <t>2026-09-14 18:27:10</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-39</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5069,28 +5161,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:32</t>
+          <t>2026-09-14 18:26:47</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-25 12:17:19</t>
+          <t>2026-09-14 18:27:07</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SCRUM-37</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5109,38 +5201,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:05</t>
+          <t>2026-09-14 18:26:32</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:25</t>
+          <t>2026-09-25 12:17:19</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SCRUM-36</t>
+          <t>SCRUM-37</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Submit A2, Artefacts</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5153,69 +5245,69 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-14 17:45:50</t>
+          <t>2026-09-14 18:26:05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-28 13:34:01</t>
+          <t>2026-09-14 18:26:25</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ethical Considerations</t>
+          <t>Submit A2, Artefacts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-14 16:26:10</t>
+          <t>2026-09-14 17:45:50</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-27 22:42:27</t>
+          <t>2026-09-28 13:34:01</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Functional Requirements 2</t>
+          <t>Ethical Considerations</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5229,33 +5321,33 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:56</t>
+          <t>2026-09-14 16:26:10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-25 17:15:26</t>
+          <t>2026-09-27 22:42:27</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Functional Requirements 1</t>
+          <t>Functional Requirements 2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5269,33 +5361,33 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:41</t>
+          <t>2026-09-14 16:25:56</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-25 17:15:07</t>
+          <t>2026-09-25 17:15:26</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SCRUM-32</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Components</t>
+          <t>Functional Requirements 1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5309,33 +5401,33 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:35</t>
+          <t>2026-09-14 16:25:41</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-24 14:03:01</t>
+          <t>2026-09-25 17:15:07</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SCRUM-31</t>
+          <t>SCRUM-32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Definitions</t>
+          <t>Components</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5353,29 +5445,29 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:28</t>
+          <t>2026-09-14 16:25:35</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:18</t>
+          <t>2026-09-24 14:03:01</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SCRUM-30</t>
+          <t>SCRUM-31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Definitions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5393,29 +5485,29 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:21</t>
+          <t>2026-09-14 16:25:28</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-24 14:03:33</t>
+          <t>2026-09-24 13:57:18</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SCRUM-29</t>
+          <t>SCRUM-30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>User Requirements 2</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5425,7 +5517,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5433,29 +5525,29 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:13</t>
+          <t>2026-09-14 16:25:21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:18</t>
+          <t>2026-09-24 14:03:33</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SCRUM-28</t>
+          <t>SCRUM-29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>User Requirements 1</t>
+          <t>User Requirements 2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5473,29 +5565,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:02</t>
+          <t>2026-09-14 14:14:13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:06</t>
+          <t>2026-09-14 14:17:18</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>User Classes</t>
+          <t>User Requirements 1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5509,33 +5601,33 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:58</t>
+          <t>2026-09-14 14:14:02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-25 12:14:32</t>
+          <t>2026-09-14 14:17:06</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SCRUM-26</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Layout and Ethical Concerns</t>
+          <t>User Classes</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5549,33 +5641,33 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:52</t>
+          <t>2026-09-14 14:13:58</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:08</t>
+          <t>2026-09-25 12:14:32</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SCRUM-20</t>
+          <t>SCRUM-26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Layout and Ethical Concerns</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5593,34 +5685,34 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:22</t>
+          <t>2026-09-14 14:13:52</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-14 14:08:16</t>
+          <t>2026-09-14 14:17:08</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SCRUM-19</t>
+          <t>SCRUM-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Attend Technical Meeting</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5633,29 +5725,29 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:09</t>
+          <t>2026-09-14 14:07:22</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:44</t>
+          <t>2026-09-14 14:08:16</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SCRUM-18</t>
+          <t>SCRUM-19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Attend Project Management Meeting</t>
+          <t>Attend Technical Meeting</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5673,29 +5765,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-14 14:05:54</t>
+          <t>2026-09-14 14:06:09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:21</t>
+          <t>2026-09-14 14:07:44</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Submit D3, Requirements Specification</t>
+          <t>Attend Project Management Meeting</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5709,38 +5801,38 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-14 11:38:16</t>
+          <t>2026-09-14 14:05:54</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-28 22:43:58</t>
+          <t>2026-09-14 14:06:21</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Submit D3, Requirements Specification</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5749,38 +5841,38 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-14 11:34:01</t>
+          <t>2026-09-14 11:38:16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-28 22:35:13</t>
+          <t>2026-09-28 22:43:58</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Client Meeting (online)</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5789,33 +5881,33 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-14 11:32:26</t>
+          <t>2026-09-14 11:34:01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-28 22:28:42</t>
+          <t>2026-09-28 22:35:13</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SCRUM-14</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Submit A1, Artefacts</t>
+          <t>Client Meeting (online)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5829,33 +5921,33 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-07 12:36:46</t>
+          <t>2026-09-14 11:32:26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:29</t>
+          <t>2026-09-28 22:28:42</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Submit D2, Requirements Elicitation</t>
+          <t>Submit A1, Artefacts</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5869,33 +5961,33 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-07 12:34:14</t>
+          <t>2026-09-07 12:36:46</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:02</t>
+          <t>2026-09-14 18:29:29</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Submit D1, Group Agreement</t>
+          <t>Submit D2, Requirements Elicitation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5909,33 +6001,33 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-07 12:31:35</t>
+          <t>2026-09-07 12:34:14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-28 22:30:22</t>
+          <t>2026-09-28 22:55:02</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Revisit the group agreement</t>
+          <t>Submit D1, Group Agreement</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5949,73 +6041,73 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-04 12:43:07</t>
+          <t>2026-09-07 12:31:35</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-28 22:52:55</t>
+          <t>2026-09-28 22:30:22</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fix issue with level 1</t>
+          <t>Revisit the group agreement</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-04 11:57:26</t>
+          <t>2026-09-04 12:43:07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-25 12:18:34</t>
+          <t>2026-09-28 22:52:55</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fix duplicate word issue in level 2</t>
+          <t>Fix issue with level 1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6025,37 +6117,37 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-04 11:54:17</t>
+          <t>2026-09-04 11:57:26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:53</t>
+          <t>2026-09-25 12:18:34</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-9</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fix case-sensitivity issue</t>
+          <t>Fix duplicate word issue in level 2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6065,7 +6157,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -6073,55 +6165,95 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-04 11:52:58</t>
+          <t>2026-09-04 11:54:17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-28 13:39:15</t>
+          <t>2026-09-28 13:37:53</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Fix case-sensitivity issue</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:52:58</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:57:00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>SCRUM-4</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Subtask 2.1</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Subtask</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>To Do</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="E68" t="n">
         <v>0</v>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-4</t>
         </is>

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="16">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="6">
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,27 +1108,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 17:56:13</t>
+          <t>2026-09-21 19:00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1143,23 +1143,23 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:24</t>
+          <t>2026-09-28 17:56:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1179,33 +1179,33 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:25</t>
+          <t>2026-09-28 11:00:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1246,12 +1246,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:30</t>
+          <t>2026-09-28 11:00:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1292,12 +1292,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:28</t>
+          <t>2026-09-28 11:00:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1338,12 +1338,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:00</t>
+          <t>2026-09-28 11:00:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1384,42 +1384,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1430,42 +1430,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-09-10 19:30:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1476,7 +1476,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1522,12 +1522,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1568,12 +1568,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1614,12 +1614,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1660,12 +1660,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1706,17 +1706,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1731,33 +1731,33 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1798,12 +1798,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1844,12 +1844,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1885,21 +1885,17 @@
       <c r="I18" t="n">
         <v>1.5</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1919,12 +1915,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1935,17 +1931,21 @@
       <c r="I19" t="n">
         <v>1.5</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1986,22 +1986,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2011,43 +2011,43 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2057,33 +2057,33 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2117,19 +2117,19 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2170,37 +2170,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2209,75 +2209,75 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-21 11:53:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-21 11:53:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2287,33 +2287,33 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2354,12 +2354,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2400,12 +2400,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2425,12 +2425,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2446,12 +2446,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2492,12 +2492,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2538,22 +2538,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2563,43 +2563,43 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2609,43 +2609,43 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2655,38 +2655,38 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2711,23 +2711,23 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2757,140 +2757,140 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2899,24 +2899,24 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2991,24 +2991,24 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3023,48 +3023,48 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3079,28 +3079,28 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3125,23 +3125,23 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3161,38 +3161,38 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3221,19 +3221,19 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-10 19:29:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3263,109 +3263,155 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-10 20:22:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>10071</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:14:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>SCRUM-10</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>10369</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>2026-09-16 19:56:00</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>2026-W38</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Calvin Koch</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I50" t="n">
+      <c r="I51" t="n">
         <v>1</v>
       </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3534,7 +3580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3582,17 +3628,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-81</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Worklog Report Solution</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3601,78 +3647,78 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:55</t>
+          <t>2026-09-28 23:02:03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-28 22:56:19</t>
+          <t>2026-09-28 23:02:04</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-81</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCRUM-78</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk analysis and planning</t>
+          <t>Project Management 2 Meeting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-28 13:38:45</t>
+          <t>2026-09-28 22:59:42</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:32</t>
+          <t>2026-09-28 23:01:15</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-80</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCRUM-77</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>List of potential risks</t>
+          <t>Worklog Report Solution</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3681,33 +3727,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:59</t>
+          <t>2026-09-28 22:55:55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:14</t>
+          <t>2026-09-28 23:02:08</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCRUM-76</t>
+          <t>SCRUM-78</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Risk analysis and planning</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3725,34 +3771,34 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:40</t>
+          <t>2026-09-28 13:38:45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42:36</t>
+          <t>2026-09-28 13:40:32</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-77</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sprint 3 planning meeting</t>
+          <t>List of potential risks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3761,38 +3807,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-25 10:49:06</t>
+          <t>2026-09-28 13:37:59</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-28 22:36:57</t>
+          <t>2026-09-28 13:40:14</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-76</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Look through options for time tracking</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3801,33 +3847,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-25 10:40:35</t>
+          <t>2026-09-28 13:37:40</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-28 22:30:53</t>
+          <t>2026-09-28 13:42:36</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCRUM-73</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prepare for Project Management and Tech Lead meeting</t>
+          <t>Sprint 3 planning meeting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3841,33 +3887,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-25 10:32:10</t>
+          <t>2026-09-25 10:49:06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:03</t>
+          <t>2026-09-28 23:01:42</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCRUM-72</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Design Level 4</t>
+          <t>Look through options for time tracking</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3881,33 +3927,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:23</t>
+          <t>2026-09-25 10:40:35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:33</t>
+          <t>2026-09-28 23:01:31</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCRUM-71</t>
+          <t>SCRUM-73</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Attend Technical Lead meeting 3</t>
+          <t>Prepare for Project Management and Tech Lead meeting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3925,29 +3971,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:18</t>
+          <t>2026-09-25 10:32:10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-28 13:39:58</t>
+          <t>2026-09-28 13:40:03</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-72</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Attend Project Management meeting 3</t>
+          <t>Design Level 4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3965,29 +4011,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:17</t>
+          <t>2026-09-23 14:07:23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-28 13:39:56</t>
+          <t>2026-09-23 14:07:33</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCRUM-69</t>
+          <t>SCRUM-71</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Submit A3, Artefacts</t>
+          <t>Attend Technical Lead meeting 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4005,29 +4051,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-23 14:03:04</t>
+          <t>2026-09-23 14:05:18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-28 13:43:04</t>
+          <t>2026-09-28 13:39:58</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCRUM-68</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Initial planning of sprint 3</t>
+          <t>Attend Project Management meeting 3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4037,7 +4083,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -4045,29 +4091,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-23 14:00:17</t>
+          <t>2026-09-23 14:05:17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-23 14:08:42</t>
+          <t>2026-09-28 13:39:56</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-69</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Submit D5, Integration and Project Completion Plan</t>
+          <t>Submit A3, Artefacts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4085,29 +4131,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:53</t>
+          <t>2026-09-23 14:03:04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-23 14:02:47</t>
+          <t>2026-09-28 13:43:04</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SCRUM-66</t>
+          <t>SCRUM-68</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Submit D4, Risk Assesment Plan</t>
+          <t>Initial planning of sprint 3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4117,7 +4163,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -4125,34 +4171,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:26</t>
+          <t>2026-09-23 14:00:17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42:01</t>
+          <t>2026-09-23 14:08:42</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SCRUM-65</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>User Requirements</t>
+          <t>Submit D5, Integration and Project Completion Plan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4165,29 +4211,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-23 13:55:24</t>
+          <t>2026-09-23 13:59:53</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-23 13:56:06</t>
+          <t>2026-09-23 14:02:47</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-66</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Group Meeting 24.09.2026</t>
+          <t>Submit D4, Risk Assesment Plan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4197,37 +4243,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-23 13:48:35</t>
+          <t>2026-09-23 13:59:26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-28 13:53:59</t>
+          <t>2026-09-28 13:42:01</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SCRUM-63</t>
+          <t>SCRUM-65</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Project Handover Code Cleanup</t>
+          <t>User Requirements</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4245,69 +4291,69 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:11</t>
+          <t>2026-09-23 13:55:24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:12</t>
+          <t>2026-09-23 13:56:06</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SCRUM-62</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>Group Meeting 24.09.2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:13</t>
+          <t>2026-09-23 13:48:35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-21 16:10:11</t>
+          <t>2026-09-28 13:53:59</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SCRUM-61</t>
+          <t>SCRUM-63</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Project Handover Code Cleanup</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4325,34 +4371,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-21 16:05:17</t>
+          <t>2026-09-21 16:08:11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:47</t>
+          <t>2026-09-21 16:08:12</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SCRUM-60</t>
+          <t>SCRUM-62</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Level 4 Game Logic</t>
+          <t>Meetings</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4365,29 +4411,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:04</t>
+          <t>2026-09-21 16:06:13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:56</t>
+          <t>2026-09-21 16:10:11</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SCRUM-59</t>
+          <t>SCRUM-61</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Course</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4405,29 +4451,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-21 16:02:30</t>
+          <t>2026-09-21 16:05:17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:57</t>
+          <t>2026-09-21 16:09:47</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-60</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Group Meeting 21.09.2026</t>
+          <t>Level 4 Game Logic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4437,47 +4483,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-21 14:29:42</t>
+          <t>2026-09-21 16:03:04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-28 13:36:42</t>
+          <t>2026-09-21 16:03:56</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SCRUM-57</t>
+          <t>SCRUM-59</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>add more user stories</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -4485,34 +4531,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:53</t>
+          <t>2026-09-21 16:02:30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:49</t>
+          <t>2026-09-21 16:09:57</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SCRUM-56</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Adjusting user requirements and adding more user stories</t>
+          <t>Group Meeting 21.09.2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4521,78 +4567,78 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:48</t>
+          <t>2026-09-21 14:29:42</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-23 22:58:08</t>
+          <t>2026-09-28 13:36:42</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Reorganise the files and folders in the github repo</t>
+          <t>add more user stories</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-21 13:15:32</t>
+          <t>2026-09-21 14:16:53</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-28 14:38:13</t>
+          <t>2026-09-23 13:41:49</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Update D2, Requirements Specification</t>
+          <t>Adjusting user requirements and adding more user stories</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4601,33 +4647,33 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-20 18:22:35</t>
+          <t>2026-09-21 14:16:48</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-28 22:24:30</t>
+          <t>2026-09-23 22:58:08</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SCRUM-53</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Update D1, Group Agreement</t>
+          <t>Reorganise the files and folders in the github repo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4637,37 +4683,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-20 18:15:13</t>
+          <t>2026-09-21 13:15:32</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-24 13:36:15</t>
+          <t>2026-09-28 14:38:13</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SCRUM-52</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Brainstorming drafts of level 4</t>
+          <t>Update D2, Requirements Specification</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4681,33 +4727,33 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-16 11:04:20</t>
+          <t>2026-09-20 18:22:35</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-24 13:33:59</t>
+          <t>2026-09-28 22:24:30</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-53</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Change the en/ett button in level 3 to a field you can fill out</t>
+          <t>Update D1, Group Agreement</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4717,47 +4763,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-16 10:51:26</t>
+          <t>2026-09-20 18:15:13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-28 13:54:24</t>
+          <t>2026-09-24 13:36:15</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fix issue with language change not affecting instructions</t>
+          <t>Brainstorming drafts of level 4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4765,29 +4811,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-16 10:46:54</t>
+          <t>2026-09-16 11:04:20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-28 13:23:24</t>
+          <t>2026-09-24 13:33:59</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sprint planning meeting</t>
+          <t>Change the en/ett button in level 3 to a field you can fill out</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4797,37 +4843,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-16 10:43:45</t>
+          <t>2026-09-16 10:51:26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:21</t>
+          <t>2026-09-28 13:54:24</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fix issue with the educational information page</t>
+          <t>Fix issue with language change not affecting instructions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4837,37 +4883,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39:28</t>
+          <t>2026-09-16 10:46:54</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-24 14:14:59</t>
+          <t>2026-09-28 13:23:24</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Look through the existing code</t>
+          <t>Sprint planning meeting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4877,87 +4923,87 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-16 10:26:40</t>
+          <t>2026-09-16 10:43:45</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-28 13:34:18</t>
+          <t>2026-09-21 16:06:21</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SCRUM-45</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Write Submission</t>
+          <t>Fix issue with the educational information page</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:10</t>
+          <t>2026-09-16 10:39:28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:18</t>
+          <t>2026-09-24 14:14:59</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SCRUM-44</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Write Submission</t>
+          <t>Look through the existing code</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4965,24 +5011,24 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:48</t>
+          <t>2026-09-16 10:26:40</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:01</t>
+          <t>2026-09-28 13:34:18</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SCRUM-43</t>
+          <t>SCRUM-45</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5005,24 +5051,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:35</t>
+          <t>2026-09-14 18:29:10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:42</t>
+          <t>2026-09-14 18:29:18</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SCRUM-42</t>
+          <t>SCRUM-44</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5045,24 +5091,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:17</t>
+          <t>2026-09-14 18:28:48</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:28</t>
+          <t>2026-09-14 18:29:01</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SCRUM-41</t>
+          <t>SCRUM-43</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5085,29 +5131,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:07</t>
+          <t>2026-09-14 18:28:35</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-14 18:30:21</t>
+          <t>2026-09-14 18:28:42</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SCRUM-40</t>
+          <t>SCRUM-42</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Write Submission</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5125,29 +5171,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:58</t>
+          <t>2026-09-14 18:28:17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:10</t>
+          <t>2026-09-14 18:28:28</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SCRUM-39</t>
+          <t>SCRUM-41</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Write Submission</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5165,24 +5211,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:47</t>
+          <t>2026-09-14 18:28:07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:07</t>
+          <t>2026-09-14 18:30:21</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5201,28 +5247,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:32</t>
+          <t>2026-09-14 18:26:58</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-25 12:17:19</t>
+          <t>2026-09-14 18:27:10</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SCRUM-37</t>
+          <t>SCRUM-39</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5245,34 +5291,34 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:05</t>
+          <t>2026-09-14 18:26:47</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:25</t>
+          <t>2026-09-14 18:27:07</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SCRUM-36</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Submit A2, Artefacts</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5281,33 +5327,33 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-14 17:45:50</t>
+          <t>2026-09-14 18:26:32</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-28 13:34:01</t>
+          <t>2026-09-25 12:17:19</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-37</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ethical Considerations</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5317,77 +5363,77 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-14 16:26:10</t>
+          <t>2026-09-14 18:26:05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-27 22:42:27</t>
+          <t>2026-09-14 18:26:25</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Functional Requirements 2</t>
+          <t>Submit A2, Artefacts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:56</t>
+          <t>2026-09-14 17:45:50</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-25 17:15:26</t>
+          <t>2026-09-28 13:34:01</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Functional Requirements 1</t>
+          <t>Ethical Considerations</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5401,33 +5447,33 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:41</t>
+          <t>2026-09-14 16:26:10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-25 17:15:07</t>
+          <t>2026-09-27 22:42:27</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SCRUM-32</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Components</t>
+          <t>Functional Requirements 2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5441,33 +5487,33 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:35</t>
+          <t>2026-09-14 16:25:56</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-24 14:03:01</t>
+          <t>2026-09-25 17:15:26</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SCRUM-31</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Definitions</t>
+          <t>Functional Requirements 1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5481,33 +5527,33 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:28</t>
+          <t>2026-09-14 16:25:41</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:18</t>
+          <t>2026-09-25 17:15:07</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SCRUM-30</t>
+          <t>SCRUM-32</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Components</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5525,29 +5571,29 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:21</t>
+          <t>2026-09-14 16:25:35</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-24 14:03:33</t>
+          <t>2026-09-24 14:03:01</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SCRUM-29</t>
+          <t>SCRUM-31</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>User Requirements 2</t>
+          <t>Definitions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5557,7 +5603,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5565,29 +5611,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:13</t>
+          <t>2026-09-14 16:25:28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:18</t>
+          <t>2026-09-24 13:57:18</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SCRUM-28</t>
+          <t>SCRUM-30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>User Requirements 1</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5597,7 +5643,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5605,29 +5651,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:02</t>
+          <t>2026-09-14 16:25:21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:06</t>
+          <t>2026-09-24 14:03:33</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>User Classes</t>
+          <t>User Requirements 2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5641,33 +5687,33 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:58</t>
+          <t>2026-09-14 14:14:13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-25 12:14:32</t>
+          <t>2026-09-14 14:17:18</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SCRUM-26</t>
+          <t>SCRUM-28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Layout and Ethical Concerns</t>
+          <t>User Requirements 1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5685,29 +5731,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:52</t>
+          <t>2026-09-14 14:14:02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:08</t>
+          <t>2026-09-14 14:17:06</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SCRUM-20</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>User Classes</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5721,38 +5767,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:22</t>
+          <t>2026-09-14 14:13:58</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-14 14:08:16</t>
+          <t>2026-09-25 12:14:32</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SCRUM-19</t>
+          <t>SCRUM-26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Attend Technical Meeting</t>
+          <t>Layout and Ethical Concerns</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5765,34 +5811,34 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:09</t>
+          <t>2026-09-14 14:13:52</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:44</t>
+          <t>2026-09-14 14:17:08</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SCRUM-18</t>
+          <t>SCRUM-20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Attend Project Management Meeting</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5805,29 +5851,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-14 14:05:54</t>
+          <t>2026-09-14 14:07:22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:21</t>
+          <t>2026-09-14 14:08:16</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Submit D3, Requirements Specification</t>
+          <t>Attend Technical Meeting</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5841,38 +5887,38 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-14 11:38:16</t>
+          <t>2026-09-14 14:06:09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-28 22:43:58</t>
+          <t>2026-09-14 14:07:44</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Attend Project Management Meeting</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5881,33 +5927,33 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-14 11:34:01</t>
+          <t>2026-09-14 14:05:54</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-28 22:35:13</t>
+          <t>2026-09-14 14:06:21</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Client Meeting (online)</t>
+          <t>Submit D3, Requirements Specification</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5921,38 +5967,38 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.5</v>
+        <v>18</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-14 11:32:26</t>
+          <t>2026-09-14 11:38:16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-28 22:28:42</t>
+          <t>2026-09-28 22:43:58</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SCRUM-14</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Submit A1, Artefacts</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5961,33 +6007,33 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-07 12:36:46</t>
+          <t>2026-09-14 11:34:01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:29</t>
+          <t>2026-09-28 22:35:13</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Submit D2, Requirements Elicitation</t>
+          <t>Client Meeting (online)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6001,33 +6047,33 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-07 12:34:14</t>
+          <t>2026-09-14 11:32:26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:02</t>
+          <t>2026-09-28 22:28:42</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Submit D1, Group Agreement</t>
+          <t>Submit A1, Artefacts</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6041,33 +6087,33 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-07 12:31:35</t>
+          <t>2026-09-07 12:36:46</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-28 22:30:22</t>
+          <t>2026-09-14 18:29:29</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Revisit the group agreement</t>
+          <t>Submit D2, Requirements Elicitation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6081,113 +6127,113 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-04 12:43:07</t>
+          <t>2026-09-07 12:34:14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-28 22:52:55</t>
+          <t>2026-09-28 22:55:02</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fix issue with level 1</t>
+          <t>Submit D1, Group Agreement</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-04 11:57:26</t>
+          <t>2026-09-07 12:31:35</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-25 12:18:34</t>
+          <t>2026-09-28 22:30:22</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fix duplicate word issue in level 2</t>
+          <t>Revisit the group agreement</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-04 11:54:17</t>
+          <t>2026-09-04 12:43:07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:53</t>
+          <t>2026-09-28 22:52:55</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fix case-sensitivity issue</t>
+          <t>Fix issue with level 1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6201,43 +6247,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-04 11:52:58</t>
+          <t>2026-09-04 11:57:26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-28 22:57:00</t>
+          <t>2026-09-25 12:18:34</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SCRUM-4</t>
+          <t>SCRUM-9</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Subtask 2.1</t>
+          <t>Fix duplicate word issue in level 2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -6245,15 +6291,95 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>2026-09-04 11:54:17</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:37:53</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Fix case-sensitivity issue</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:52:58</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:57:00</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SCRUM-4</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Subtask 2.1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Subtask</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-4</t>
         </is>

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="25">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="15">
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,73 +1108,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 19:00:00</t>
+          <t>2026-09-29 07:20:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SCRUM-80</t>
+          <t>SCRUM-82</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-28 17:56:13</t>
+          <t>2026-09-21 19:00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1189,23 +1189,23 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:24</t>
+          <t>2026-09-28 17:56:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1225,33 +1225,33 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:25</t>
+          <t>2026-09-28 11:00:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1292,12 +1292,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:30</t>
+          <t>2026-09-28 11:00:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1338,12 +1338,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:28</t>
+          <t>2026-09-28 11:00:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1384,12 +1384,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:00</t>
+          <t>2026-09-28 11:00:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1430,42 +1430,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1476,42 +1476,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-09-10 19:30:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1522,7 +1522,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1568,12 +1568,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1614,12 +1614,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1660,12 +1660,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1706,12 +1706,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1731,12 +1731,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1752,17 +1752,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1777,33 +1777,33 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1844,12 +1844,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1890,12 +1890,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1931,21 +1931,17 @@
       <c r="I19" t="n">
         <v>1.5</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1965,12 +1961,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1981,17 +1977,21 @@
       <c r="I20" t="n">
         <v>1.5</v>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2032,22 +2032,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2057,43 +2057,43 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2103,33 +2103,33 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2195,12 +2195,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2216,37 +2216,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2255,75 +2255,75 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-21 11:53:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-21 11:53:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2333,33 +2333,33 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2400,12 +2400,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2425,12 +2425,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2446,12 +2446,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2492,12 +2492,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2538,12 +2538,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2584,22 +2584,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2609,43 +2609,43 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2655,43 +2655,43 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2701,38 +2701,38 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2757,23 +2757,23 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2803,140 +2803,140 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2945,24 +2945,24 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2998,12 +2998,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3037,24 +3037,24 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3069,48 +3069,48 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3125,28 +3125,28 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3171,23 +3171,23 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3207,38 +3207,38 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3267,19 +3267,19 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-10 19:29:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3309,109 +3309,201 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-10 20:22:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>10071</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:14:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>SCRUM-10</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:44:17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>SCRUM-9</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>10369</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>2026-09-16 19:56:00</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>2026-W38</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>SCRUM Sprint 2</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Calvin Koch</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I51" t="n">
+      <c r="I53" t="n">
         <v>1</v>
       </c>
-      <c r="J51" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3580,7 +3672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3628,92 +3720,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCRUM-81</t>
+          <t>SCRUM-82</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Update the User Interface.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:02:03</t>
+          <t>2026-09-29 13:16:11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-28 23:02:04</t>
+          <t>2026-09-29 13:21:23</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-81</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-82</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCRUM-80</t>
+          <t>SCRUM-81</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Project Management 2 Meeting</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-28 22:59:42</t>
+          <t>2026-09-28 23:02:03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-28 23:01:15</t>
+          <t>2026-09-28 23:02:04</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-80</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-81</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Worklog Report Solution</t>
+          <t>Project Management 2 Meeting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3723,42 +3815,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:55</t>
+          <t>2026-09-28 22:59:42</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-28 23:02:08</t>
+          <t>2026-09-28 23:01:15</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-80</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCRUM-78</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Risk analysis and planning</t>
+          <t>Worklog Report Solution</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3767,33 +3859,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-28 13:38:45</t>
+          <t>2026-09-28 22:55:55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:32</t>
+          <t>2026-09-28 23:02:08</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCRUM-77</t>
+          <t>SCRUM-78</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>List of potential risks</t>
+          <t>Risk analysis and planning</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3811,29 +3903,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:59</t>
+          <t>2026-09-28 13:38:45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:14</t>
+          <t>2026-09-28 13:40:32</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCRUM-76</t>
+          <t>SCRUM-77</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>List of potential risks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3851,34 +3943,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:40</t>
+          <t>2026-09-28 13:37:59</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42:36</t>
+          <t>2026-09-28 13:40:14</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-76</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sprint 3 planning meeting</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3887,33 +3979,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-25 10:49:06</t>
+          <t>2026-09-28 13:37:40</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-28 23:01:42</t>
+          <t>2026-09-28 13:42:36</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Look through options for time tracking</t>
+          <t>Sprint 3 planning meeting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3927,33 +4019,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-25 10:40:35</t>
+          <t>2026-09-25 10:49:06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:01:31</t>
+          <t>2026-09-28 23:01:42</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCRUM-73</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prepare for Project Management and Tech Lead meeting</t>
+          <t>Look through options for time tracking</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3967,33 +4059,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-25 10:32:10</t>
+          <t>2026-09-25 10:40:35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:03</t>
+          <t>2026-09-28 23:01:31</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCRUM-72</t>
+          <t>SCRUM-73</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Design Level 4</t>
+          <t>Prepare for Project Management and Tech Lead meeting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4011,29 +4103,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:23</t>
+          <t>2026-09-25 10:32:10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:33</t>
+          <t>2026-09-28 13:40:03</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCRUM-71</t>
+          <t>SCRUM-72</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Attend Technical Lead meeting 3</t>
+          <t>Design Level 4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4051,29 +4143,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:18</t>
+          <t>2026-09-23 14:07:23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-28 13:39:58</t>
+          <t>2026-09-23 14:07:33</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-71</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Attend Project Management meeting 3</t>
+          <t>Attend Technical Lead meeting 3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4091,29 +4183,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:17</t>
+          <t>2026-09-23 14:05:18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-28 13:39:56</t>
+          <t>2026-09-28 13:39:58</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SCRUM-69</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Submit A3, Artefacts</t>
+          <t>Attend Project Management meeting 3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4131,29 +4223,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-23 14:03:04</t>
+          <t>2026-09-23 14:05:17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-28 13:43:04</t>
+          <t>2026-09-28 13:39:56</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SCRUM-68</t>
+          <t>SCRUM-69</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Initial planning of sprint 3</t>
+          <t>Submit A3, Artefacts</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4163,7 +4255,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -4171,29 +4263,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-23 14:00:17</t>
+          <t>2026-09-23 14:03:04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-23 14:08:42</t>
+          <t>2026-09-28 13:43:04</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-68</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Submit D5, Integration and Project Completion Plan</t>
+          <t>Initial planning of sprint 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4203,7 +4295,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -4211,29 +4303,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:53</t>
+          <t>2026-09-23 14:00:17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-23 14:02:47</t>
+          <t>2026-09-23 14:08:42</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SCRUM-66</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Submit D4, Risk Assesment Plan</t>
+          <t>Submit D5, Integration and Project Completion Plan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4251,34 +4343,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:26</t>
+          <t>2026-09-23 13:59:53</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42:01</t>
+          <t>2026-09-23 14:02:47</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SCRUM-65</t>
+          <t>SCRUM-66</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>User Requirements</t>
+          <t>Submit D4, Risk Assesment Plan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4291,109 +4383,109 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-23 13:55:24</t>
+          <t>2026-09-23 13:59:26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-23 13:56:06</t>
+          <t>2026-09-28 13:42:01</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-65</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Group Meeting 24.09.2026</t>
+          <t>User Requirements</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-23 13:48:35</t>
+          <t>2026-09-23 13:55:24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-28 13:53:59</t>
+          <t>2026-09-23 13:56:06</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SCRUM-63</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Project Handover Code Cleanup</t>
+          <t>Group Meeting 24.09.2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:11</t>
+          <t>2026-09-23 13:48:35</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:12</t>
+          <t>2026-09-28 13:53:59</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SCRUM-62</t>
+          <t>SCRUM-63</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>Project Handover Code Cleanup</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4411,29 +4503,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:13</t>
+          <t>2026-09-21 16:08:11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-21 16:10:11</t>
+          <t>2026-09-21 16:08:12</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SCRUM-61</t>
+          <t>SCRUM-62</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Meetings</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4451,34 +4543,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-21 16:05:17</t>
+          <t>2026-09-21 16:06:13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:47</t>
+          <t>2026-09-21 16:10:11</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SCRUM-60</t>
+          <t>SCRUM-61</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Level 4 Game Logic</t>
+          <t>Course</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4491,34 +4583,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:04</t>
+          <t>2026-09-21 16:05:17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:56</t>
+          <t>2026-09-21 16:09:47</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SCRUM-59</t>
+          <t>SCRUM-60</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 4 Game Logic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4531,74 +4623,74 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-21 16:02:30</t>
+          <t>2026-09-21 16:03:04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:57</t>
+          <t>2026-09-21 16:03:56</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-59</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Group Meeting 21.09.2026</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-21 14:29:42</t>
+          <t>2026-09-21 16:02:30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-28 13:36:42</t>
+          <t>2026-09-21 16:09:57</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SCRUM-57</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>add more user stories</t>
+          <t>Group Meeting 21.09.2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4607,33 +4699,33 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:53</t>
+          <t>2026-09-21 14:29:42</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:49</t>
+          <t>2026-09-28 13:36:42</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SCRUM-56</t>
+          <t>SCRUM-57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Adjusting user requirements and adding more user stories</t>
+          <t>add more user stories</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4651,69 +4743,69 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:48</t>
+          <t>2026-09-21 14:16:53</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-23 22:58:08</t>
+          <t>2026-09-23 13:41:49</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-56</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Reorganise the files and folders in the github repo</t>
+          <t>Adjusting user requirements and adding more user stories</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-21 13:15:32</t>
+          <t>2026-09-21 14:16:48</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-28 14:38:13</t>
+          <t>2026-09-23 22:58:08</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Update D2, Requirements Specification</t>
+          <t>Reorganise the files and folders in the github repo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4723,37 +4815,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-20 18:22:35</t>
+          <t>2026-09-21 13:15:32</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-28 22:24:30</t>
+          <t>2026-09-28 14:38:13</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SCRUM-53</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Update D1, Group Agreement</t>
+          <t>Update D2, Requirements Specification</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4767,33 +4859,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-20 18:15:13</t>
+          <t>2026-09-20 18:22:35</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-24 13:36:15</t>
+          <t>2026-09-28 22:24:30</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SCRUM-52</t>
+          <t>SCRUM-53</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Brainstorming drafts of level 4</t>
+          <t>Update D1, Group Agreement</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4811,29 +4903,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-16 11:04:20</t>
+          <t>2026-09-20 18:15:13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-24 13:33:59</t>
+          <t>2026-09-24 13:36:15</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-52</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Change the en/ett button in level 3 to a field you can fill out</t>
+          <t>Brainstorming drafts of level 4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4843,42 +4935,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-16 10:51:26</t>
+          <t>2026-09-16 11:04:20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-28 13:54:24</t>
+          <t>2026-09-24 13:33:59</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fix issue with language change not affecting instructions</t>
+          <t>Change the en/ett button in level 3 to a field you can fill out</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4887,163 +4979,163 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-16 10:46:54</t>
+          <t>2026-09-16 10:51:26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-28 13:23:24</t>
+          <t>2026-09-28 13:54:24</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sprint planning meeting</t>
+          <t>Fix issue with language change not affecting instructions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-16 10:43:45</t>
+          <t>2026-09-16 10:46:54</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:21</t>
+          <t>2026-09-28 13:23:24</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fix issue with the educational information page</t>
+          <t>Sprint planning meeting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39:28</t>
+          <t>2026-09-16 10:43:45</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-24 14:14:59</t>
+          <t>2026-09-21 16:06:21</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Look through the existing code</t>
+          <t>Fix issue with the educational information page</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-16 10:26:40</t>
+          <t>2026-09-16 10:39:28</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-28 13:34:18</t>
+          <t>2026-09-24 14:14:59</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SCRUM-45</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Write Submission</t>
+          <t>Look through the existing code</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -5051,24 +5143,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:10</t>
+          <t>2026-09-16 10:26:40</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:18</t>
+          <t>2026-09-28 13:34:18</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SCRUM-44</t>
+          <t>SCRUM-45</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5091,24 +5183,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:48</t>
+          <t>2026-09-14 18:29:10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:01</t>
+          <t>2026-09-14 18:29:18</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SCRUM-43</t>
+          <t>SCRUM-44</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5131,24 +5223,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:35</t>
+          <t>2026-09-14 18:28:48</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:42</t>
+          <t>2026-09-14 18:29:01</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SCRUM-42</t>
+          <t>SCRUM-43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5171,24 +5263,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:17</t>
+          <t>2026-09-14 18:28:35</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:28</t>
+          <t>2026-09-14 18:28:42</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SCRUM-41</t>
+          <t>SCRUM-42</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5211,29 +5303,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:07</t>
+          <t>2026-09-14 18:28:17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-14 18:30:21</t>
+          <t>2026-09-14 18:28:28</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SCRUM-40</t>
+          <t>SCRUM-41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Write Submission</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5251,24 +5343,24 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:58</t>
+          <t>2026-09-14 18:28:07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:10</t>
+          <t>2026-09-14 18:30:21</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SCRUM-39</t>
+          <t>SCRUM-40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5291,24 +5383,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:47</t>
+          <t>2026-09-14 18:26:58</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:07</t>
+          <t>2026-09-14 18:27:10</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-39</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5327,28 +5419,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:32</t>
+          <t>2026-09-14 18:26:47</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-25 12:17:19</t>
+          <t>2026-09-14 18:27:07</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SCRUM-37</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5367,38 +5459,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:05</t>
+          <t>2026-09-14 18:26:32</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:25</t>
+          <t>2026-09-25 12:17:19</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SCRUM-36</t>
+          <t>SCRUM-37</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Submit A2, Artefacts</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5411,69 +5503,69 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-14 17:45:50</t>
+          <t>2026-09-14 18:26:05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-28 13:34:01</t>
+          <t>2026-09-14 18:26:25</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-36</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ethical Considerations</t>
+          <t>Submit A2, Artefacts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-14 16:26:10</t>
+          <t>2026-09-14 17:45:50</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-27 22:42:27</t>
+          <t>2026-09-28 13:34:01</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Functional Requirements 2</t>
+          <t>Ethical Considerations</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5487,33 +5579,33 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:56</t>
+          <t>2026-09-14 16:26:10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-25 17:15:26</t>
+          <t>2026-09-27 22:42:27</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Functional Requirements 1</t>
+          <t>Functional Requirements 2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5527,33 +5619,33 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:41</t>
+          <t>2026-09-14 16:25:56</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-25 17:15:07</t>
+          <t>2026-09-25 17:15:26</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SCRUM-32</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Components</t>
+          <t>Functional Requirements 1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5567,33 +5659,33 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:35</t>
+          <t>2026-09-14 16:25:41</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-24 14:03:01</t>
+          <t>2026-09-25 17:15:07</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SCRUM-31</t>
+          <t>SCRUM-32</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Definitions</t>
+          <t>Components</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5611,29 +5703,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:28</t>
+          <t>2026-09-14 16:25:35</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:18</t>
+          <t>2026-09-24 14:03:01</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SCRUM-30</t>
+          <t>SCRUM-31</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Definitions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5651,29 +5743,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:21</t>
+          <t>2026-09-14 16:25:28</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-24 14:03:33</t>
+          <t>2026-09-24 13:57:18</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SCRUM-29</t>
+          <t>SCRUM-30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>User Requirements 2</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5683,7 +5775,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -5691,29 +5783,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:13</t>
+          <t>2026-09-14 16:25:21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:18</t>
+          <t>2026-09-24 14:03:33</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SCRUM-28</t>
+          <t>SCRUM-29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>User Requirements 1</t>
+          <t>User Requirements 2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5731,29 +5823,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:02</t>
+          <t>2026-09-14 14:14:13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:06</t>
+          <t>2026-09-14 14:17:18</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-28</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>User Classes</t>
+          <t>User Requirements 1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5767,33 +5859,33 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:58</t>
+          <t>2026-09-14 14:14:02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-25 12:14:32</t>
+          <t>2026-09-14 14:17:06</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SCRUM-26</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Layout and Ethical Concerns</t>
+          <t>User Classes</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5807,33 +5899,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:52</t>
+          <t>2026-09-14 14:13:58</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:08</t>
+          <t>2026-09-25 12:14:32</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SCRUM-20</t>
+          <t>SCRUM-26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Layout and Ethical Concerns</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5851,34 +5943,34 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:22</t>
+          <t>2026-09-14 14:13:52</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-14 14:08:16</t>
+          <t>2026-09-14 14:17:08</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SCRUM-19</t>
+          <t>SCRUM-20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Attend Technical Meeting</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5891,29 +5983,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:09</t>
+          <t>2026-09-14 14:07:22</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:44</t>
+          <t>2026-09-14 14:08:16</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SCRUM-18</t>
+          <t>SCRUM-19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Attend Project Management Meeting</t>
+          <t>Attend Technical Meeting</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5931,29 +6023,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-14 14:05:54</t>
+          <t>2026-09-14 14:06:09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:21</t>
+          <t>2026-09-14 14:07:44</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Submit D3, Requirements Specification</t>
+          <t>Attend Project Management Meeting</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5967,38 +6059,38 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-14 11:38:16</t>
+          <t>2026-09-14 14:05:54</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-28 22:43:58</t>
+          <t>2026-09-14 14:06:21</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Submit D3, Requirements Specification</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6007,38 +6099,38 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-14 11:34:01</t>
+          <t>2026-09-14 11:38:16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-28 22:35:13</t>
+          <t>2026-09-28 22:43:58</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Client Meeting (online)</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6047,33 +6139,33 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-14 11:32:26</t>
+          <t>2026-09-14 11:34:01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-28 22:28:42</t>
+          <t>2026-09-28 22:35:13</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SCRUM-14</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Submit A1, Artefacts</t>
+          <t>Client Meeting (online)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6087,33 +6179,33 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-07 12:36:46</t>
+          <t>2026-09-14 11:32:26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:29</t>
+          <t>2026-09-28 22:28:42</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-14</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Submit D2, Requirements Elicitation</t>
+          <t>Submit A1, Artefacts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6127,33 +6219,33 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-07 12:34:14</t>
+          <t>2026-09-07 12:36:46</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:02</t>
+          <t>2026-09-14 18:29:29</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Submit D1, Group Agreement</t>
+          <t>Submit D2, Requirements Elicitation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6167,33 +6259,33 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-07 12:31:35</t>
+          <t>2026-09-07 12:34:14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-28 22:30:22</t>
+          <t>2026-09-28 22:55:02</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Revisit the group agreement</t>
+          <t>Submit D1, Group Agreement</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6207,73 +6299,73 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-04 12:43:07</t>
+          <t>2026-09-07 12:31:35</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-28 22:52:55</t>
+          <t>2026-09-28 22:30:22</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fix issue with level 1</t>
+          <t>Revisit the group agreement</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-04 11:57:26</t>
+          <t>2026-09-04 12:43:07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-25 12:18:34</t>
+          <t>2026-09-28 22:52:55</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fix duplicate word issue in level 2</t>
+          <t>Fix issue with level 1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6283,37 +6375,37 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-04 11:54:17</t>
+          <t>2026-09-04 11:57:26</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:53</t>
+          <t>2026-09-25 12:18:34</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-9</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fix case-sensitivity issue</t>
+          <t>Fix duplicate word issue in level 2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6327,59 +6419,99 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-04 11:52:58</t>
+          <t>2026-09-04 11:54:17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-28 22:57:00</t>
+          <t>2026-09-29 13:14:37</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Fix case-sensitivity issue</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:52:58</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:57:00</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>SCRUM-4</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Subtask 2.1</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Subtask</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>To Do</t>
         </is>
       </c>
-      <c r="E70" t="n">
+      <c r="E71" t="n">
         <v>0</v>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-4</t>
         </is>

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -809,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,26 +852,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
@@ -882,11 +882,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13.5</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="6">
@@ -897,11 +897,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="7">
@@ -912,11 +912,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8">
@@ -927,11 +927,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -942,26 +942,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="11">
@@ -972,11 +972,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -987,11 +987,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1002,11 +1002,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -1017,11 +1017,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1032,10 +1032,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Seleman Hassan</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1050,7 +1065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3504,6 +3519,52 @@
         <v>1</v>
       </c>
       <c r="J53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>10437</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:00:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Klas Widebeck</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3602,7 +3663,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3637,7 +3698,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4815,7 +4876,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -4828,7 +4889,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-28 14:38:13</t>
+          <t>2026-09-30 12:37:29</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5095,7 +5156,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -5108,7 +5169,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-24 14:14:59</t>
+          <t>2026-09-30 12:38:00</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5575,7 +5636,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5588,7 +5649,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-27 22:42:27</t>
+          <t>2026-09-30 12:43:14</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5615,7 +5676,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5628,7 +5689,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-25 17:15:26</t>
+          <t>2026-09-30 12:43:12</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5655,7 +5716,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5668,7 +5729,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-25 17:15:07</t>
+          <t>2026-09-30 12:43:11</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5695,7 +5756,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5708,7 +5769,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-24 14:03:01</t>
+          <t>2026-09-30 12:43:08</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5735,7 +5796,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5748,7 +5809,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:18</t>
+          <t>2026-09-30 12:43:01</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5775,7 +5836,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -5788,7 +5849,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-24 14:03:33</t>
+          <t>2026-09-30 12:43:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6375,7 +6436,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -6388,7 +6449,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-25 12:18:34</t>
+          <t>2026-09-30 12:37:26</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6455,11 +6516,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6468,7 +6529,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-28 22:57:00</t>
+          <t>2026-09-30 12:36:51</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="23">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="14">
@@ -1065,7 +1065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1491,42 +1491,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1537,42 +1537,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-09-10 19:30:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1583,7 +1583,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1767,12 +1767,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1813,17 +1813,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1838,33 +1838,33 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1905,12 +1905,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1951,12 +1951,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1992,21 +1992,17 @@
       <c r="I20" t="n">
         <v>1.5</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2026,12 +2022,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2042,17 +2038,21 @@
       <c r="I21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2093,22 +2093,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2118,43 +2118,43 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2164,33 +2164,33 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2224,19 +2224,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2277,37 +2277,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2316,75 +2316,75 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-21 11:53:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-21 11:53:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2394,33 +2394,33 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2461,12 +2461,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2553,12 +2553,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2599,12 +2599,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2645,22 +2645,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2670,43 +2670,43 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2716,43 +2716,43 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2762,38 +2762,38 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2818,23 +2818,23 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2864,140 +2864,140 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3006,24 +3006,24 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3059,12 +3059,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3098,24 +3098,24 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3130,48 +3130,48 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3186,28 +3186,28 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3232,23 +3232,23 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3268,38 +3268,38 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3328,19 +3328,19 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-10 19:29:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3370,88 +3370,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-10 20:22:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-29 07:44:17</t>
+          <t>2026-09-18 09:14:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3466,105 +3462,155 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-10</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J52" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-16 19:56:00</t>
+          <t>2026-09-29 07:44:17</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-9</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>10437</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>2026-09-10 11:00:00</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>2026-W37</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I54" t="n">
+      <c r="I55" t="n">
         <v>5</v>
       </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4076,11 +4122,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -4089,7 +4135,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:01:42</t>
+          <t>2026-10-01 11:39:18</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -4396,7 +4442,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -4409,7 +4455,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-23 14:02:47</t>
+          <t>2026-10-01 11:39:31</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4449,7 +4495,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42:01</t>
+          <t>2026-10-01 11:39:48</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1065,7 +1065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1583,27 +1583,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-01 09:00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1618,18 +1618,18 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1767,12 +1767,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1813,12 +1813,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1859,17 +1859,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1884,33 +1884,33 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1951,12 +1951,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1997,12 +1997,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2038,21 +2038,17 @@
       <c r="I21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2072,12 +2068,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2088,17 +2084,21 @@
       <c r="I22" t="n">
         <v>1.5</v>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2139,22 +2139,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2164,43 +2164,43 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2210,33 +2210,33 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2270,19 +2270,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2323,37 +2323,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2362,75 +2362,75 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-21 11:53:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-21 11:53:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2440,33 +2440,33 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2553,12 +2553,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2599,12 +2599,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2645,12 +2645,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2691,22 +2691,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2716,43 +2716,43 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2762,43 +2762,43 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2808,38 +2808,38 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2864,23 +2864,23 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2910,140 +2910,140 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3052,24 +3052,24 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3105,12 +3105,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3144,24 +3144,24 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3176,48 +3176,48 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3232,28 +3232,28 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3278,23 +3278,23 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3314,38 +3314,38 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3374,19 +3374,19 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-10 19:29:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3416,88 +3416,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-10 20:22:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-29 07:44:17</t>
+          <t>2026-09-18 09:14:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3512,105 +3508,155 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-10</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J53" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-16 19:56:00</t>
+          <t>2026-09-29 07:44:17</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-9</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>10437</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>2026-09-10 11:00:00</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>2026-W37</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I55" t="n">
+      <c r="I56" t="n">
         <v>5</v>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4446,7 +4492,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4455,7 +4501,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-01 11:39:31</t>
+          <t>2026-10-01 15:08:32</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -796,6 +796,96 @@
       </c>
       <c r="C25" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-W41</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Anton Hedlund</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-W41</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-W41</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Einar Eriksson Wahlin</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-W41</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Klas Widebeck</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-W41</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-W41</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Seleman Hassan</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -976,7 +1066,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1096,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -1065,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1629,27 +1719,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-05 07:49:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1664,18 +1754,18 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1700,12 +1790,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1721,12 +1811,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1746,12 +1836,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1767,12 +1857,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1792,12 +1882,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1813,12 +1903,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1838,12 +1928,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1859,12 +1949,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1884,12 +1974,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1905,17 +1995,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1930,33 +2020,33 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1976,12 +2066,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1997,12 +2087,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2022,12 +2112,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2043,12 +2133,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2068,12 +2158,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2084,21 +2174,17 @@
       <c r="I22" t="n">
         <v>1.5</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2118,12 +2204,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2134,17 +2220,21 @@
       <c r="I23" t="n">
         <v>1.5</v>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2164,12 +2254,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2185,22 +2275,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2210,43 +2300,43 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2256,33 +2346,33 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2302,12 +2392,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2316,19 +2406,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2348,12 +2438,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2369,37 +2459,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2408,75 +2498,75 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-21 11:53:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-21 11:53:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2486,79 +2576,79 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-10-04 13:27:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2578,12 +2668,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2599,12 +2689,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2624,12 +2714,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2645,12 +2735,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2670,12 +2760,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2691,12 +2781,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2716,12 +2806,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2737,22 +2827,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2762,38 +2852,38 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2808,17 +2898,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2829,17 +2919,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2854,17 +2944,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2875,22 +2965,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2900,38 +2990,38 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2956,186 +3046,186 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3144,24 +3234,24 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3176,12 +3266,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3190,24 +3280,24 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3222,94 +3312,94 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3324,28 +3414,28 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3360,17 +3450,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3381,17 +3471,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3416,28 +3506,28 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3452,17 +3542,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3473,113 +3563,109 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-10 19:29:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-29 07:44:17</t>
+          <t>2026-09-10 20:22:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-16 19:56:00</t>
+          <t>2026-09-18 09:14:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3594,69 +3680,165 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-10</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:44:17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>SCRUM-9</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>10437</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>2026-09-10 11:00:00</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>2026-W37</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I56" t="n">
+      <c r="I58" t="n">
         <v>5</v>
       </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4261,7 +4443,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:03</t>
+          <t>2026-10-05 11:53:53</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4492,7 +4674,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4501,7 +4683,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-01 15:08:32</t>
+          <t>2026-10-05 11:49:56</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5172,7 +5354,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5181,7 +5363,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-28 13:23:24</t>
+          <t>2026-10-04 20:28:06</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -1155,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1673,22 +1673,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:00</t>
+          <t>2026-10-05 13:00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1708,33 +1708,33 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-05 07:49:53</t>
+          <t>2026-10-01 09:00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1758,34 +1758,34 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-05 07:49:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1800,18 +1800,18 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1857,12 +1857,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1903,12 +1903,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1949,12 +1949,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2041,17 +2041,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2066,33 +2066,33 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2179,12 +2179,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2220,21 +2220,17 @@
       <c r="I23" t="n">
         <v>1.5</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2254,12 +2250,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2270,17 +2266,21 @@
       <c r="I24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2321,22 +2321,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2346,43 +2346,43 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2392,33 +2392,33 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2452,19 +2452,19 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2505,37 +2505,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2544,95 +2544,95 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-21 11:53:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-04 13:27:59</t>
+          <t>2026-09-21 11:53:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2643,58 +2643,58 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-10-04 13:27:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2735,12 +2735,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2781,12 +2781,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2827,12 +2827,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2873,12 +2873,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2919,22 +2919,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2944,43 +2944,43 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2990,43 +2990,43 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3036,38 +3036,38 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3092,23 +3092,23 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3138,140 +3138,140 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3280,24 +3280,24 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3372,24 +3372,24 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3404,48 +3404,48 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3460,28 +3460,28 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3506,23 +3506,23 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3542,38 +3542,38 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3602,19 +3602,19 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-10 19:29:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3644,88 +3644,84 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-10 20:22:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-29 07:44:17</t>
+          <t>2026-09-18 09:14:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3740,105 +3736,155 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-10</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-16 19:56:00</t>
+          <t>2026-09-29 07:44:17</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-9</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>10437</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>2026-09-10 11:00:00</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>2026-W37</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I58" t="n">
+      <c r="I59" t="n">
         <v>5</v>
       </c>
-      <c r="J58" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4510,7 +4556,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -4523,7 +4569,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-28 13:39:58</t>
+          <t>2026-10-06 16:34:25</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4550,11 +4596,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -4563,7 +4609,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-28 13:39:56</t>
+          <t>2026-10-06 16:34:14</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="22">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="13">
@@ -1155,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1213,22 +1213,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 07:20:10</t>
+          <t>2026-10-07 10:43:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1238,48 +1238,48 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SCRUM-82</t>
+          <t>SCRUM-84</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21 19:00:00</t>
+          <t>2026-10-07 10:22:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1294,28 +1294,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SCRUM-80</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28 17:56:13</t>
+          <t>2026-09-29 07:20:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1330,79 +1330,79 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-82</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:24</t>
+          <t>2026-09-21 19:00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:25</t>
+          <t>2026-09-28 17:56:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1422,33 +1422,33 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:30</t>
+          <t>2026-09-28 11:00:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1489,12 +1489,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:28</t>
+          <t>2026-09-28 11:00:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1535,12 +1535,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:00</t>
+          <t>2026-09-28 11:00:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:00</t>
+          <t>2026-09-28 11:00:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1627,42 +1627,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1673,22 +1673,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-05 13:00:00</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1719,58 +1719,58 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:00</t>
+          <t>2026-09-10 19:30:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-05 07:49:53</t>
+          <t>2026-10-05 13:00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1800,38 +1800,38 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-01 09:00:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1846,84 +1846,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-05 07:49:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-10-02 11:40:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1938,69 +1938,69 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-10-07 09:42:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2041,12 +2041,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2087,17 +2087,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2122,28 +2122,28 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2158,38 +2158,38 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2204,38 +2204,38 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2250,37 +2250,33 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2300,12 +2296,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2321,12 +2317,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2346,12 +2342,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2367,22 +2363,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2392,38 +2388,38 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2438,38 +2434,42 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2484,38 +2484,38 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2540,53 +2540,53 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2597,17 +2597,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-21 11:53:00</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2622,48 +2622,48 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-04 13:27:59</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2678,33 +2678,33 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2714,89 +2714,89 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-21 11:53:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2806,79 +2806,79 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-10-04 13:27:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2919,12 +2919,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2965,22 +2965,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2990,38 +2990,38 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3036,17 +3036,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -3057,22 +3057,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3092,33 +3092,33 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3128,38 +3128,38 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3174,48 +3174,48 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3230,74 +3230,74 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3312,38 +3312,38 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>0.25</v>
       </c>
       <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3358,48 +3358,48 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3414,176 +3414,176 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3598,38 +3598,38 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3655,17 +3655,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -3701,77 +3701,73 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-29 07:44:17</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3786,38 +3782,38 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-16 19:56:00</t>
+          <t>2026-09-10 19:29:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3832,7 +3828,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -3843,48 +3839,236 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>10366</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-10 20:22:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>SCRUM-11</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>10071</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:14:00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>SCRUM-10</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:44:17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>SCRUM-9</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>10437</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>2026-09-10 11:00:00</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>2026-W37</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I59" t="n">
+      <c r="I63" t="n">
         <v>5</v>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4053,7 +4237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4101,92 +4285,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCRUM-82</t>
+          <t>SCRUM-84</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Update the User Interface.</t>
+          <t>Correct and resubmit D3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:16:11</t>
+          <t>2026-10-07 13:07:21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:21:23</t>
+          <t>2026-10-07 13:43:15</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-82</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-84</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCRUM-81</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Meeting 7.10.2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-28 23:02:03</t>
+          <t>2026-10-07 12:47:48</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-28 23:02:04</t>
+          <t>2026-10-07 13:22:44</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-81</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-83</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCRUM-80</t>
+          <t>SCRUM-82</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Project Management 2 Meeting</t>
+          <t>Update the User Interface.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4196,42 +4380,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-28 22:59:42</t>
+          <t>2026-09-29 13:16:11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-28 23:01:15</t>
+          <t>2026-09-29 13:21:23</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-80</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-82</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-81</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Worklog Report Solution</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4240,113 +4424,113 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:55</t>
+          <t>2026-09-28 23:02:03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-28 23:02:08</t>
+          <t>2026-09-28 23:02:04</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-81</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCRUM-78</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Risk analysis and planning</t>
+          <t>Project Management 2 Meeting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-28 13:38:45</t>
+          <t>2026-09-28 22:59:42</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:32</t>
+          <t>2026-09-28 23:01:15</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-80</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCRUM-77</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>List of potential risks</t>
+          <t>Worklog Report Solution</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:59</t>
+          <t>2026-09-28 22:55:55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:14</t>
+          <t>2026-10-07 13:08:15</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCRUM-76</t>
+          <t>SCRUM-78</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Risk analysis and planning</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4364,74 +4548,74 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:40</t>
+          <t>2026-09-28 13:38:45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42:36</t>
+          <t>2026-09-28 13:40:32</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-77</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sprint 3 planning meeting</t>
+          <t>List of potential risks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-25 10:49:06</t>
+          <t>2026-09-28 13:37:59</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-01 11:39:18</t>
+          <t>2026-09-28 13:40:14</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-76</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Look through options for time tracking</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4440,33 +4624,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-25 10:40:35</t>
+          <t>2026-09-28 13:37:40</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-28 23:01:31</t>
+          <t>2026-09-28 13:42:36</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCRUM-73</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prepare for Project Management and Tech Lead meeting</t>
+          <t>Sprint 3 planning meeting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4476,37 +4660,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-25 10:32:10</t>
+          <t>2026-09-25 10:49:06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-05 11:53:53</t>
+          <t>2026-10-01 11:39:18</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCRUM-72</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Design Level 4</t>
+          <t>Look through options for time tracking</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4516,37 +4700,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:23</t>
+          <t>2026-09-25 10:40:35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:33</t>
+          <t>2026-10-07 13:08:02</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCRUM-71</t>
+          <t>SCRUM-73</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Attend Technical Lead meeting 3</t>
+          <t>Prepare for Project Management and Tech Lead meeting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4556,7 +4740,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -4564,29 +4748,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:18</t>
+          <t>2026-09-25 10:32:10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-06 16:34:25</t>
+          <t>2026-10-05 11:53:53</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-72</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Attend Project Management meeting 3</t>
+          <t>Design Level 4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4596,37 +4780,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:17</t>
+          <t>2026-09-23 14:07:23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-06 16:34:14</t>
+          <t>2026-09-23 14:07:33</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SCRUM-69</t>
+          <t>SCRUM-71</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Submit A3, Artefacts</t>
+          <t>Attend Technical Lead meeting 3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4636,7 +4820,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -4644,29 +4828,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-23 14:03:04</t>
+          <t>2026-09-23 14:05:18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-28 13:43:04</t>
+          <t>2026-10-06 16:34:25</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SCRUM-68</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Initial planning of sprint 3</t>
+          <t>Attend Project Management meeting 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4680,33 +4864,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-23 14:00:17</t>
+          <t>2026-09-23 14:05:17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-23 14:08:42</t>
+          <t>2026-10-06 16:34:14</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-69</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Submit D5, Integration and Project Completion Plan</t>
+          <t>Submit A3, Artefacts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4716,37 +4900,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:53</t>
+          <t>2026-09-23 14:03:04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-05 11:49:56</t>
+          <t>2026-09-28 13:43:04</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SCRUM-66</t>
+          <t>SCRUM-68</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Submit D4, Risk Assesment Plan</t>
+          <t>Initial planning of sprint 3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4756,7 +4940,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -4764,69 +4948,69 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:26</t>
+          <t>2026-09-23 14:00:17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-01 11:39:48</t>
+          <t>2026-09-23 14:08:42</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SCRUM-65</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>User Requirements</t>
+          <t>Submit D5, Integration and Project Completion Plan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-23 13:55:24</t>
+          <t>2026-09-23 13:59:53</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-23 13:56:06</t>
+          <t>2026-10-07 13:42:37</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-66</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Group Meeting 24.09.2026</t>
+          <t>Submit D4, Risk Assesment Plan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4836,37 +5020,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-23 13:48:35</t>
+          <t>2026-09-23 13:59:26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-28 13:53:59</t>
+          <t>2026-10-01 11:39:48</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SCRUM-63</t>
+          <t>SCRUM-65</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Project Handover Code Cleanup</t>
+          <t>User Requirements</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4884,69 +5068,69 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:11</t>
+          <t>2026-09-23 13:55:24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:12</t>
+          <t>2026-09-23 13:56:06</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SCRUM-62</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>Group Meeting 24.09.2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:13</t>
+          <t>2026-09-23 13:48:35</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-21 16:10:11</t>
+          <t>2026-09-28 13:53:59</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SCRUM-61</t>
+          <t>SCRUM-63</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Project Handover Code Cleanup</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4964,34 +5148,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-21 16:05:17</t>
+          <t>2026-09-21 16:08:11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:47</t>
+          <t>2026-09-21 16:08:12</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SCRUM-60</t>
+          <t>SCRUM-62</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Level 4 Game Logic</t>
+          <t>Meetings</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5004,29 +5188,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:04</t>
+          <t>2026-09-21 16:06:13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:56</t>
+          <t>2026-09-21 16:10:11</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SCRUM-59</t>
+          <t>SCRUM-61</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Course</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5044,29 +5228,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-21 16:02:30</t>
+          <t>2026-09-21 16:05:17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:57</t>
+          <t>2026-09-21 16:09:47</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-60</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Group Meeting 21.09.2026</t>
+          <t>Level 4 Game Logic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5076,47 +5260,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-21 14:29:42</t>
+          <t>2026-09-21 16:03:04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-28 13:36:42</t>
+          <t>2026-09-21 16:03:56</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SCRUM-57</t>
+          <t>SCRUM-59</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>add more user stories</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -5124,34 +5308,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:53</t>
+          <t>2026-09-21 16:02:30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:49</t>
+          <t>2026-09-21 16:09:57</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SCRUM-56</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adjusting user requirements and adding more user stories</t>
+          <t>Group Meeting 21.09.2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5160,38 +5344,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:48</t>
+          <t>2026-09-21 14:29:42</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-23 22:58:08</t>
+          <t>2026-09-28 13:36:42</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Reorganise the files and folders in the github repo</t>
+          <t>add more user stories</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5200,38 +5384,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-21 13:15:32</t>
+          <t>2026-09-21 14:16:53</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-30 12:37:29</t>
+          <t>2026-09-23 13:41:49</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Update D2, Requirements Specification</t>
+          <t>Adjusting user requirements and adding more user stories</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5240,33 +5424,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-20 18:22:35</t>
+          <t>2026-09-21 14:16:48</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-28 22:24:30</t>
+          <t>2026-09-23 22:58:08</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SCRUM-53</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Update D1, Group Agreement</t>
+          <t>Reorganise the files and folders in the github repo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5280,33 +5464,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-20 18:15:13</t>
+          <t>2026-09-21 13:15:32</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-24 13:36:15</t>
+          <t>2026-09-30 12:37:29</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SCRUM-52</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Brainstorming drafts of level 4</t>
+          <t>Update D2, Requirements Specification</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5320,33 +5504,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-16 11:04:20</t>
+          <t>2026-09-20 18:22:35</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-24 13:33:59</t>
+          <t>2026-09-28 22:24:30</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-53</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Change the en/ett button in level 3 to a field you can fill out</t>
+          <t>Update D1, Group Agreement</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5356,77 +5540,77 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-16 10:51:26</t>
+          <t>2026-09-20 18:15:13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-28 13:54:24</t>
+          <t>2026-09-24 13:36:15</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fix issue with language change not affecting instructions</t>
+          <t>Brainstorming drafts of level 4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-16 10:46:54</t>
+          <t>2026-09-16 11:04:20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-04 20:28:06</t>
+          <t>2026-09-24 13:33:59</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sprint planning meeting</t>
+          <t>Change the en/ett button in level 3 to a field you can fill out</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5436,37 +5620,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-16 10:43:45</t>
+          <t>2026-09-16 10:51:26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:21</t>
+          <t>2026-09-28 13:54:24</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fix issue with the educational information page</t>
+          <t>Fix issue with language change not affecting instructions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5476,37 +5660,37 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39:28</t>
+          <t>2026-09-16 10:46:54</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-30 12:38:00</t>
+          <t>2026-10-04 20:28:06</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Look through the existing code</t>
+          <t>Sprint planning meeting</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5516,42 +5700,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-16 10:26:40</t>
+          <t>2026-09-16 10:43:45</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-28 13:34:18</t>
+          <t>2026-09-21 16:06:21</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SCRUM-45</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Write Submission</t>
+          <t>Fix issue with the educational information page</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5560,43 +5744,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:10</t>
+          <t>2026-09-16 10:39:28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:18</t>
+          <t>2026-09-30 12:38:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SCRUM-44</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Write Submission</t>
+          <t>Look through the existing code</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -5604,24 +5788,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:48</t>
+          <t>2026-09-16 10:26:40</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:01</t>
+          <t>2026-09-28 13:34:18</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SCRUM-43</t>
+          <t>SCRUM-45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5644,24 +5828,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:35</t>
+          <t>2026-09-14 18:29:10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:42</t>
+          <t>2026-09-14 18:29:18</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SCRUM-42</t>
+          <t>SCRUM-44</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5684,24 +5868,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:17</t>
+          <t>2026-09-14 18:28:48</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:28</t>
+          <t>2026-09-14 18:29:01</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SCRUM-41</t>
+          <t>SCRUM-43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5724,29 +5908,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:07</t>
+          <t>2026-09-14 18:28:35</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-14 18:30:21</t>
+          <t>2026-09-14 18:28:42</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SCRUM-40</t>
+          <t>SCRUM-42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Write Submission</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5764,29 +5948,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:58</t>
+          <t>2026-09-14 18:28:17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:10</t>
+          <t>2026-09-14 18:28:28</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SCRUM-39</t>
+          <t>SCRUM-41</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Write Submission</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5804,24 +5988,24 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:47</t>
+          <t>2026-09-14 18:28:07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:07</t>
+          <t>2026-09-14 18:30:21</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-40</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5840,28 +6024,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:32</t>
+          <t>2026-09-14 18:26:58</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-25 12:17:19</t>
+          <t>2026-09-14 18:27:10</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SCRUM-37</t>
+          <t>SCRUM-39</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5884,34 +6068,34 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:05</t>
+          <t>2026-09-14 18:26:47</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:25</t>
+          <t>2026-09-14 18:27:07</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SCRUM-36</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Submit A2, Artefacts</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5920,33 +6104,33 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-14 17:45:50</t>
+          <t>2026-09-14 18:26:32</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-28 13:34:01</t>
+          <t>2026-09-25 12:17:19</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-37</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ethical Considerations</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5960,38 +6144,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-14 16:26:10</t>
+          <t>2026-09-14 18:26:05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:14</t>
+          <t>2026-09-14 18:26:25</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-36</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Functional Requirements 2</t>
+          <t>Submit A2, Artefacts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6000,33 +6184,33 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:56</t>
+          <t>2026-09-14 17:45:50</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:12</t>
+          <t>2026-09-28 13:34:01</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Functional Requirements 1</t>
+          <t>Ethical Considerations</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6040,33 +6224,33 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:41</t>
+          <t>2026-09-14 16:26:10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:11</t>
+          <t>2026-09-30 12:43:14</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SCRUM-32</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Components</t>
+          <t>Functional Requirements 2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6080,33 +6264,33 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:35</t>
+          <t>2026-09-14 16:25:56</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:08</t>
+          <t>2026-09-30 12:43:12</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SCRUM-31</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Definitions</t>
+          <t>Functional Requirements 1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6120,33 +6304,33 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:28</t>
+          <t>2026-09-14 16:25:41</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:01</t>
+          <t>2026-09-30 12:43:11</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SCRUM-30</t>
+          <t>SCRUM-32</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Components</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6164,29 +6348,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:21</t>
+          <t>2026-09-14 16:25:35</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:00</t>
+          <t>2026-09-30 12:43:08</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SCRUM-29</t>
+          <t>SCRUM-31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>User Requirements 2</t>
+          <t>Definitions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6204,29 +6388,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:13</t>
+          <t>2026-09-14 16:25:28</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:18</t>
+          <t>2026-09-30 12:43:01</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SCRUM-28</t>
+          <t>SCRUM-30</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>User Requirements 1</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6244,29 +6428,29 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:02</t>
+          <t>2026-09-14 16:25:21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:06</t>
+          <t>2026-09-30 12:43:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>User Classes</t>
+          <t>User Requirements 2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6280,33 +6464,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:58</t>
+          <t>2026-09-14 14:14:13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-25 12:14:32</t>
+          <t>2026-09-14 14:17:18</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SCRUM-26</t>
+          <t>SCRUM-28</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Layout and Ethical Concerns</t>
+          <t>User Requirements 1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6324,29 +6508,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:52</t>
+          <t>2026-09-14 14:14:02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:08</t>
+          <t>2026-09-14 14:17:06</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SCRUM-20</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>User Classes</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6360,38 +6544,38 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:22</t>
+          <t>2026-09-14 14:13:58</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-14 14:08:16</t>
+          <t>2026-09-25 12:14:32</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SCRUM-19</t>
+          <t>SCRUM-26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Attend Technical Meeting</t>
+          <t>Layout and Ethical Concerns</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6404,34 +6588,34 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:09</t>
+          <t>2026-09-14 14:13:52</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:44</t>
+          <t>2026-09-14 14:17:08</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SCRUM-18</t>
+          <t>SCRUM-20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Attend Project Management Meeting</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6444,29 +6628,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-14 14:05:54</t>
+          <t>2026-09-14 14:07:22</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:21</t>
+          <t>2026-09-14 14:08:16</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Submit D3, Requirements Specification</t>
+          <t>Attend Technical Meeting</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6480,38 +6664,38 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-14 11:38:16</t>
+          <t>2026-09-14 14:06:09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-28 22:43:58</t>
+          <t>2026-09-14 14:07:44</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Attend Project Management Meeting</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6520,33 +6704,33 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-14 11:34:01</t>
+          <t>2026-09-14 14:05:54</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-28 22:35:13</t>
+          <t>2026-09-14 14:06:21</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Client Meeting (online)</t>
+          <t>Submit D3, Requirements Specification</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6560,38 +6744,38 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.5</v>
+        <v>18</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-14 11:32:26</t>
+          <t>2026-09-14 11:38:16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-28 22:28:42</t>
+          <t>2026-09-28 22:43:58</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SCRUM-14</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Submit A1, Artefacts</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6600,33 +6784,33 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-07 12:36:46</t>
+          <t>2026-09-14 11:34:01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:29</t>
+          <t>2026-09-28 22:35:13</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Submit D2, Requirements Elicitation</t>
+          <t>Client Meeting (online)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6640,33 +6824,33 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-07 12:34:14</t>
+          <t>2026-09-14 11:32:26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:02</t>
+          <t>2026-09-28 22:28:42</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Submit D1, Group Agreement</t>
+          <t>Submit A1, Artefacts</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6680,33 +6864,33 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-07 12:31:35</t>
+          <t>2026-09-07 12:36:46</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-28 22:30:22</t>
+          <t>2026-09-14 18:29:29</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Revisit the group agreement</t>
+          <t>Submit D2, Requirements Elicitation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6720,38 +6904,38 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-04 12:43:07</t>
+          <t>2026-09-07 12:34:14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-28 22:52:55</t>
+          <t>2026-09-28 22:55:02</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fix issue with level 1</t>
+          <t>Submit D1, Group Agreement</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6760,73 +6944,73 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-04 11:57:26</t>
+          <t>2026-09-07 12:31:35</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-30 12:37:26</t>
+          <t>2026-09-28 22:30:22</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fix duplicate word issue in level 2</t>
+          <t>Revisit the group agreement</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-04 11:54:17</t>
+          <t>2026-09-04 12:43:07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14:37</t>
+          <t>2026-09-28 22:52:55</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fix case-sensitivity issue</t>
+          <t>Fix issue with level 1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6840,59 +7024,139 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-04 11:52:58</t>
+          <t>2026-09-04 11:57:26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-30 12:36:51</t>
+          <t>2026-09-30 12:37:26</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>SCRUM-9</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Fix duplicate word issue in level 2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:54:17</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:14:37</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Fix case-sensitivity issue</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:52:58</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:36:51</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>SCRUM-4</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Subtask 2.1</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Subtask</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>To Do</t>
         </is>
       </c>
-      <c r="E71" t="n">
+      <c r="E73" t="n">
         <v>0</v>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-4</t>
         </is>

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="23">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="28">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="29">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="31">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -1155,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1298,29 +1298,29 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 07:20:10</t>
+          <t>2026-10-07 10:52:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1340,79 +1340,79 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SCRUM-82</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21 19:00:00</t>
+          <t>2026-10-07 10:52:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SCRUM-80</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28 17:56:13</t>
+          <t>2026-10-07 10:52:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1422,38 +1422,38 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:24</t>
+          <t>2026-09-29 07:20:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1468,79 +1468,79 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-82</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:25</t>
+          <t>2026-09-21 19:00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:30</t>
+          <t>2026-09-28 17:56:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1560,33 +1560,33 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:28</t>
+          <t>2026-09-28 11:00:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:00</t>
+          <t>2026-09-28 11:00:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1673,12 +1673,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:00</t>
+          <t>2026-09-28 11:00:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1719,27 +1719,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-28 11:00:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1765,22 +1765,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-05 13:00:00</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1790,17 +1790,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1811,17 +1811,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:00</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1857,68 +1857,68 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-05 07:49:53</t>
+          <t>2026-09-10 19:30:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 11:40:00</t>
+          <t>2026-10-07 11:22:56</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1928,38 +1928,38 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-73</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-07 09:42:30</t>
+          <t>2026-10-05 13:00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1974,48 +1974,48 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-01 09:00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2030,84 +2030,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-05 07:49:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-10-02 11:40:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2122,69 +2122,69 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-10-07 09:42:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2225,12 +2225,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2271,17 +2271,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2306,28 +2306,28 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2342,38 +2342,38 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2388,38 +2388,38 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2434,37 +2434,33 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2484,12 +2480,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2505,12 +2501,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2530,12 +2526,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2551,22 +2547,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2576,38 +2572,38 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2622,38 +2618,42 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2668,38 +2668,38 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2724,53 +2724,53 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2781,17 +2781,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-21 11:53:00</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2806,48 +2806,48 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-04 13:27:59</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2862,33 +2862,33 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2898,89 +2898,89 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-21 11:53:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2990,79 +2990,79 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-10-04 13:27:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3103,12 +3103,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3149,22 +3149,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3174,38 +3174,38 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3220,17 +3220,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -3241,22 +3241,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3276,33 +3276,33 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3312,38 +3312,38 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3358,48 +3358,48 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3414,74 +3414,74 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3496,38 +3496,38 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>0.25</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3542,48 +3542,48 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3598,176 +3598,176 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3782,38 +3782,38 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -3839,17 +3839,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -3885,77 +3885,73 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-29 07:44:17</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3970,38 +3966,38 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-16 19:56:00</t>
+          <t>2026-09-10 19:29:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4016,7 +4012,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -4027,48 +4023,236 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>10366</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-10 20:22:00</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>SCRUM-11</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>10071</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:14:00</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>SCRUM-10</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:44:17</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>SCRUM-9</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>10437</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>2026-09-10 11:00:00</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>2026-W37</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I63" t="n">
+      <c r="I67" t="n">
         <v>5</v>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4237,7 +4421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4285,17 +4469,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCRUM-84</t>
+          <t>SCRUM-87</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Correct and resubmit D3</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4304,73 +4488,73 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:07:21</t>
+          <t>2026-10-07 14:13:56</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:43:15</t>
+          <t>2026-10-07 14:13:56</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-84</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-87</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCRUM-83</t>
+          <t>SCRUM-86</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Meeting 7.10.2026</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-07 12:47:48</t>
+          <t>2026-10-07 14:13:50</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:22:44</t>
+          <t>2026-10-07 14:13:50</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-83</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-86</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCRUM-82</t>
+          <t>SCRUM-85</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Update the User Interface.</t>
+          <t>Change the en/ett button in level 2 to separate the en/ett input</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4380,42 +4564,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-29 13:16:11</t>
+          <t>2026-10-07 14:11:37</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-29 13:21:23</t>
+          <t>2026-10-07 14:14:09</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-82</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-85</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCRUM-81</t>
+          <t>SCRUM-84</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Correct and resubmit D3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4424,73 +4608,73 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-28 23:02:03</t>
+          <t>2026-10-07 13:07:21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-28 23:02:04</t>
+          <t>2026-10-07 13:43:15</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-81</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-84</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCRUM-80</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Project Management 2 Meeting</t>
+          <t>Meeting 7.10.2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-28 22:59:42</t>
+          <t>2026-10-07 12:47:48</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-28 23:01:15</t>
+          <t>2026-10-07 14:22:43</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-80</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-83</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-82</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Worklog Report Solution</t>
+          <t>Update the User Interface.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4500,42 +4684,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:55</t>
+          <t>2026-09-29 13:16:11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:08:15</t>
+          <t>2026-09-29 13:21:23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-82</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCRUM-78</t>
+          <t>SCRUM-81</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk analysis and planning</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4548,194 +4732,194 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-28 13:38:45</t>
+          <t>2026-09-28 23:02:03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:32</t>
+          <t>2026-09-28 23:02:04</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-81</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCRUM-77</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>List of potential risks</t>
+          <t>Project Management 2 Meeting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:59</t>
+          <t>2026-09-28 22:59:42</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:14</t>
+          <t>2026-09-28 23:01:15</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-80</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCRUM-76</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Worklog Report Solution</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:40</t>
+          <t>2026-09-28 22:55:55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42:36</t>
+          <t>2026-10-07 13:08:15</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-78</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sprint 3 planning meeting</t>
+          <t>Risk analysis and planning</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-25 10:49:06</t>
+          <t>2026-09-28 13:38:45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-01 11:39:18</t>
+          <t>2026-09-28 13:40:32</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-77</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Look through options for time tracking</t>
+          <t>List of potential risks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-25 10:40:35</t>
+          <t>2026-09-28 13:37:59</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:08:02</t>
+          <t>2026-09-28 13:40:14</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCRUM-73</t>
+          <t>SCRUM-76</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Prepare for Project Management and Tech Lead meeting</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4748,29 +4932,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-25 10:32:10</t>
+          <t>2026-09-28 13:37:40</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-05 11:53:53</t>
+          <t>2026-09-28 13:42:36</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SCRUM-72</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Design Level 4</t>
+          <t>Sprint 3 planning meeting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4780,37 +4964,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:23</t>
+          <t>2026-09-25 10:49:06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:33</t>
+          <t>2026-10-07 14:23:25</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SCRUM-71</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Attend Technical Lead meeting 3</t>
+          <t>Look through options for time tracking</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4820,37 +5004,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:18</t>
+          <t>2026-09-25 10:40:35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-06 16:34:25</t>
+          <t>2026-10-07 13:08:02</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-73</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Attend Project Management meeting 3</t>
+          <t>Prepare for Project Management and Tech Lead meeting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4868,29 +5052,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:17</t>
+          <t>2026-09-25 10:32:10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-06 16:34:14</t>
+          <t>2026-10-07 14:22:59</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SCRUM-69</t>
+          <t>SCRUM-72</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Submit A3, Artefacts</t>
+          <t>Design Level 4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4908,29 +5092,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-23 14:03:04</t>
+          <t>2026-09-23 14:07:23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-28 13:43:04</t>
+          <t>2026-09-23 14:07:33</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SCRUM-68</t>
+          <t>SCRUM-71</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Initial planning of sprint 3</t>
+          <t>Attend Technical Lead meeting 3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4948,29 +5132,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-23 14:00:17</t>
+          <t>2026-09-23 14:05:18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-23 14:08:42</t>
+          <t>2026-10-07 14:10:29</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Submit D5, Integration and Project Completion Plan</t>
+          <t>Attend Project Management meeting 3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4980,37 +5164,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:53</t>
+          <t>2026-09-23 14:05:17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:42:37</t>
+          <t>2026-10-06 16:34:14</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SCRUM-66</t>
+          <t>SCRUM-69</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Submit D4, Risk Assesment Plan</t>
+          <t>Submit A3, Artefacts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5028,39 +5212,39 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:26</t>
+          <t>2026-09-23 14:03:04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-01 11:39:48</t>
+          <t>2026-09-28 13:43:04</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SCRUM-65</t>
+          <t>SCRUM-68</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>User Requirements</t>
+          <t>Initial planning of sprint 3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -5068,29 +5252,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-23 13:55:24</t>
+          <t>2026-09-23 14:00:17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-23 13:56:06</t>
+          <t>2026-09-23 14:08:42</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Group Meeting 24.09.2026</t>
+          <t>Submit D5, Integration and Project Completion Plan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5100,47 +5284,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-23 13:48:35</t>
+          <t>2026-09-23 13:59:53</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-28 13:53:59</t>
+          <t>2026-10-07 13:42:37</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SCRUM-63</t>
+          <t>SCRUM-66</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Project Handover Code Cleanup</t>
+          <t>Submit D4, Risk Assesment Plan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -5148,29 +5332,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:11</t>
+          <t>2026-09-23 13:59:26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:12</t>
+          <t>2026-10-07 14:08:43</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SCRUM-62</t>
+          <t>SCRUM-65</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>User Requirements</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5188,74 +5372,74 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:13</t>
+          <t>2026-09-23 13:55:24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-21 16:10:11</t>
+          <t>2026-09-23 13:56:06</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SCRUM-61</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Group Meeting 24.09.2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-21 16:05:17</t>
+          <t>2026-09-23 13:48:35</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:47</t>
+          <t>2026-09-28 13:53:59</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SCRUM-60</t>
+          <t>SCRUM-63</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Level 4 Game Logic</t>
+          <t>Project Handover Code Cleanup</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5268,29 +5452,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:04</t>
+          <t>2026-09-21 16:08:11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:56</t>
+          <t>2026-09-21 16:08:12</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SCRUM-59</t>
+          <t>SCRUM-62</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Meetings</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5308,79 +5492,79 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-21 16:02:30</t>
+          <t>2026-09-21 16:06:13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:57</t>
+          <t>2026-09-21 16:10:11</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-61</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Group Meeting 21.09.2026</t>
+          <t>Course</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-21 14:29:42</t>
+          <t>2026-09-21 16:05:17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-28 13:36:42</t>
+          <t>2026-09-21 16:09:47</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SCRUM-57</t>
+          <t>SCRUM-60</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>add more user stories</t>
+          <t>Level 4 Game Logic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -5388,39 +5572,39 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:53</t>
+          <t>2026-09-21 16:03:04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:49</t>
+          <t>2026-09-21 16:03:56</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SCRUM-56</t>
+          <t>SCRUM-59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Adjusting user requirements and adding more user stories</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -5428,29 +5612,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:48</t>
+          <t>2026-09-21 16:02:30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-23 22:58:08</t>
+          <t>2026-09-21 16:09:57</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Reorganise the files and folders in the github repo</t>
+          <t>Group Meeting 21.09.2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5464,38 +5648,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-21 13:15:32</t>
+          <t>2026-09-21 14:29:42</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-30 12:37:29</t>
+          <t>2026-09-28 13:36:42</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-57</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Update D2, Requirements Specification</t>
+          <t>add more user stories</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5504,38 +5688,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-20 18:22:35</t>
+          <t>2026-09-21 14:16:53</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-28 22:24:30</t>
+          <t>2026-09-23 13:41:49</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SCRUM-53</t>
+          <t>SCRUM-56</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Update D1, Group Agreement</t>
+          <t>Adjusting user requirements and adding more user stories</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5548,29 +5732,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-20 18:15:13</t>
+          <t>2026-09-21 14:16:48</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-24 13:36:15</t>
+          <t>2026-09-23 22:58:08</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SCRUM-52</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Brainstorming drafts of level 4</t>
+          <t>Reorganise the files and folders in the github repo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5584,33 +5768,33 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-16 11:04:20</t>
+          <t>2026-09-21 13:15:32</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-24 13:33:59</t>
+          <t>2026-09-30 12:37:29</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Change the en/ett button in level 3 to a field you can fill out</t>
+          <t>Update D2, Requirements Specification</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5620,7 +5804,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -5628,69 +5812,69 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-16 10:51:26</t>
+          <t>2026-09-20 18:22:35</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-28 13:54:24</t>
+          <t>2026-09-28 22:24:30</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-53</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fix issue with language change not affecting instructions</t>
+          <t>Update D1, Group Agreement</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-16 10:46:54</t>
+          <t>2026-09-20 18:15:13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-04 20:28:06</t>
+          <t>2026-09-24 13:36:15</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sprint planning meeting</t>
+          <t>Brainstorming drafts of level 4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5704,118 +5888,118 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-16 10:43:45</t>
+          <t>2026-09-16 11:04:20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:21</t>
+          <t>2026-09-24 13:33:59</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fix issue with the educational information page</t>
+          <t>Change the en/ett button in level 3 to a field you can fill out</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39:28</t>
+          <t>2026-09-16 10:51:26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-30 12:38:00</t>
+          <t>2026-10-07 14:15:52</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Look through the existing code</t>
+          <t>Fix issue with language change not affecting instructions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-16 10:26:40</t>
+          <t>2026-09-16 10:46:54</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-28 13:34:18</t>
+          <t>2026-10-04 20:28:06</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SCRUM-45</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Write Submission</t>
+          <t>Sprint planning meeting</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5824,38 +6008,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:10</t>
+          <t>2026-09-16 10:43:45</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:18</t>
+          <t>2026-09-21 16:06:21</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SCRUM-44</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Write Submission</t>
+          <t>Fix issue with the educational information page</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5864,38 +6048,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:48</t>
+          <t>2026-09-16 10:39:28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:01</t>
+          <t>2026-09-30 12:38:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SCRUM-43</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Write Submission</t>
+          <t>Look through the existing code</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5908,24 +6092,24 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:35</t>
+          <t>2026-09-16 10:26:40</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:42</t>
+          <t>2026-10-07 14:08:33</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SCRUM-42</t>
+          <t>SCRUM-45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5948,24 +6132,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:17</t>
+          <t>2026-09-14 18:29:10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:28</t>
+          <t>2026-09-14 18:29:18</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SCRUM-41</t>
+          <t>SCRUM-44</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5988,29 +6172,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:07</t>
+          <t>2026-09-14 18:28:48</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-14 18:30:21</t>
+          <t>2026-09-14 18:29:01</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SCRUM-40</t>
+          <t>SCRUM-43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Write Submission</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6028,29 +6212,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:58</t>
+          <t>2026-09-14 18:28:35</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:10</t>
+          <t>2026-09-14 18:28:42</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SCRUM-39</t>
+          <t>SCRUM-42</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Write Submission</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6068,29 +6252,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:47</t>
+          <t>2026-09-14 18:28:17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:07</t>
+          <t>2026-09-14 18:28:28</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-41</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Write Submission</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6104,28 +6288,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:32</t>
+          <t>2026-09-14 18:28:07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-25 12:17:19</t>
+          <t>2026-09-14 18:30:21</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SCRUM-37</t>
+          <t>SCRUM-40</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6148,34 +6332,34 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:05</t>
+          <t>2026-09-14 18:26:58</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:25</t>
+          <t>2026-09-14 18:27:10</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SCRUM-36</t>
+          <t>SCRUM-39</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Submit A2, Artefacts</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6188,29 +6372,29 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-14 17:45:50</t>
+          <t>2026-09-14 18:26:47</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-28 13:34:01</t>
+          <t>2026-09-14 18:27:07</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ethical Considerations</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6224,33 +6408,33 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-14 16:26:10</t>
+          <t>2026-09-14 18:26:32</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:14</t>
+          <t>2026-09-25 12:17:19</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-37</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Functional Requirements 2</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6264,38 +6448,38 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:56</t>
+          <t>2026-09-14 18:26:05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:12</t>
+          <t>2026-09-14 18:26:25</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-36</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Functional Requirements 1</t>
+          <t>Submit A2, Artefacts</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6304,33 +6488,33 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:41</t>
+          <t>2026-09-14 17:45:50</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:11</t>
+          <t>2026-09-28 13:34:01</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SCRUM-32</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Components</t>
+          <t>Ethical Considerations</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6344,33 +6528,33 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:35</t>
+          <t>2026-09-14 16:26:10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:08</t>
+          <t>2026-09-30 12:43:14</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SCRUM-31</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Definitions</t>
+          <t>Functional Requirements 2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6384,33 +6568,33 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:28</t>
+          <t>2026-09-14 16:25:56</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:01</t>
+          <t>2026-09-30 12:43:12</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SCRUM-30</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Functional Requirements 1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6424,33 +6608,33 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:21</t>
+          <t>2026-09-14 16:25:41</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:00</t>
+          <t>2026-09-30 12:43:11</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SCRUM-29</t>
+          <t>SCRUM-32</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>User Requirements 2</t>
+          <t>Components</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6468,29 +6652,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:13</t>
+          <t>2026-09-14 16:25:35</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:18</t>
+          <t>2026-09-30 12:43:08</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SCRUM-28</t>
+          <t>SCRUM-31</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>User Requirements 1</t>
+          <t>Definitions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6508,29 +6692,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:02</t>
+          <t>2026-09-14 16:25:28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:06</t>
+          <t>2026-09-30 12:43:01</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-30</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>User Classes</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6544,33 +6728,33 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:58</t>
+          <t>2026-09-14 16:25:21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-25 12:14:32</t>
+          <t>2026-09-30 12:43:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SCRUM-26</t>
+          <t>SCRUM-29</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Layout and Ethical Concerns</t>
+          <t>User Requirements 2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6588,29 +6772,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:52</t>
+          <t>2026-09-14 14:14:13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:08</t>
+          <t>2026-09-14 14:17:18</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SCRUM-20</t>
+          <t>SCRUM-28</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>User Requirements 1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6628,34 +6812,34 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:22</t>
+          <t>2026-09-14 14:14:02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-14 14:08:16</t>
+          <t>2026-09-14 14:17:06</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SCRUM-19</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Attend Technical Meeting</t>
+          <t>User Classes</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6664,38 +6848,38 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:09</t>
+          <t>2026-09-14 14:13:58</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:44</t>
+          <t>2026-09-25 12:14:32</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SCRUM-18</t>
+          <t>SCRUM-26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Attend Project Management Meeting</t>
+          <t>Layout and Ethical Concerns</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6708,34 +6892,34 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-14 14:05:54</t>
+          <t>2026-09-14 14:13:52</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:21</t>
+          <t>2026-09-14 14:17:08</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Submit D3, Requirements Specification</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6744,38 +6928,38 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-14 11:38:16</t>
+          <t>2026-09-14 14:07:22</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-28 22:43:58</t>
+          <t>2026-09-14 14:08:16</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Attend Technical Meeting</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6784,33 +6968,33 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-14 11:34:01</t>
+          <t>2026-09-14 14:06:09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-28 22:35:13</t>
+          <t>2026-09-14 14:07:44</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-18</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Client Meeting (online)</t>
+          <t>Attend Project Management Meeting</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6824,33 +7008,33 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-14 11:32:26</t>
+          <t>2026-09-14 14:05:54</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-28 22:28:42</t>
+          <t>2026-09-14 14:06:21</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SCRUM-14</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Submit A1, Artefacts</t>
+          <t>Submit D3, Requirements Specification</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6864,38 +7048,38 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-07 12:36:46</t>
+          <t>2026-09-14 11:38:16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:29</t>
+          <t>2026-09-28 22:43:58</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Submit D2, Requirements Elicitation</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6904,33 +7088,33 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-07 12:34:14</t>
+          <t>2026-09-14 11:34:01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:02</t>
+          <t>2026-09-28 22:35:13</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Submit D1, Group Agreement</t>
+          <t>Client Meeting (online)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6944,33 +7128,33 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-07 12:31:35</t>
+          <t>2026-09-14 11:32:26</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-28 22:30:22</t>
+          <t>2026-09-28 22:28:42</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Revisit the group agreement</t>
+          <t>Submit A1, Artefacts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6984,38 +7168,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-04 12:43:07</t>
+          <t>2026-09-07 12:36:46</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-28 22:52:55</t>
+          <t>2026-09-14 18:29:29</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fix issue with level 1</t>
+          <t>Submit D2, Requirements Elicitation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7024,78 +7208,78 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-04 11:57:26</t>
+          <t>2026-09-07 12:34:14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-30 12:37:26</t>
+          <t>2026-09-28 22:55:02</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fix duplicate word issue in level 2</t>
+          <t>Submit D1, Group Agreement</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-04 11:54:17</t>
+          <t>2026-09-07 12:31:35</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14:37</t>
+          <t>2026-09-28 22:30:22</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fix case-sensitivity issue</t>
+          <t>Revisit the group agreement</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7104,59 +7288,179 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-04 11:52:58</t>
+          <t>2026-09-04 12:43:07</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-30 12:36:51</t>
+          <t>2026-09-28 22:52:55</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>SCRUM-10</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Fix issue with level 1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:57:26</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:37:26</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SCRUM-9</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Fix duplicate word issue in level 2</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:54:17</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:14:37</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Fix case-sensitivity issue</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:52:58</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:36:51</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>SCRUM-4</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Subtask 2.1</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Subtask</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>To Do</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="E76" t="n">
         <v>0</v>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-4</t>
         </is>

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1155,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1949,7 +1949,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1974,17 +1974,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-71</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1995,22 +1995,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:00</t>
+          <t>2026-10-05 13:00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2030,33 +2030,33 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-05 07:49:53</t>
+          <t>2026-10-01 09:00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2080,29 +2080,29 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 11:40:00</t>
+          <t>2026-10-05 07:49:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2126,29 +2126,29 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-07 09:42:30</t>
+          <t>2026-10-02 11:40:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2172,60 +2172,60 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-07 09:42:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2271,12 +2271,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2317,12 +2317,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2363,12 +2363,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2409,12 +2409,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2455,17 +2455,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2480,33 +2480,33 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2547,12 +2547,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2593,12 +2593,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2634,21 +2634,17 @@
       <c r="I32" t="n">
         <v>1.5</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2668,12 +2664,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2684,17 +2680,21 @@
       <c r="I33" t="n">
         <v>1.5</v>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2735,22 +2735,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2760,43 +2760,43 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2806,33 +2806,33 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2866,19 +2866,19 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2919,37 +2919,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2958,95 +2958,95 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-21 11:53:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-04 13:27:59</t>
+          <t>2026-09-21 11:53:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -3057,58 +3057,58 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-10-04 13:27:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3149,12 +3149,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3241,12 +3241,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3287,12 +3287,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3333,22 +3333,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3358,43 +3358,43 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3404,43 +3404,43 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3450,38 +3450,38 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3506,23 +3506,23 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3552,140 +3552,140 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3694,24 +3694,24 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3747,12 +3747,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3786,24 +3786,24 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3818,48 +3818,48 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3874,28 +3874,28 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3920,23 +3920,23 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3956,38 +3956,38 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4016,19 +4016,19 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-10 19:29:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4058,88 +4058,84 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-10 20:22:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-29 07:44:17</t>
+          <t>2026-09-18 09:14:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4154,105 +4150,155 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-10</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J65" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-16 19:56:00</t>
+          <t>2026-09-29 07:44:17</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-9</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>10437</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>2026-09-10 11:00:00</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>2026-W37</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I67" t="n">
+      <c r="I68" t="n">
         <v>5</v>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5128,7 +5174,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -5137,7 +5183,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-07 14:10:29</t>
+          <t>2026-10-08 02:14:19</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="20">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="26">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="31">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="11">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -1155,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1213,17 +1213,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07 10:43:05</t>
+          <t>2026-10-08 19:05:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SCRUM-84</t>
+          <t>SCRUM-88</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -1259,17 +1259,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-07 10:22:37</t>
+          <t>2026-10-08 16:48:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1284,33 +1284,33 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SCRUM-83</t>
+          <t>SCRUM-85</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07 10:52:19</t>
+          <t>2026-10-07 10:43:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1330,33 +1330,33 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SCRUM-83</t>
+          <t>SCRUM-84</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-07 10:52:19</t>
+          <t>2026-10-07 10:22:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1397,12 +1397,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-07 10:52:40</t>
+          <t>2026-10-07 10:52:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1443,22 +1443,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 07:20:10</t>
+          <t>2026-10-07 10:52:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1468,84 +1468,84 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SCRUM-82</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-21 19:00:00</t>
+          <t>2026-10-07 10:52:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SCRUM-80</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-28 17:56:13</t>
+          <t>2026-09-29 07:20:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1560,79 +1560,79 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-82</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:24</t>
+          <t>2026-09-21 19:00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:25</t>
+          <t>2026-09-28 17:56:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1652,43 +1652,43 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:30</t>
+          <t>2026-10-09 00:45:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1698,43 +1698,43 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-78</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:28</t>
+          <t>2026-10-09 01:45:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1744,33 +1744,33 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-77</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:00</t>
+          <t>2026-09-28 11:00:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1811,12 +1811,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:00</t>
+          <t>2026-09-28 11:00:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1850,49 +1850,49 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-28 11:00:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1903,22 +1903,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-07 11:22:56</t>
+          <t>2026-09-28 11:00:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1928,17 +1928,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SCRUM-73</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1949,22 +1949,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-05 13:00:00</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1974,17 +1974,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SCRUM-71</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1995,22 +1995,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-05 13:00:00</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2030,74 +2030,74 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:00</t>
+          <t>2026-09-10 19:30:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-05 07:49:53</t>
+          <t>2026-10-07 11:22:56</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-73</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 11:40:00</t>
+          <t>2026-10-05 13:00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2158,38 +2158,38 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-71</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-07 09:42:30</t>
+          <t>2026-10-05 13:00:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2204,48 +2204,48 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-01 09:00:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2260,84 +2260,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-05 07:49:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-10-02 11:40:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2352,69 +2352,69 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-10-07 09:42:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2455,12 +2455,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2501,17 +2501,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2536,28 +2536,28 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2572,38 +2572,38 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2618,38 +2618,38 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2664,37 +2664,33 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2714,12 +2710,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2735,12 +2731,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2760,12 +2756,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2781,22 +2777,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2806,38 +2802,38 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2852,38 +2848,42 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2898,38 +2898,38 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2954,53 +2954,53 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -3011,17 +3011,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-21 11:53:00</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3036,48 +3036,48 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-04 13:27:59</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3092,33 +3092,33 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3128,84 +3128,84 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-18 11:53:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3220,48 +3220,48 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-29 07:47:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3276,38 +3276,38 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-10-04 13:27:59</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3322,23 +3322,23 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3379,22 +3379,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3414,28 +3414,28 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3471,22 +3471,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3496,43 +3496,43 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3552,33 +3552,33 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3588,17 +3588,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -3609,68 +3609,68 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-10-05 07:56:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3726,38 +3726,38 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3772,38 +3772,38 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3818,38 +3818,38 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.5</v>
+        <v>0.25</v>
       </c>
       <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3864,17 +3864,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -3885,17 +3885,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3910,227 +3910,227 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4140,98 +4140,94 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-29 07:44:17</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-16 19:56:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4246,59 +4242,339 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>10213</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:42:00</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>SCRUM-12</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>10362</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:29:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>SCRUM-12</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>10366</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-10 20:22:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>SCRUM-11</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>10071</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:14:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>SCRUM-10</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:44:17</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>SCRUM-9</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>10437</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>2026-09-10 11:00:00</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>2026-W37</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I68" t="n">
+      <c r="I74" t="n">
         <v>5</v>
       </c>
-      <c r="J68" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4467,7 +4743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4515,52 +4791,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCRUM-87</t>
+          <t>SCRUM-88</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Fix D3 Issues for Resubmission</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-07 14:13:56</t>
+          <t>2026-10-08 22:04:14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-07 14:13:56</t>
+          <t>2026-10-08 22:05:19</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-87</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-88</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCRUM-86</t>
+          <t>SCRUM-87</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4578,39 +4854,39 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-07 14:13:50</t>
+          <t>2026-10-07 14:13:56</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-07 14:13:50</t>
+          <t>2026-10-07 14:13:56</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-86</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-87</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCRUM-85</t>
+          <t>SCRUM-86</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Change the en/ett button in level 2 to separate the en/ett input</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -4618,69 +4894,69 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-07 14:11:37</t>
+          <t>2026-10-07 14:13:50</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-07 14:14:09</t>
+          <t>2026-10-07 14:13:50</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-85</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-86</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCRUM-84</t>
+          <t>SCRUM-85</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Correct and resubmit D3</t>
+          <t>Change the en/ett button in level 2 to separate the en/ett input</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:07:21</t>
+          <t>2026-10-07 14:11:37</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:43:15</t>
+          <t>2026-10-08 23:48:36</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-84</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-85</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCRUM-83</t>
+          <t>SCRUM-84</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meeting 7.10.2026</t>
+          <t>Correct and resubmit D3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4690,157 +4966,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07 12:47:48</t>
+          <t>2026-10-07 13:07:21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-07 14:22:43</t>
+          <t>2026-10-07 13:43:15</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-83</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-84</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCRUM-82</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Update the User Interface.</t>
+          <t>Meeting 7.10.2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-29 13:16:11</t>
+          <t>2026-10-07 12:47:48</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-29 13:21:23</t>
+          <t>2026-10-07 14:22:43</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-82</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-83</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCRUM-81</t>
+          <t>SCRUM-82</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Update the User Interface.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-28 23:02:03</t>
+          <t>2026-09-29 13:16:11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-28 23:02:04</t>
+          <t>2026-09-29 13:21:23</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-81</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-82</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCRUM-80</t>
+          <t>SCRUM-81</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Project Management 2 Meeting</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-28 22:59:42</t>
+          <t>2026-09-28 23:02:03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:01:15</t>
+          <t>2026-09-28 23:02:04</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-80</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-81</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Worklog Report Solution</t>
+          <t>Project Management 2 Meeting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4854,73 +5130,73 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:55</t>
+          <t>2026-09-28 22:59:42</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:08:15</t>
+          <t>2026-09-28 23:01:15</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-80</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCRUM-78</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk analysis and planning</t>
+          <t>Worklog Report Solution</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-28 13:38:45</t>
+          <t>2026-09-28 22:55:55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:32</t>
+          <t>2026-10-07 13:08:15</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCRUM-77</t>
+          <t>SCRUM-78</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>List of potential risks</t>
+          <t>Risk analysis and planning</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4934,33 +5210,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:59</t>
+          <t>2026-09-28 13:38:45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-28 13:40:14</t>
+          <t>2026-10-09 05:45:46</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCRUM-76</t>
+          <t>SCRUM-77</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>List of potential risks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4974,73 +5250,73 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:40</t>
+          <t>2026-09-28 13:37:59</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42:36</t>
+          <t>2026-10-09 05:45:31</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-76</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sprint 3 planning meeting</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-25 10:49:06</t>
+          <t>2026-09-28 13:37:40</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-07 14:23:25</t>
+          <t>2026-09-28 13:42:36</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Look through options for time tracking</t>
+          <t>Sprint 3 planning meeting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5054,33 +5330,33 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-25 10:40:35</t>
+          <t>2026-09-25 10:49:06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:08:02</t>
+          <t>2026-10-07 14:23:25</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SCRUM-73</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Prepare for Project Management and Tech Lead meeting</t>
+          <t>Look through options for time tracking</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5098,29 +5374,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-25 10:32:10</t>
+          <t>2026-09-25 10:40:35</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-07 14:22:59</t>
+          <t>2026-10-07 13:08:02</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SCRUM-72</t>
+          <t>SCRUM-73</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Design Level 4</t>
+          <t>Prepare for Project Management and Tech Lead meeting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5130,37 +5406,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:23</t>
+          <t>2026-09-25 10:32:10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:33</t>
+          <t>2026-10-07 14:22:59</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SCRUM-71</t>
+          <t>SCRUM-72</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Attend Technical Lead meeting 3</t>
+          <t>Design Level 4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5170,37 +5446,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:18</t>
+          <t>2026-09-23 14:07:23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-08 02:14:19</t>
+          <t>2026-09-23 14:07:33</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-71</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Attend Project Management meeting 3</t>
+          <t>Attend Technical Lead meeting 3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5218,29 +5494,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:17</t>
+          <t>2026-09-23 14:05:18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-06 16:34:14</t>
+          <t>2026-10-08 02:14:19</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SCRUM-69</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Submit A3, Artefacts</t>
+          <t>Attend Project Management meeting 3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5250,37 +5526,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-23 14:03:04</t>
+          <t>2026-09-23 14:05:17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-28 13:43:04</t>
+          <t>2026-10-06 16:34:14</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SCRUM-68</t>
+          <t>SCRUM-69</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Initial planning of sprint 3</t>
+          <t>Submit A3, Artefacts</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5290,7 +5566,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -5298,29 +5574,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-23 14:00:17</t>
+          <t>2026-09-23 14:03:04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-23 14:08:42</t>
+          <t>2026-09-28 13:43:04</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-68</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Submit D5, Integration and Project Completion Plan</t>
+          <t>Initial planning of sprint 3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5330,37 +5606,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:53</t>
+          <t>2026-09-23 14:00:17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-07 13:42:37</t>
+          <t>2026-09-23 14:08:42</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SCRUM-66</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Submit D4, Risk Assesment Plan</t>
+          <t>Submit D5, Integration and Project Completion Plan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5374,43 +5650,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:26</t>
+          <t>2026-09-23 13:59:53</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-07 14:08:43</t>
+          <t>2026-10-07 13:42:37</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SCRUM-65</t>
+          <t>SCRUM-66</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>User Requirements</t>
+          <t>Submit D4, Risk Assesment Plan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -5418,109 +5694,109 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-23 13:55:24</t>
+          <t>2026-09-23 13:59:26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-23 13:56:06</t>
+          <t>2026-10-07 14:08:43</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-65</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Group Meeting 24.09.2026</t>
+          <t>User Requirements</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-23 13:48:35</t>
+          <t>2026-09-23 13:55:24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-28 13:53:59</t>
+          <t>2026-09-23 13:56:06</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SCRUM-63</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Project Handover Code Cleanup</t>
+          <t>Group Meeting 24.09.2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:11</t>
+          <t>2026-09-23 13:48:35</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:12</t>
+          <t>2026-09-28 13:53:59</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SCRUM-62</t>
+          <t>SCRUM-63</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>Project Handover Code Cleanup</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5538,29 +5814,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:13</t>
+          <t>2026-09-21 16:08:11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-21 16:10:11</t>
+          <t>2026-09-21 16:08:12</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SCRUM-61</t>
+          <t>SCRUM-62</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Meetings</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5578,34 +5854,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-21 16:05:17</t>
+          <t>2026-09-21 16:06:13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:47</t>
+          <t>2026-09-21 16:10:11</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SCRUM-60</t>
+          <t>SCRUM-61</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Level 4 Game Logic</t>
+          <t>Course</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5618,34 +5894,34 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:04</t>
+          <t>2026-09-21 16:05:17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:56</t>
+          <t>2026-09-21 16:09:47</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SCRUM-59</t>
+          <t>SCRUM-60</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 4 Game Logic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5658,74 +5934,74 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-21 16:02:30</t>
+          <t>2026-09-21 16:03:04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:57</t>
+          <t>2026-09-21 16:03:56</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Group Meeting 21.09.2026</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-21 14:29:42</t>
+          <t>2026-09-21 16:02:30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-28 13:36:42</t>
+          <t>2026-09-21 16:09:57</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SCRUM-57</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>add more user stories</t>
+          <t>Group Meeting 21.09.2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5734,33 +6010,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:53</t>
+          <t>2026-09-21 14:29:42</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:49</t>
+          <t>2026-09-28 13:36:42</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SCRUM-56</t>
+          <t>SCRUM-57</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Adjusting user requirements and adding more user stories</t>
+          <t>add more user stories</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5778,34 +6054,34 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:48</t>
+          <t>2026-09-21 14:16:53</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-23 22:58:08</t>
+          <t>2026-09-23 13:41:49</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Reorganise the files and folders in the github repo</t>
+          <t>Adjusting user requirements and adding more user stories</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5814,33 +6090,33 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-21 13:15:32</t>
+          <t>2026-09-21 14:16:48</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-30 12:37:29</t>
+          <t>2026-09-23 22:58:08</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Update D2, Requirements Specification</t>
+          <t>Reorganise the files and folders in the github repo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5854,33 +6130,33 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-20 18:22:35</t>
+          <t>2026-09-21 13:15:32</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-28 22:24:30</t>
+          <t>2026-09-30 12:37:29</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SCRUM-53</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Update D1, Group Agreement</t>
+          <t>Update D2, Requirements Specification</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5894,33 +6170,33 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-20 18:15:13</t>
+          <t>2026-09-20 18:22:35</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-24 13:36:15</t>
+          <t>2026-09-28 22:24:30</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SCRUM-52</t>
+          <t>SCRUM-53</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Brainstorming drafts of level 4</t>
+          <t>Update D1, Group Agreement</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5938,29 +6214,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-16 11:04:20</t>
+          <t>2026-09-20 18:15:13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-24 13:33:59</t>
+          <t>2026-09-24 13:36:15</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Change the en/ett button in level 3 to a field you can fill out</t>
+          <t>Brainstorming drafts of level 4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5970,42 +6246,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-16 10:51:26</t>
+          <t>2026-09-16 11:04:20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-07 14:15:52</t>
+          <t>2026-09-24 13:33:59</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fix issue with language change not affecting instructions</t>
+          <t>Change the en/ett button in level 3 to a field you can fill out</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6014,78 +6290,78 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-16 10:46:54</t>
+          <t>2026-09-16 10:51:26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-04 20:28:06</t>
+          <t>2026-10-09 09:52:24</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sprint planning meeting</t>
+          <t>Fix issue with language change not affecting instructions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-16 10:43:45</t>
+          <t>2026-09-16 10:46:54</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:21</t>
+          <t>2026-10-04 20:28:06</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fix issue with the educational information page</t>
+          <t>Sprint planning meeting</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6094,38 +6370,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39:28</t>
+          <t>2026-09-16 10:43:45</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-30 12:38:00</t>
+          <t>2026-09-21 16:06:21</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Look through the existing code</t>
+          <t>Fix issue with the educational information page</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6134,38 +6410,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-16 10:26:40</t>
+          <t>2026-09-16 10:39:28</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-07 14:08:33</t>
+          <t>2026-09-30 12:38:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SCRUM-45</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Write Submission</t>
+          <t>Look through the existing code</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6174,28 +6450,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:10</t>
+          <t>2026-09-16 10:26:40</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:18</t>
+          <t>2026-10-09 09:59:02</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SCRUM-44</t>
+          <t>SCRUM-45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6218,24 +6494,24 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:48</t>
+          <t>2026-09-14 18:29:10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:01</t>
+          <t>2026-09-14 18:29:18</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SCRUM-43</t>
+          <t>SCRUM-44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6258,24 +6534,24 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:35</t>
+          <t>2026-09-14 18:28:48</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:42</t>
+          <t>2026-09-14 18:29:01</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SCRUM-42</t>
+          <t>SCRUM-43</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6298,24 +6574,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:17</t>
+          <t>2026-09-14 18:28:35</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:28</t>
+          <t>2026-09-14 18:28:42</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SCRUM-41</t>
+          <t>SCRUM-42</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6338,29 +6614,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:07</t>
+          <t>2026-09-14 18:28:17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-14 18:30:21</t>
+          <t>2026-09-14 18:28:28</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SCRUM-40</t>
+          <t>SCRUM-41</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Write Submission</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6378,24 +6654,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:58</t>
+          <t>2026-09-14 18:28:07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:10</t>
+          <t>2026-09-14 18:30:21</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SCRUM-39</t>
+          <t>SCRUM-40</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6418,24 +6694,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:47</t>
+          <t>2026-09-14 18:26:58</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:07</t>
+          <t>2026-09-14 18:27:10</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-39</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6454,28 +6730,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:32</t>
+          <t>2026-09-14 18:26:47</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-25 12:17:19</t>
+          <t>2026-09-14 18:27:07</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SCRUM-37</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6494,38 +6770,38 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:05</t>
+          <t>2026-09-14 18:26:32</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:25</t>
+          <t>2026-09-25 12:17:19</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SCRUM-36</t>
+          <t>SCRUM-37</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Submit A2, Artefacts</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6538,34 +6814,34 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-14 17:45:50</t>
+          <t>2026-09-14 18:26:05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-28 13:34:01</t>
+          <t>2026-09-14 18:26:25</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-36</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ethical Considerations</t>
+          <t>Submit A2, Artefacts</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6574,33 +6850,33 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-14 16:26:10</t>
+          <t>2026-09-14 17:45:50</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:14</t>
+          <t>2026-09-28 13:34:01</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Functional Requirements 2</t>
+          <t>Ethical Considerations</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6614,33 +6890,33 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:56</t>
+          <t>2026-09-14 16:26:10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:12</t>
+          <t>2026-09-30 12:43:14</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Functional Requirements 1</t>
+          <t>Functional Requirements 2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6654,33 +6930,33 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:41</t>
+          <t>2026-09-14 16:25:56</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:11</t>
+          <t>2026-09-30 12:43:12</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SCRUM-32</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Components</t>
+          <t>Functional Requirements 1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6694,33 +6970,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:35</t>
+          <t>2026-09-14 16:25:41</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:08</t>
+          <t>2026-09-30 12:43:11</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SCRUM-31</t>
+          <t>SCRUM-32</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Definitions</t>
+          <t>Components</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6738,29 +7014,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:28</t>
+          <t>2026-09-14 16:25:35</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:01</t>
+          <t>2026-09-30 12:43:08</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SCRUM-30</t>
+          <t>SCRUM-31</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Definitions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6778,29 +7054,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:21</t>
+          <t>2026-09-14 16:25:28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:00</t>
+          <t>2026-09-30 12:43:01</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SCRUM-29</t>
+          <t>SCRUM-30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>User Requirements 2</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6818,29 +7094,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:13</t>
+          <t>2026-09-14 16:25:21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:18</t>
+          <t>2026-09-30 12:43:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SCRUM-28</t>
+          <t>SCRUM-29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>User Requirements 1</t>
+          <t>User Requirements 2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6858,29 +7134,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:02</t>
+          <t>2026-09-14 14:14:13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:06</t>
+          <t>2026-09-14 14:17:18</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>User Classes</t>
+          <t>User Requirements 1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6894,33 +7170,33 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:58</t>
+          <t>2026-09-14 14:14:02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-25 12:14:32</t>
+          <t>2026-09-14 14:17:06</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SCRUM-26</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Layout and Ethical Concerns</t>
+          <t>User Classes</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6934,33 +7210,33 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:52</t>
+          <t>2026-09-14 14:13:58</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:08</t>
+          <t>2026-09-25 12:14:32</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SCRUM-20</t>
+          <t>SCRUM-26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Layout and Ethical Concerns</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6978,34 +7254,34 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:22</t>
+          <t>2026-09-14 14:13:52</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-14 14:08:16</t>
+          <t>2026-09-14 14:17:08</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SCRUM-19</t>
+          <t>SCRUM-20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Attend Technical Meeting</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7018,29 +7294,29 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:09</t>
+          <t>2026-09-14 14:07:22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:44</t>
+          <t>2026-09-14 14:08:16</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SCRUM-18</t>
+          <t>SCRUM-19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Attend Project Management Meeting</t>
+          <t>Attend Technical Meeting</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7058,29 +7334,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-14 14:05:54</t>
+          <t>2026-09-14 14:06:09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:21</t>
+          <t>2026-09-14 14:07:44</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-18</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Submit D3, Requirements Specification</t>
+          <t>Attend Project Management Meeting</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7094,38 +7370,38 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-14 11:38:16</t>
+          <t>2026-09-14 14:05:54</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-28 22:43:58</t>
+          <t>2026-09-14 14:06:21</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Submit D3, Requirements Specification</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7134,38 +7410,38 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-14 11:34:01</t>
+          <t>2026-09-14 11:38:16</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-28 22:35:13</t>
+          <t>2026-09-28 22:43:58</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Client Meeting (online)</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7174,33 +7450,33 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-14 11:32:26</t>
+          <t>2026-09-14 11:34:01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-28 22:28:42</t>
+          <t>2026-09-28 22:35:13</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SCRUM-14</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Submit A1, Artefacts</t>
+          <t>Client Meeting (online)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7214,33 +7490,33 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-07 12:36:46</t>
+          <t>2026-09-14 11:32:26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:29</t>
+          <t>2026-09-28 22:28:42</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-14</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Submit D2, Requirements Elicitation</t>
+          <t>Submit A1, Artefacts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7254,33 +7530,33 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-07 12:34:14</t>
+          <t>2026-09-07 12:36:46</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:02</t>
+          <t>2026-09-14 18:29:29</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Submit D1, Group Agreement</t>
+          <t>Submit D2, Requirements Elicitation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7294,33 +7570,33 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-07 12:31:35</t>
+          <t>2026-09-07 12:34:14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-28 22:30:22</t>
+          <t>2026-09-28 22:55:02</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Revisit the group agreement</t>
+          <t>Submit D1, Group Agreement</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -7334,38 +7610,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-04 12:43:07</t>
+          <t>2026-09-07 12:31:35</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-28 22:52:55</t>
+          <t>2026-09-28 22:30:22</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fix issue with level 1</t>
+          <t>Revisit the group agreement</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7374,33 +7650,33 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-04 11:57:26</t>
+          <t>2026-09-04 12:43:07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-30 12:37:26</t>
+          <t>2026-09-28 22:52:55</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fix duplicate word issue in level 2</t>
+          <t>Fix issue with level 1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7410,37 +7686,37 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-04 11:54:17</t>
+          <t>2026-09-04 11:57:26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14:37</t>
+          <t>2026-09-30 12:37:26</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-9</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fix case-sensitivity issue</t>
+          <t>Fix duplicate word issue in level 2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7450,63 +7726,103 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-04 11:52:58</t>
+          <t>2026-09-04 11:54:17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-30 12:36:51</t>
+          <t>2026-09-29 13:14:37</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Fix case-sensitivity issue</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:52:58</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:36:51</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>SCRUM-4</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Subtask 2.1</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Subtask</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>To Do</t>
         </is>
       </c>
-      <c r="E76" t="n">
+      <c r="E77" t="n">
         <v>0</v>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-4</t>
         </is>

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -4966,7 +4966,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:43:15</t>
+          <t>2026-10-09 11:09:30</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-07 14:22:43</t>
+          <t>2026-10-09 11:09:43</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-28 13:43:04</t>
+          <t>2026-10-09 11:35:35</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -4743,7 +4743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4791,12 +4791,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCRUM-88</t>
+          <t>SCRUM-89</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fix D3 Issues for Resubmission</t>
+          <t>Make a Readme</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4806,77 +4806,77 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-08 22:04:14</t>
+          <t>2026-10-09 12:26:17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-08 22:05:19</t>
+          <t>2026-10-09 12:26:17</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-88</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-89</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCRUM-87</t>
+          <t>SCRUM-88</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Fix D3 Issues for Resubmission</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-07 14:13:56</t>
+          <t>2026-10-08 22:04:14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-07 14:13:56</t>
+          <t>2026-10-08 22:05:19</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-87</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-88</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCRUM-86</t>
+          <t>SCRUM-87</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4894,109 +4894,109 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-07 14:13:50</t>
+          <t>2026-10-07 14:13:56</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-07 14:13:50</t>
+          <t>2026-10-07 14:13:56</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-86</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-87</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCRUM-85</t>
+          <t>SCRUM-86</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Change the en/ett button in level 2 to separate the en/ett input</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-07 14:11:37</t>
+          <t>2026-10-07 14:13:50</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-08 23:48:36</t>
+          <t>2026-10-07 14:13:50</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-85</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-86</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCRUM-84</t>
+          <t>SCRUM-85</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Correct and resubmit D3</t>
+          <t>Change the en/ett button in level 2 to separate the en/ett input</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:07:21</t>
+          <t>2026-10-07 14:11:37</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-09 11:09:30</t>
+          <t>2026-10-08 23:48:36</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-84</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-85</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCRUM-83</t>
+          <t>SCRUM-84</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meeting 7.10.2026</t>
+          <t>Correct and resubmit D3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5006,157 +5006,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-07 12:47:48</t>
+          <t>2026-10-07 13:07:21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-09 11:09:43</t>
+          <t>2026-10-09 11:09:30</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-83</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-84</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCRUM-82</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Update the User Interface.</t>
+          <t>Meeting 7.10.2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-29 13:16:11</t>
+          <t>2026-10-07 12:47:48</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-29 13:21:23</t>
+          <t>2026-10-09 11:09:43</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-82</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-83</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCRUM-81</t>
+          <t>SCRUM-82</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Update the User Interface.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:02:03</t>
+          <t>2026-09-29 13:16:11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-28 23:02:04</t>
+          <t>2026-09-29 13:21:23</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-81</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-82</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCRUM-80</t>
+          <t>SCRUM-81</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Project Management 2 Meeting</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-28 22:59:42</t>
+          <t>2026-09-28 23:02:03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-28 23:01:15</t>
+          <t>2026-09-28 23:02:04</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-80</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-81</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Worklog Report Solution</t>
+          <t>Project Management 2 Meeting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5170,43 +5170,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:55</t>
+          <t>2026-09-28 22:59:42</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:08:15</t>
+          <t>2026-09-28 23:01:15</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-80</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCRUM-78</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk analysis and planning</t>
+          <t>Worklog Report Solution</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -5214,29 +5214,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-28 13:38:45</t>
+          <t>2026-09-28 22:55:55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-09 05:45:46</t>
+          <t>2026-10-07 13:08:15</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCRUM-77</t>
+          <t>SCRUM-78</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>List of potential risks</t>
+          <t>Risk analysis and planning</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5250,33 +5250,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:59</t>
+          <t>2026-09-28 13:38:45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-09 05:45:31</t>
+          <t>2026-10-09 05:45:46</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SCRUM-76</t>
+          <t>SCRUM-77</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>List of potential risks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5290,73 +5290,73 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:40</t>
+          <t>2026-09-28 13:37:59</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42:36</t>
+          <t>2026-10-09 05:45:31</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-76</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sprint 3 planning meeting</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-25 10:49:06</t>
+          <t>2026-09-28 13:37:40</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-07 14:23:25</t>
+          <t>2026-09-28 13:42:36</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Look through options for time tracking</t>
+          <t>Sprint 3 planning meeting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5370,33 +5370,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-25 10:40:35</t>
+          <t>2026-09-25 10:49:06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:08:02</t>
+          <t>2026-10-07 14:23:25</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SCRUM-73</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prepare for Project Management and Tech Lead meeting</t>
+          <t>Look through options for time tracking</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5414,29 +5414,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-25 10:32:10</t>
+          <t>2026-09-25 10:40:35</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-07 14:22:59</t>
+          <t>2026-10-07 13:08:02</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SCRUM-72</t>
+          <t>SCRUM-73</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Design Level 4</t>
+          <t>Prepare for Project Management and Tech Lead meeting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5446,37 +5446,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:23</t>
+          <t>2026-09-25 10:32:10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:33</t>
+          <t>2026-10-07 14:22:59</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SCRUM-71</t>
+          <t>SCRUM-72</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Attend Technical Lead meeting 3</t>
+          <t>Design Level 4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5486,37 +5486,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:18</t>
+          <t>2026-09-23 14:07:23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-08 02:14:19</t>
+          <t>2026-09-23 14:07:33</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-71</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Attend Project Management meeting 3</t>
+          <t>Attend Technical Lead meeting 3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5534,29 +5534,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:17</t>
+          <t>2026-09-23 14:05:18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-06 16:34:14</t>
+          <t>2026-10-08 02:14:19</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SCRUM-69</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Submit A3, Artefacts</t>
+          <t>Attend Project Management meeting 3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5566,37 +5566,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-23 14:03:04</t>
+          <t>2026-09-23 14:05:17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-09 11:35:35</t>
+          <t>2026-10-06 16:34:14</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SCRUM-68</t>
+          <t>SCRUM-69</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Initial planning of sprint 3</t>
+          <t>Submit A3, Artefacts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -5614,29 +5614,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-23 14:00:17</t>
+          <t>2026-09-23 14:03:04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-23 14:08:42</t>
+          <t>2026-10-09 11:35:35</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-68</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Submit D5, Integration and Project Completion Plan</t>
+          <t>Initial planning of sprint 3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5646,37 +5646,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:53</t>
+          <t>2026-09-23 14:00:17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-07 13:42:37</t>
+          <t>2026-09-23 14:08:42</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SCRUM-66</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Submit D4, Risk Assesment Plan</t>
+          <t>Submit D5, Integration and Project Completion Plan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5690,43 +5690,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:26</t>
+          <t>2026-09-23 13:59:53</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-07 14:08:43</t>
+          <t>2026-10-07 13:42:37</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SCRUM-65</t>
+          <t>SCRUM-66</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>User Requirements</t>
+          <t>Submit D4, Risk Assesment Plan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -5734,109 +5734,109 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-23 13:55:24</t>
+          <t>2026-09-23 13:59:26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-23 13:56:06</t>
+          <t>2026-10-07 14:08:43</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-65</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Group Meeting 24.09.2026</t>
+          <t>User Requirements</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-23 13:48:35</t>
+          <t>2026-09-23 13:55:24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-28 13:53:59</t>
+          <t>2026-09-23 13:56:06</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SCRUM-63</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Project Handover Code Cleanup</t>
+          <t>Group Meeting 24.09.2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:11</t>
+          <t>2026-09-23 13:48:35</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:12</t>
+          <t>2026-09-28 13:53:59</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SCRUM-62</t>
+          <t>SCRUM-63</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>Project Handover Code Cleanup</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5854,29 +5854,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:13</t>
+          <t>2026-09-21 16:08:11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-21 16:10:11</t>
+          <t>2026-09-21 16:08:12</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SCRUM-61</t>
+          <t>SCRUM-62</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Meetings</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5894,34 +5894,34 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-21 16:05:17</t>
+          <t>2026-09-21 16:06:13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:47</t>
+          <t>2026-09-21 16:10:11</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SCRUM-60</t>
+          <t>SCRUM-61</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Level 4 Game Logic</t>
+          <t>Course</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5934,34 +5934,34 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:04</t>
+          <t>2026-09-21 16:05:17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:56</t>
+          <t>2026-09-21 16:09:47</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SCRUM-59</t>
+          <t>SCRUM-60</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 4 Game Logic</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5974,74 +5974,74 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-21 16:02:30</t>
+          <t>2026-09-21 16:03:04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:57</t>
+          <t>2026-09-21 16:03:56</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Group Meeting 21.09.2026</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-21 14:29:42</t>
+          <t>2026-09-21 16:02:30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-28 13:36:42</t>
+          <t>2026-09-21 16:09:57</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SCRUM-57</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>add more user stories</t>
+          <t>Group Meeting 21.09.2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6050,33 +6050,33 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:53</t>
+          <t>2026-09-21 14:29:42</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:49</t>
+          <t>2026-09-28 13:36:42</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SCRUM-56</t>
+          <t>SCRUM-57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Adjusting user requirements and adding more user stories</t>
+          <t>add more user stories</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6094,34 +6094,34 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:48</t>
+          <t>2026-09-21 14:16:53</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-23 22:58:08</t>
+          <t>2026-09-23 13:41:49</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Reorganise the files and folders in the github repo</t>
+          <t>Adjusting user requirements and adding more user stories</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6130,33 +6130,33 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-21 13:15:32</t>
+          <t>2026-09-21 14:16:48</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-30 12:37:29</t>
+          <t>2026-09-23 22:58:08</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Update D2, Requirements Specification</t>
+          <t>Reorganise the files and folders in the github repo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6170,33 +6170,33 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-20 18:22:35</t>
+          <t>2026-09-21 13:15:32</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-28 22:24:30</t>
+          <t>2026-09-30 12:37:29</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SCRUM-53</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Update D1, Group Agreement</t>
+          <t>Update D2, Requirements Specification</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6210,33 +6210,33 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-20 18:15:13</t>
+          <t>2026-09-20 18:22:35</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-24 13:36:15</t>
+          <t>2026-09-28 22:24:30</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SCRUM-52</t>
+          <t>SCRUM-53</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brainstorming drafts of level 4</t>
+          <t>Update D1, Group Agreement</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6254,29 +6254,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-16 11:04:20</t>
+          <t>2026-09-20 18:15:13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-24 13:33:59</t>
+          <t>2026-09-24 13:36:15</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Change the en/ett button in level 3 to a field you can fill out</t>
+          <t>Brainstorming drafts of level 4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6286,42 +6286,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-16 10:51:26</t>
+          <t>2026-09-16 11:04:20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-09 09:52:24</t>
+          <t>2026-09-24 13:33:59</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fix issue with language change not affecting instructions</t>
+          <t>Change the en/ett button in level 3 to a field you can fill out</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6330,78 +6330,78 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-16 10:46:54</t>
+          <t>2026-09-16 10:51:26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-04 20:28:06</t>
+          <t>2026-10-09 09:52:24</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sprint planning meeting</t>
+          <t>Fix issue with language change not affecting instructions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-16 10:43:45</t>
+          <t>2026-09-16 10:46:54</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:21</t>
+          <t>2026-10-04 20:28:06</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fix issue with the educational information page</t>
+          <t>Sprint planning meeting</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6410,38 +6410,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39:28</t>
+          <t>2026-09-16 10:43:45</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-30 12:38:00</t>
+          <t>2026-09-21 16:06:21</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Look through the existing code</t>
+          <t>Fix issue with the educational information page</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6450,38 +6450,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-16 10:26:40</t>
+          <t>2026-09-16 10:39:28</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-09 09:59:02</t>
+          <t>2026-09-30 12:38:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SCRUM-45</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Write Submission</t>
+          <t>Look through the existing code</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6490,28 +6490,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:10</t>
+          <t>2026-09-16 10:26:40</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:18</t>
+          <t>2026-10-09 09:59:02</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SCRUM-44</t>
+          <t>SCRUM-45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6534,24 +6534,24 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:48</t>
+          <t>2026-09-14 18:29:10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:01</t>
+          <t>2026-09-14 18:29:18</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SCRUM-43</t>
+          <t>SCRUM-44</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6574,24 +6574,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:35</t>
+          <t>2026-09-14 18:28:48</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:42</t>
+          <t>2026-09-14 18:29:01</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SCRUM-42</t>
+          <t>SCRUM-43</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6614,24 +6614,24 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:17</t>
+          <t>2026-09-14 18:28:35</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:28</t>
+          <t>2026-09-14 18:28:42</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SCRUM-41</t>
+          <t>SCRUM-42</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6654,29 +6654,29 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:07</t>
+          <t>2026-09-14 18:28:17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-14 18:30:21</t>
+          <t>2026-09-14 18:28:28</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SCRUM-40</t>
+          <t>SCRUM-41</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Write Submission</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6694,24 +6694,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:58</t>
+          <t>2026-09-14 18:28:07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:10</t>
+          <t>2026-09-14 18:30:21</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SCRUM-39</t>
+          <t>SCRUM-40</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6734,24 +6734,24 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:47</t>
+          <t>2026-09-14 18:26:58</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:07</t>
+          <t>2026-09-14 18:27:10</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6770,28 +6770,28 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:32</t>
+          <t>2026-09-14 18:26:47</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-25 12:17:19</t>
+          <t>2026-09-14 18:27:07</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SCRUM-37</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6810,38 +6810,38 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:05</t>
+          <t>2026-09-14 18:26:32</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:25</t>
+          <t>2026-09-25 12:17:19</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SCRUM-36</t>
+          <t>SCRUM-37</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Submit A2, Artefacts</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6854,34 +6854,34 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-14 17:45:50</t>
+          <t>2026-09-14 18:26:05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-28 13:34:01</t>
+          <t>2026-09-14 18:26:25</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-36</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ethical Considerations</t>
+          <t>Submit A2, Artefacts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6890,33 +6890,33 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-14 16:26:10</t>
+          <t>2026-09-14 17:45:50</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:14</t>
+          <t>2026-09-28 13:34:01</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Functional Requirements 2</t>
+          <t>Ethical Considerations</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6930,33 +6930,33 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:56</t>
+          <t>2026-09-14 16:26:10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:12</t>
+          <t>2026-09-30 12:43:14</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Functional Requirements 1</t>
+          <t>Functional Requirements 2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6970,33 +6970,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:41</t>
+          <t>2026-09-14 16:25:56</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:11</t>
+          <t>2026-09-30 12:43:12</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SCRUM-32</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Components</t>
+          <t>Functional Requirements 1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7010,33 +7010,33 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:35</t>
+          <t>2026-09-14 16:25:41</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:08</t>
+          <t>2026-09-30 12:43:11</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SCRUM-31</t>
+          <t>SCRUM-32</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Definitions</t>
+          <t>Components</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7054,29 +7054,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:28</t>
+          <t>2026-09-14 16:25:35</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:01</t>
+          <t>2026-09-30 12:43:08</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SCRUM-30</t>
+          <t>SCRUM-31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Definitions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -7094,29 +7094,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:21</t>
+          <t>2026-09-14 16:25:28</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:00</t>
+          <t>2026-09-30 12:43:01</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SCRUM-29</t>
+          <t>SCRUM-30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>User Requirements 2</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7134,29 +7134,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:13</t>
+          <t>2026-09-14 16:25:21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:18</t>
+          <t>2026-09-30 12:43:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SCRUM-28</t>
+          <t>SCRUM-29</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>User Requirements 1</t>
+          <t>User Requirements 2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7174,29 +7174,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:02</t>
+          <t>2026-09-14 14:14:13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:06</t>
+          <t>2026-09-14 14:17:18</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>User Classes</t>
+          <t>User Requirements 1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7210,33 +7210,33 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:58</t>
+          <t>2026-09-14 14:14:02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-25 12:14:32</t>
+          <t>2026-09-14 14:17:06</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SCRUM-26</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Layout and Ethical Concerns</t>
+          <t>User Classes</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7250,33 +7250,33 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:52</t>
+          <t>2026-09-14 14:13:58</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:08</t>
+          <t>2026-09-25 12:14:32</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SCRUM-20</t>
+          <t>SCRUM-26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Layout and Ethical Concerns</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7294,34 +7294,34 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:22</t>
+          <t>2026-09-14 14:13:52</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-14 14:08:16</t>
+          <t>2026-09-14 14:17:08</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SCRUM-19</t>
+          <t>SCRUM-20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Attend Technical Meeting</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7334,29 +7334,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:09</t>
+          <t>2026-09-14 14:07:22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:44</t>
+          <t>2026-09-14 14:08:16</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SCRUM-18</t>
+          <t>SCRUM-19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Attend Project Management Meeting</t>
+          <t>Attend Technical Meeting</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7374,29 +7374,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-14 14:05:54</t>
+          <t>2026-09-14 14:06:09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:21</t>
+          <t>2026-09-14 14:07:44</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Submit D3, Requirements Specification</t>
+          <t>Attend Project Management Meeting</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7410,38 +7410,38 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-14 11:38:16</t>
+          <t>2026-09-14 14:05:54</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-28 22:43:58</t>
+          <t>2026-09-14 14:06:21</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Submit D3, Requirements Specification</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7450,38 +7450,38 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-14 11:34:01</t>
+          <t>2026-09-14 11:38:16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-28 22:35:13</t>
+          <t>2026-09-28 22:43:58</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Client Meeting (online)</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7490,33 +7490,33 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-14 11:32:26</t>
+          <t>2026-09-14 11:34:01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-28 22:28:42</t>
+          <t>2026-09-28 22:35:13</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SCRUM-14</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Submit A1, Artefacts</t>
+          <t>Client Meeting (online)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7530,33 +7530,33 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-07 12:36:46</t>
+          <t>2026-09-14 11:32:26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:29</t>
+          <t>2026-09-28 22:28:42</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Submit D2, Requirements Elicitation</t>
+          <t>Submit A1, Artefacts</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7570,33 +7570,33 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-07 12:34:14</t>
+          <t>2026-09-07 12:36:46</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:02</t>
+          <t>2026-09-14 18:29:29</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Submit D1, Group Agreement</t>
+          <t>Submit D2, Requirements Elicitation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -7610,33 +7610,33 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-07 12:31:35</t>
+          <t>2026-09-07 12:34:14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-28 22:30:22</t>
+          <t>2026-09-28 22:55:02</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Revisit the group agreement</t>
+          <t>Submit D1, Group Agreement</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7650,38 +7650,38 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-04 12:43:07</t>
+          <t>2026-09-07 12:31:35</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-28 22:52:55</t>
+          <t>2026-09-28 22:30:22</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fix issue with level 1</t>
+          <t>Revisit the group agreement</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7690,33 +7690,33 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-04 11:57:26</t>
+          <t>2026-09-04 12:43:07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-30 12:37:26</t>
+          <t>2026-09-28 22:52:55</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fix duplicate word issue in level 2</t>
+          <t>Fix issue with level 1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7726,37 +7726,37 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-04 11:54:17</t>
+          <t>2026-09-04 11:57:26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14:37</t>
+          <t>2026-09-30 12:37:26</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-9</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fix case-sensitivity issue</t>
+          <t>Fix duplicate word issue in level 2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7766,63 +7766,103 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-04 11:52:58</t>
+          <t>2026-09-04 11:54:17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-30 12:36:51</t>
+          <t>2026-09-29 13:14:37</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Fix case-sensitivity issue</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:52:58</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:36:51</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>SCRUM-4</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Subtask 2.1</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Subtask</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>To Do</t>
         </is>
       </c>
-      <c r="E77" t="n">
+      <c r="E78" t="n">
         <v>0</v>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-4</t>
         </is>

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -4979,7 +4979,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-08 23:48:36</t>
+          <t>2026-10-10 11:59:43</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-09 11:09:30</t>
+          <t>2026-10-10 11:59:41</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-29 13:21:23</t>
+          <t>2026-10-10 11:59:44</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-09 11:35:35</t>
+          <t>2026-10-10 11:59:28</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-07 13:42:37</t>
+          <t>2026-10-10 11:59:35</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-07 14:08:43</t>
+          <t>2026-10-10 11:59:37</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-09 09:52:24</t>
+          <t>2026-10-10 11:59:33</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-04 20:28:06</t>
+          <t>2026-10-10 11:59:32</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14:37</t>
+          <t>2026-10-10 11:59:46</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="30">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="15">
@@ -1155,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1213,22 +1213,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>10842</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 19:05:06</t>
+          <t>2026-10-01 14:33:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1238,33 +1238,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SCRUM-88</t>
+          <t>SCRUM-90</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10741</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 16:48:20</t>
+          <t>2026-10-08 19:05:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1294,28 +1294,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SCRUM-85</t>
+          <t>SCRUM-88</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07 10:43:05</t>
+          <t>2026-10-08 16:48:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1330,33 +1330,33 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SCRUM-84</t>
+          <t>SCRUM-85</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-07 10:22:37</t>
+          <t>2026-10-07 10:43:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1386,28 +1386,28 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SCRUM-83</t>
+          <t>SCRUM-84</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-07 10:52:19</t>
+          <t>2026-10-10 18:38:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1422,33 +1422,33 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SCRUM-83</t>
+          <t>SCRUM-84</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-07 10:52:19</t>
+          <t>2026-10-07 10:22:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1489,12 +1489,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-07 10:52:40</t>
+          <t>2026-10-07 10:52:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1535,22 +1535,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 07:20:10</t>
+          <t>2026-10-07 10:52:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1560,89 +1560,89 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SCRUM-82</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-21 19:00:00</t>
+          <t>2026-10-07 10:52:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SCRUM-80</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-28 17:56:13</t>
+          <t>2026-10-07 11:00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1652,43 +1652,43 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-09 00:45:44</t>
+          <t>2026-09-29 07:20:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1698,63 +1698,63 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SCRUM-78</t>
+          <t>SCRUM-82</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-09 01:45:26</t>
+          <t>2026-09-21 19:00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SCRUM-77</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1765,12 +1765,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:24</t>
+          <t>2026-09-28 17:56:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1790,43 +1790,43 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:25</t>
+          <t>2026-10-09 00:45:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1836,43 +1836,43 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-78</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:30</t>
+          <t>2026-10-09 01:45:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1882,33 +1882,33 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-77</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:28</t>
+          <t>2026-09-28 11:00:24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1949,12 +1949,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:00</t>
+          <t>2026-09-28 11:00:25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:00</t>
+          <t>2026-09-28 11:00:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2034,34 +2034,34 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-28 11:00:28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -2087,22 +2087,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-07 11:22:56</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SCRUM-73</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -2133,22 +2133,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-05 13:00:00</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2158,63 +2158,63 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SCRUM-71</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-05 13:00:00</t>
+          <t>2026-09-10 19:30:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -2225,22 +2225,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:00</t>
+          <t>2026-10-07 11:22:56</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2260,23 +2260,23 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-73</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-05 07:49:53</t>
+          <t>2026-10-05 13:00:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2296,43 +2296,43 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-71</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 11:40:00</t>
+          <t>2026-10-05 13:00:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2342,38 +2342,38 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-71</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-07 09:42:30</t>
+          <t>2026-10-05 13:00:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2388,48 +2388,48 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-01 09:00:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2444,84 +2444,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-05 07:49:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-10-02 11:40:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2536,69 +2536,69 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-10-07 09:42:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2639,12 +2639,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2685,17 +2685,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2720,28 +2720,28 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2756,38 +2756,38 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2802,38 +2802,38 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2848,37 +2848,33 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2898,12 +2894,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2919,12 +2915,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2944,12 +2940,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2965,22 +2961,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2990,38 +2986,38 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3036,38 +3032,42 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3082,38 +3082,38 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3138,53 +3138,53 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3195,22 +3195,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-18 11:53:00</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3220,140 +3220,140 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 07:47:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-04 13:27:59</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3368,28 +3368,28 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-18 11:53:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3404,125 +3404,125 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-29 07:47:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-10-04 13:27:59</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3563,12 +3563,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3609,22 +3609,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3634,48 +3634,48 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-05 07:56:00</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3690,28 +3690,28 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3726,17 +3726,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -3747,22 +3747,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3772,38 +3772,38 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3818,171 +3818,171 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-10-05 07:56:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-17 16:36:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4002,38 +4002,38 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4048,38 +4048,38 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>0.25</v>
       </c>
       <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4094,278 +4094,278 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4380,201 +4380,431 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-29 07:44:17</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-16 19:56:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>10362</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:29:00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>SCRUM-12</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>10366</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-10 20:22:00</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>SCRUM-11</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>10071</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:14:00</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>SCRUM-10</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:44:17</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>SCRUM-9</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>10437</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>2026-09-10 11:00:00</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>2026-W37</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I74" t="n">
+      <c r="I79" t="n">
         <v>5</v>
       </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4743,7 +4973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4791,52 +5021,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCRUM-89</t>
+          <t>SCRUM-90</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Make a Readme</t>
+          <t>Show license for photos in-game</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-09 12:26:17</t>
+          <t>2026-10-10 18:53:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-09 12:26:17</t>
+          <t>2026-10-10 21:33:49</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-89</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-90</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCRUM-88</t>
+          <t>SCRUM-89</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fix D3 Issues for Resubmission</t>
+          <t>Make a Readme</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4846,77 +5076,77 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-08 22:04:14</t>
+          <t>2026-10-09 12:26:17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-08 22:05:19</t>
+          <t>2026-10-09 12:26:17</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-88</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-89</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCRUM-87</t>
+          <t>SCRUM-88</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Fix D3 Issues for Resubmission</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-07 14:13:56</t>
+          <t>2026-10-08 22:04:14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-07 14:13:56</t>
+          <t>2026-10-08 22:05:19</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-87</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-88</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCRUM-86</t>
+          <t>SCRUM-87</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4934,109 +5164,109 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-07 14:13:50</t>
+          <t>2026-10-07 14:13:56</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-07 14:13:50</t>
+          <t>2026-10-07 14:13:56</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-86</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-87</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCRUM-85</t>
+          <t>SCRUM-86</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Change the en/ett button in level 2 to separate the en/ett input</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07 14:11:37</t>
+          <t>2026-10-07 14:13:50</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-10 11:59:43</t>
+          <t>2026-10-07 14:13:50</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-85</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-86</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCRUM-84</t>
+          <t>SCRUM-85</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Correct and resubmit D3</t>
+          <t>Change the en/ett button in level 2 to separate the en/ett input</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:07:21</t>
+          <t>2026-10-07 14:11:37</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-10 11:59:41</t>
+          <t>2026-10-10 18:54:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-84</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-85</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCRUM-83</t>
+          <t>SCRUM-84</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meeting 7.10.2026</t>
+          <t>Correct and resubmit D3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5046,157 +5276,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-07 12:47:48</t>
+          <t>2026-10-07 13:07:21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-09 11:09:43</t>
+          <t>2026-10-10 21:38:09</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-83</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-84</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCRUM-82</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Update the User Interface.</t>
+          <t>Meeting 7.10.2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-29 13:16:11</t>
+          <t>2026-10-07 12:47:48</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-10 11:59:44</t>
+          <t>2026-10-10 21:39:01</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-82</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-83</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCRUM-81</t>
+          <t>SCRUM-82</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Update the User Interface.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-28 23:02:03</t>
+          <t>2026-09-29 13:16:11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-28 23:02:04</t>
+          <t>2026-10-10 18:43:02</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-81</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-82</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCRUM-80</t>
+          <t>SCRUM-81</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Project Management 2 Meeting</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-28 22:59:42</t>
+          <t>2026-09-28 23:02:03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-28 23:01:15</t>
+          <t>2026-09-28 23:02:04</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-80</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-81</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Worklog Report Solution</t>
+          <t>Project Management 2 Meeting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5210,43 +5440,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:55</t>
+          <t>2026-09-28 22:59:42</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:08:15</t>
+          <t>2026-09-28 23:01:15</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-80</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SCRUM-78</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk analysis and planning</t>
+          <t>Worklog Report Solution</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -5254,29 +5484,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-28 13:38:45</t>
+          <t>2026-09-28 22:55:55</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-09 05:45:46</t>
+          <t>2026-10-07 13:08:15</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SCRUM-77</t>
+          <t>SCRUM-78</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>List of potential risks</t>
+          <t>Risk analysis and planning</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5290,33 +5520,33 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:59</t>
+          <t>2026-09-28 13:38:45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-09 05:45:31</t>
+          <t>2026-10-09 05:45:46</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-78</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SCRUM-76</t>
+          <t>SCRUM-77</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>List of potential risks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5330,73 +5560,73 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-28 13:37:40</t>
+          <t>2026-09-28 13:37:59</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42:36</t>
+          <t>2026-10-09 05:45:31</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-77</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-76</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sprint 3 planning meeting</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-25 10:49:06</t>
+          <t>2026-09-28 13:37:40</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-07 14:23:25</t>
+          <t>2026-09-28 13:42:36</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Look through options for time tracking</t>
+          <t>Sprint 3 planning meeting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5410,33 +5640,33 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-25 10:40:35</t>
+          <t>2026-09-25 10:49:06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:08:02</t>
+          <t>2026-10-07 14:23:25</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-75</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SCRUM-73</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Prepare for Project Management and Tech Lead meeting</t>
+          <t>Look through options for time tracking</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5454,29 +5684,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-25 10:32:10</t>
+          <t>2026-09-25 10:40:35</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-07 14:22:59</t>
+          <t>2026-10-07 13:08:02</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-74</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SCRUM-72</t>
+          <t>SCRUM-73</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Design Level 4</t>
+          <t>Prepare for Project Management and Tech Lead meeting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5486,37 +5716,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:23</t>
+          <t>2026-09-25 10:32:10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-23 14:07:33</t>
+          <t>2026-10-07 14:22:59</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-73</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SCRUM-71</t>
+          <t>SCRUM-72</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Attend Technical Lead meeting 3</t>
+          <t>Design Level 4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5526,37 +5756,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:18</t>
+          <t>2026-09-23 14:07:23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-08 02:14:19</t>
+          <t>2026-09-23 14:07:33</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-72</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-71</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Attend Project Management meeting 3</t>
+          <t>Attend Technical Lead meeting 3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5570,33 +5800,33 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-23 14:05:17</t>
+          <t>2026-09-23 14:05:18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-06 16:34:14</t>
+          <t>2026-10-10 21:39:55</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-71</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SCRUM-69</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Submit A3, Artefacts</t>
+          <t>Attend Project Management meeting 3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5610,33 +5840,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-23 14:03:04</t>
+          <t>2026-09-23 14:05:17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-10 11:59:28</t>
+          <t>2026-10-06 16:34:14</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-70</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SCRUM-68</t>
+          <t>SCRUM-69</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Initial planning of sprint 3</t>
+          <t>Submit A3, Artefacts</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5654,29 +5884,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-23 14:00:17</t>
+          <t>2026-09-23 14:03:04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-23 14:08:42</t>
+          <t>2026-10-10 11:59:28</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-69</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-68</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Submit D5, Integration and Project Completion Plan</t>
+          <t>Initial planning of sprint 3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5686,37 +5916,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:53</t>
+          <t>2026-09-23 14:00:17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-10 11:59:35</t>
+          <t>2026-09-23 14:08:42</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-68</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SCRUM-66</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Submit D4, Risk Assesment Plan</t>
+          <t>Submit D5, Integration and Project Completion Plan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5730,43 +5960,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-23 13:59:26</t>
+          <t>2026-09-23 13:59:53</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-10 11:59:37</t>
+          <t>2026-10-10 11:59:35</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-67</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SCRUM-65</t>
+          <t>SCRUM-66</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>User Requirements</t>
+          <t>Submit D4, Risk Assesment Plan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -5774,109 +6004,109 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-23 13:55:24</t>
+          <t>2026-09-23 13:59:26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-23 13:56:06</t>
+          <t>2026-10-10 11:59:37</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-66</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-65</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Group Meeting 24.09.2026</t>
+          <t>User Requirements</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-23 13:48:35</t>
+          <t>2026-09-23 13:55:24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-28 13:53:59</t>
+          <t>2026-09-23 13:56:06</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-65</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SCRUM-63</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Project Handover Code Cleanup</t>
+          <t>Group Meeting 24.09.2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:11</t>
+          <t>2026-09-23 13:48:35</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-21 16:08:12</t>
+          <t>2026-09-28 13:53:59</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-64</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SCRUM-62</t>
+          <t>SCRUM-63</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>Project Handover Code Cleanup</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5894,29 +6124,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:13</t>
+          <t>2026-09-21 16:08:11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-21 16:10:11</t>
+          <t>2026-09-21 16:08:12</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-63</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SCRUM-61</t>
+          <t>SCRUM-62</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Meetings</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5934,34 +6164,34 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-21 16:05:17</t>
+          <t>2026-09-21 16:06:13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:47</t>
+          <t>2026-09-21 16:10:11</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-62</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SCRUM-60</t>
+          <t>SCRUM-61</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Level 4 Game Logic</t>
+          <t>Course</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5974,34 +6204,34 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:04</t>
+          <t>2026-09-21 16:05:17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-21 16:03:56</t>
+          <t>2026-09-21 16:09:47</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-61</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SCRUM-59</t>
+          <t>SCRUM-60</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 4 Game Logic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6014,74 +6244,74 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-21 16:02:30</t>
+          <t>2026-09-21 16:03:04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09:57</t>
+          <t>2026-09-21 16:03:56</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-60</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Group Meeting 21.09.2026</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-21 14:29:42</t>
+          <t>2026-09-21 16:02:30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-28 13:36:42</t>
+          <t>2026-09-21 16:09:57</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-59</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SCRUM-57</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>add more user stories</t>
+          <t>Group Meeting 21.09.2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6090,33 +6320,33 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:53</t>
+          <t>2026-09-21 14:29:42</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:49</t>
+          <t>2026-09-28 13:36:42</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-58</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SCRUM-56</t>
+          <t>SCRUM-57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Adjusting user requirements and adding more user stories</t>
+          <t>add more user stories</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6134,34 +6364,34 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-21 14:16:48</t>
+          <t>2026-09-21 14:16:53</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-23 22:58:08</t>
+          <t>2026-09-23 13:41:49</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-57</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Reorganise the files and folders in the github repo</t>
+          <t>Adjusting user requirements and adding more user stories</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6170,33 +6400,33 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-21 13:15:32</t>
+          <t>2026-09-21 14:16:48</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-30 12:37:29</t>
+          <t>2026-09-23 22:58:08</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-56</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Update D2, Requirements Specification</t>
+          <t>Reorganise the files and folders in the github repo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6210,33 +6440,33 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-20 18:22:35</t>
+          <t>2026-09-21 13:15:32</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-28 22:24:30</t>
+          <t>2026-09-30 12:37:29</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-55</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SCRUM-53</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Update D1, Group Agreement</t>
+          <t>Update D2, Requirements Specification</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6250,33 +6480,33 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-20 18:15:13</t>
+          <t>2026-09-20 18:22:35</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-24 13:36:15</t>
+          <t>2026-09-28 22:24:30</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-54</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SCRUM-52</t>
+          <t>SCRUM-53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Brainstorming drafts of level 4</t>
+          <t>Update D1, Group Agreement</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6294,29 +6524,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-16 11:04:20</t>
+          <t>2026-09-20 18:15:13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-24 13:33:59</t>
+          <t>2026-09-24 13:36:15</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-53</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-52</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Change the en/ett button in level 3 to a field you can fill out</t>
+          <t>Brainstorming drafts of level 4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6326,42 +6556,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-16 10:51:26</t>
+          <t>2026-09-16 11:04:20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-10 11:59:33</t>
+          <t>2026-09-24 13:33:59</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-52</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fix issue with language change not affecting instructions</t>
+          <t>Change the en/ett button in level 3 to a field you can fill out</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6370,78 +6600,78 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-16 10:46:54</t>
+          <t>2026-09-16 10:51:26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-10 11:59:32</t>
+          <t>2026-10-10 11:59:33</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-50</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sprint planning meeting</t>
+          <t>Fix issue with language change not affecting instructions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-16 10:43:45</t>
+          <t>2026-09-16 10:46:54</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-21 16:06:21</t>
+          <t>2026-10-10 11:59:32</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-49</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fix issue with the educational information page</t>
+          <t>Sprint planning meeting</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6450,38 +6680,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-16 10:39:28</t>
+          <t>2026-09-16 10:43:45</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-30 12:38:00</t>
+          <t>2026-09-21 16:06:21</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-48</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Look through the existing code</t>
+          <t>Fix issue with the educational information page</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6490,38 +6720,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-16 10:26:40</t>
+          <t>2026-09-16 10:39:28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-09 09:59:02</t>
+          <t>2026-09-30 12:38:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-47</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SCRUM-45</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Write Submission</t>
+          <t>Look through the existing code</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6530,28 +6760,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:10</t>
+          <t>2026-09-16 10:26:40</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:18</t>
+          <t>2026-10-10 21:37:18</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-46</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SCRUM-44</t>
+          <t>SCRUM-45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6574,24 +6804,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:48</t>
+          <t>2026-09-14 18:29:10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:01</t>
+          <t>2026-09-14 18:29:18</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-45</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SCRUM-43</t>
+          <t>SCRUM-44</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6614,24 +6844,24 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:35</t>
+          <t>2026-09-14 18:28:48</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:42</t>
+          <t>2026-09-14 18:29:01</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-44</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SCRUM-42</t>
+          <t>SCRUM-43</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6654,24 +6884,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:17</t>
+          <t>2026-09-14 18:28:35</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:28</t>
+          <t>2026-09-14 18:28:42</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-43</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SCRUM-41</t>
+          <t>SCRUM-42</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6694,29 +6924,29 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-14 18:28:07</t>
+          <t>2026-09-14 18:28:17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-14 18:30:21</t>
+          <t>2026-09-14 18:28:28</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-42</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SCRUM-40</t>
+          <t>SCRUM-41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Write Submission</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6734,24 +6964,24 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:58</t>
+          <t>2026-09-14 18:28:07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:10</t>
+          <t>2026-09-14 18:30:21</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-41</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SCRUM-39</t>
+          <t>SCRUM-40</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6774,24 +7004,24 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:47</t>
+          <t>2026-09-14 18:26:58</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-14 18:27:07</t>
+          <t>2026-09-14 18:27:10</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-40</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-39</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6810,28 +7040,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:32</t>
+          <t>2026-09-14 18:26:47</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-25 12:17:19</t>
+          <t>2026-09-14 18:27:07</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-39</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SCRUM-37</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6850,38 +7080,38 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:05</t>
+          <t>2026-09-14 18:26:32</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:25</t>
+          <t>2026-09-25 12:17:19</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-38</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SCRUM-36</t>
+          <t>SCRUM-37</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Submit A2, Artefacts</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6894,34 +7124,34 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-14 17:45:50</t>
+          <t>2026-09-14 18:26:05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-28 13:34:01</t>
+          <t>2026-09-14 18:26:25</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-37</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-36</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ethical Considerations</t>
+          <t>Submit A2, Artefacts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6930,33 +7160,33 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-14 16:26:10</t>
+          <t>2026-09-14 17:45:50</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:14</t>
+          <t>2026-09-28 13:34:01</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-36</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Functional Requirements 2</t>
+          <t>Ethical Considerations</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6970,33 +7200,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:56</t>
+          <t>2026-09-14 16:26:10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:12</t>
+          <t>2026-09-30 12:43:14</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-35</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Functional Requirements 1</t>
+          <t>Functional Requirements 2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7010,33 +7240,33 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:41</t>
+          <t>2026-09-14 16:25:56</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:11</t>
+          <t>2026-09-30 12:43:12</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-34</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SCRUM-32</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Components</t>
+          <t>Functional Requirements 1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7050,33 +7280,33 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:35</t>
+          <t>2026-09-14 16:25:41</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:08</t>
+          <t>2026-09-30 12:43:11</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-33</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SCRUM-31</t>
+          <t>SCRUM-32</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Definitions</t>
+          <t>Components</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -7094,29 +7324,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:28</t>
+          <t>2026-09-14 16:25:35</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:01</t>
+          <t>2026-09-30 12:43:08</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-32</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SCRUM-30</t>
+          <t>SCRUM-31</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Definitions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7134,29 +7364,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-14 16:25:21</t>
+          <t>2026-09-14 16:25:28</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-30 12:43:00</t>
+          <t>2026-09-30 12:43:01</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-31</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SCRUM-29</t>
+          <t>SCRUM-30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>User Requirements 2</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7174,29 +7404,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:13</t>
+          <t>2026-09-14 16:25:21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:18</t>
+          <t>2026-09-30 12:43:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-30</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SCRUM-28</t>
+          <t>SCRUM-29</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>User Requirements 1</t>
+          <t>User Requirements 2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7214,29 +7444,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-14 14:14:02</t>
+          <t>2026-09-14 14:14:13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:06</t>
+          <t>2026-09-14 14:17:18</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>User Classes</t>
+          <t>User Requirements 1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7250,33 +7480,33 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:58</t>
+          <t>2026-09-14 14:14:02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-25 12:14:32</t>
+          <t>2026-09-14 14:17:06</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SCRUM-26</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Layout and Ethical Concerns</t>
+          <t>User Classes</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7290,33 +7520,33 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-14 14:13:52</t>
+          <t>2026-09-14 14:13:58</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:08</t>
+          <t>2026-09-25 12:14:32</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SCRUM-20</t>
+          <t>SCRUM-26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Attend Meeting</t>
+          <t>Layout and Ethical Concerns</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7334,34 +7564,34 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:22</t>
+          <t>2026-09-14 14:13:52</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-14 14:08:16</t>
+          <t>2026-09-14 14:17:08</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-26</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SCRUM-19</t>
+          <t>SCRUM-20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Attend Technical Meeting</t>
+          <t>Attend Meeting</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7374,29 +7604,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:09</t>
+          <t>2026-09-14 14:07:22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-14 14:07:44</t>
+          <t>2026-09-14 14:08:16</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-20</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SCRUM-18</t>
+          <t>SCRUM-19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Attend Project Management Meeting</t>
+          <t>Attend Technical Meeting</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7414,29 +7644,29 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-14 14:05:54</t>
+          <t>2026-09-14 14:06:09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:21</t>
+          <t>2026-09-14 14:07:44</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-19</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-18</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Submit D3, Requirements Specification</t>
+          <t>Attend Project Management Meeting</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7450,38 +7680,38 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-14 11:38:16</t>
+          <t>2026-09-14 14:05:54</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-28 22:43:58</t>
+          <t>2026-09-14 14:06:21</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-18</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Scope Statement</t>
+          <t>Submit D3, Requirements Specification</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Subtask</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7490,38 +7720,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-14 11:34:01</t>
+          <t>2026-09-14 11:38:16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-28 22:35:13</t>
+          <t>2026-09-28 22:43:58</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-17</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Client Meeting (online)</t>
+          <t>Scope Statement</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Subtask</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7530,33 +7760,33 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-14 11:32:26</t>
+          <t>2026-09-14 11:34:01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-28 22:28:42</t>
+          <t>2026-09-28 22:35:13</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-16</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SCRUM-14</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Submit A1, Artefacts</t>
+          <t>Client Meeting (online)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7570,33 +7800,33 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-07 12:36:46</t>
+          <t>2026-09-14 11:32:26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-14 18:29:29</t>
+          <t>2026-09-28 22:28:42</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-15</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-14</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Submit D2, Requirements Elicitation</t>
+          <t>Submit A1, Artefacts</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -7610,33 +7840,33 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-07 12:34:14</t>
+          <t>2026-09-07 12:36:46</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-28 22:55:02</t>
+          <t>2026-09-14 18:29:29</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-14</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Submit D1, Group Agreement</t>
+          <t>Submit D2, Requirements Elicitation</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7650,33 +7880,33 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-07 12:31:35</t>
+          <t>2026-09-07 12:34:14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-28 22:30:22</t>
+          <t>2026-09-28 22:55:02</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-13</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Revisit the group agreement</t>
+          <t>Submit D1, Group Agreement</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7690,38 +7920,38 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-04 12:43:07</t>
+          <t>2026-09-07 12:31:35</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-28 22:52:55</t>
+          <t>2026-09-28 22:30:22</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fix issue with level 1</t>
+          <t>Revisit the group agreement</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7730,33 +7960,33 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-04 11:57:26</t>
+          <t>2026-09-04 12:43:07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-09-30 12:37:26</t>
+          <t>2026-09-28 22:52:55</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-11</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-10</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fix duplicate word issue in level 2</t>
+          <t>Fix issue with level 1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7766,37 +7996,37 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-04 11:54:17</t>
+          <t>2026-09-04 11:57:26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-10-10 11:59:46</t>
+          <t>2026-09-30 12:37:26</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-9</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fix case-sensitivity issue</t>
+          <t>Fix duplicate word issue in level 2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -7810,59 +8040,99 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-04 11:52:58</t>
+          <t>2026-09-04 11:54:17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-09-30 12:36:51</t>
+          <t>2026-10-10 18:43:09</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Fix case-sensitivity issue</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:52:58</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:36:51</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>SCRUM-4</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Subtask 2.1</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Subtask</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>To Do</t>
         </is>
       </c>
-      <c r="E78" t="n">
+      <c r="E79" t="n">
         <v>0</v>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>2026-09-02 16:12:55</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>https://group-six-uppsala.atlassian.net/browse/SCRUM-4</t>
         </is>

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1155,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2409,27 +2409,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:00</t>
+          <t>2026-09-23 12:00:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-68</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2455,22 +2455,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-05 07:49:53</t>
+          <t>2026-10-01 09:00:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2494,29 +2494,29 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 11:40:00</t>
+          <t>2026-10-05 07:49:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2540,29 +2540,29 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-07 09:42:30</t>
+          <t>2026-10-02 11:40:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2586,60 +2586,60 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-07 09:42:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2685,12 +2685,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2710,12 +2710,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2731,12 +2731,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2823,12 +2823,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2869,17 +2869,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2894,33 +2894,33 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2961,12 +2961,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3007,12 +3007,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3048,21 +3048,17 @@
       <c r="I41" t="n">
         <v>1.5</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3082,12 +3078,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3098,17 +3094,21 @@
       <c r="I42" t="n">
         <v>1.5</v>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3149,22 +3149,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3174,43 +3174,43 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3220,33 +3220,33 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3280,19 +3280,19 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3333,37 +3333,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3372,80 +3372,80 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-18 11:53:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 07:47:00</t>
+          <t>2026-09-18 11:53:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3464,24 +3464,24 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-04 13:27:59</t>
+          <t>2026-09-29 07:47:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3496,79 +3496,79 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-10-04 13:27:59</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3609,12 +3609,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3655,12 +3655,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3701,12 +3701,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3747,12 +3747,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3793,22 +3793,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3818,104 +3818,104 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-05 07:56:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-17 16:36:00</t>
+          <t>2026-10-05 07:56:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3924,24 +3924,24 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-17 16:36:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3956,43 +3956,43 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4002,38 +4002,38 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4058,23 +4058,23 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4104,84 +4104,84 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-15 16:45:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4196,74 +4196,74 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-28</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-21 13:00:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4278,58 +4278,58 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-18</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4338,24 +4338,24 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4370,176 +4370,176 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4564,28 +4564,28 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4610,38 +4610,38 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4656,88 +4656,84 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-29 07:44:17</t>
+          <t>2026-09-10 19:29:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-16 19:56:00</t>
+          <t>2026-09-10 20:22:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4752,59 +4748,201 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>10071</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:14:00</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>SCRUM-10</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:44:17</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>SCRUM-9</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>10437</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>2026-09-10 11:00:00</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>2026-W37</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I79" t="n">
+      <c r="I82" t="n">
         <v>5</v>
       </c>
-      <c r="J79" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5920,7 +6058,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -5929,7 +6067,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-23 14:08:42</t>
+          <t>2026-10-11 20:41:39</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7480,7 +7618,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7489,7 +7627,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-14 14:17:06</t>
+          <t>2026-10-11 20:46:33</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7680,7 +7818,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7689,7 +7827,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-14 14:06:21</t>
+          <t>2026-10-11 20:44:25</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="11">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="8">
@@ -1155,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3425,17 +3425,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10883</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-18 11:53:00</t>
+          <t>2026-09-16 18:19:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3450,217 +3450,217 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-53</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 07:47:00</t>
+          <t>2026-09-16 16:49:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-52</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-04 13:27:59</t>
+          <t>2026-09-18 11:53:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-29 07:47:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-10-04 13:27:59</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3701,12 +3701,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3747,12 +3747,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3793,12 +3793,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3839,22 +3839,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3864,89 +3864,89 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-05 07:56:00</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-17 16:36:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3956,89 +3956,89 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-10-05 07:56:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-17 16:36:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4048,43 +4048,43 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4094,38 +4094,38 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4150,33 +4150,33 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-15 16:45:00</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4186,89 +4186,89 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SCRUM-28</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10880</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-21 13:00:00</t>
+          <t>2026-09-15 16:45:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4288,74 +4288,74 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SCRUM-18</t>
+          <t>SCRUM-28</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-21 13:00:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4370,58 +4370,58 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-18</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4430,24 +4430,24 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4476,24 +4476,24 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4508,94 +4508,94 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4610,28 +4610,28 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4646,17 +4646,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4667,17 +4667,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4702,28 +4702,28 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4738,17 +4738,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4759,113 +4759,109 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-10 19:29:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-29 07:44:17</t>
+          <t>2026-09-10 20:22:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-16 19:56:00</t>
+          <t>2026-09-18 09:14:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4880,69 +4876,165 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-10</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:44:17</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>SCRUM-9</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>10437</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>2026-09-10 11:00:00</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>2026-W37</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I82" t="n">
+      <c r="I84" t="n">
         <v>5</v>
       </c>
-      <c r="J82" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6658,7 +6750,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -6667,7 +6759,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-24 13:36:15</t>
+          <t>2026-10-11 20:49:29</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6698,7 +6790,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6707,7 +6799,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-24 13:33:59</t>
+          <t>2026-10-11 20:49:14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="28">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1155,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2639,42 +2639,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-08 08:20:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-66</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2685,104 +2685,104 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-02 07:54:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-66</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-10-09 07:24:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-66</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2823,12 +2823,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2869,12 +2869,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2915,17 +2915,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2940,38 +2940,38 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2986,38 +2986,38 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3042,23 +3042,23 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3094,21 +3094,17 @@
       <c r="I42" t="n">
         <v>1.5</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3128,12 +3124,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3149,12 +3145,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3174,12 +3170,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3195,22 +3191,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3220,38 +3216,42 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3266,38 +3266,38 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3312,43 +3312,43 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3358,58 +3358,58 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3418,29 +3418,29 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-16 18:19:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SCRUM-53</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3471,22 +3471,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-16 16:49:00</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3496,176 +3496,176 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SCRUM-52</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-18 11:53:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>10883</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-29 07:47:00</t>
+          <t>2026-09-16 18:19:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-53</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-04 13:27:59</t>
+          <t>2026-09-16 16:49:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-52</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-09-18 11:53:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3680,125 +3680,125 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-29 07:47:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-10-04 13:27:59</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3839,12 +3839,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3885,12 +3885,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3931,22 +3931,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3956,84 +3956,84 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-05 07:56:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-17 16:36:00</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4058,33 +4058,33 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4094,89 +4094,89 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-10-05 07:56:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-17 16:36:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4186,43 +4186,43 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4232,17 +4232,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -4253,22 +4253,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-15 16:45:00</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4278,84 +4278,84 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SCRUM-28</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10880</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-21 13:00:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4370,17 +4370,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>SCRUM-18</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -4391,27 +4391,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-15 16:45:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4426,74 +4426,74 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-28</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-21 13:00:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4508,58 +4508,58 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-18</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4568,24 +4568,24 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4600,176 +4600,176 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4794,28 +4794,28 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4840,38 +4840,38 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4886,88 +4886,84 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-29 07:44:17</t>
+          <t>2026-09-10 19:29:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-16 19:56:00</t>
+          <t>2026-09-10 20:22:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4982,59 +4978,201 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>10071</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:14:00</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>SCRUM-10</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:44:17</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>SCRUM-9</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>10437</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>2026-09-10 11:00:00</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>2026-W37</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I84" t="n">
+      <c r="I87" t="n">
         <v>5</v>
       </c>
-      <c r="J84" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6230,7 +6368,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -6239,7 +6377,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-10 11:59:37</t>
+          <t>2026-10-12 11:24:35</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -6826,7 +6964,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -6839,7 +6977,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-10 11:59:33</t>
+          <t>2026-10-12 11:20:45</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-12 11:24:35</t>
+          <t>2026-10-12 11:32:14</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="15">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-10 18:38:02</t>
+          <t>2026-10-03 18:38:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr"/>
     </row>
@@ -5648,7 +5648,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-10 21:38:09</t>
+          <t>2026-10-12 16:58:23</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="30">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-03 18:38:00</t>
+          <t>2026-10-09 18:38:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-12 16:58:23</t>
+          <t>2026-10-12 17:20:32</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-10 11:59:35</t>
+          <t>2026-10-12 17:00:26</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="30">
@@ -1155,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1252,24 +1252,24 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 19:05:06</t>
+          <t>2026-10-05 13:22:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1284,33 +1284,33 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SCRUM-88</t>
+          <t>SCRUM-90</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10741</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:48:20</t>
+          <t>2026-10-08 19:05:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1340,28 +1340,28 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SCRUM-85</t>
+          <t>SCRUM-88</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-07 10:43:05</t>
+          <t>2026-10-08 16:48:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1376,38 +1376,38 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SCRUM-84</t>
+          <t>SCRUM-85</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10844</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-09 18:38:00</t>
+          <t>2026-10-07 10:43:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1436,24 +1436,24 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-07 10:22:37</t>
+          <t>2026-10-09 18:38:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1468,33 +1468,33 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SCRUM-83</t>
+          <t>SCRUM-84</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-07 10:52:19</t>
+          <t>2026-10-07 10:22:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1535,7 +1535,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-07 10:52:40</t>
+          <t>2026-10-07 10:52:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-07 11:00:00</t>
+          <t>2026-10-07 10:52:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 07:20:10</t>
+          <t>2026-10-07 11:00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1698,94 +1698,94 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SCRUM-82</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-21 19:00:00</t>
+          <t>2026-09-29 07:20:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SCRUM-80</t>
+          <t>SCRUM-82</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-28 17:56:13</t>
+          <t>2026-09-21 19:00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1800,33 +1800,33 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-09 00:45:44</t>
+          <t>2026-09-28 17:56:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1836,17 +1836,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SCRUM-78</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1857,12 +1857,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-09 01:45:26</t>
+          <t>2026-10-09 00:45:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1892,33 +1892,33 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SCRUM-77</t>
+          <t>SCRUM-78</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:24</t>
+          <t>2026-10-09 01:45:26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1938,23 +1938,23 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-77</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:25</t>
+          <t>2026-09-28 11:00:24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:30</t>
+          <t>2026-09-28 11:00:25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2041,12 +2041,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:28</t>
+          <t>2026-09-28 11:00:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2087,12 +2087,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:00</t>
+          <t>2026-09-28 11:00:28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2133,7 +2133,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2172,95 +2172,95 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-07 11:22:56</t>
+          <t>2026-09-10 19:30:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SCRUM-73</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -2271,17 +2271,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-05 13:00:00</t>
+          <t>2026-10-07 11:22:56</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SCRUM-71</t>
+          <t>SCRUM-73</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -2317,7 +2317,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10846</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2388,17 +2388,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-71</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2409,27 +2409,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-23 12:00:00</t>
+          <t>2026-10-05 13:00:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2444,38 +2444,38 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SCRUM-68</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:00</t>
+          <t>2026-09-23 12:00:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-68</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2501,22 +2501,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-05 07:49:53</t>
+          <t>2026-10-01 09:00:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2540,29 +2540,29 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 11:40:00</t>
+          <t>2026-10-05 07:49:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2586,29 +2586,29 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-07 09:42:30</t>
+          <t>2026-10-02 11:40:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2632,24 +2632,24 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 08:20:00</t>
+          <t>2026-10-07 09:42:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2674,33 +2674,33 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SCRUM-66</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 07:54:00</t>
+          <t>2026-10-08 08:20:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2710,12 +2710,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2724,29 +2724,29 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-09 07:24:00</t>
+          <t>2026-10-02 07:54:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2770,60 +2770,60 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-09 07:24:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-66</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2869,12 +2869,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2915,12 +2915,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2961,12 +2961,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3007,12 +3007,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3053,17 +3053,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3078,33 +3078,33 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3145,12 +3145,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3191,12 +3191,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3232,21 +3232,17 @@
       <c r="I45" t="n">
         <v>1.5</v>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3266,12 +3262,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3282,17 +3278,21 @@
       <c r="I46" t="n">
         <v>1.5</v>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3333,22 +3333,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3358,43 +3358,43 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3404,33 +3404,33 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3464,19 +3464,19 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3517,37 +3517,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3556,65 +3556,65 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-16 18:19:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SCRUM-53</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>10883</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-16 16:49:00</t>
+          <t>2026-09-16 18:19:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3644,28 +3644,28 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SCRUM-52</t>
+          <t>SCRUM-53</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-18 11:53:00</t>
+          <t>2026-09-16 16:49:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3680,48 +3680,48 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-52</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-29 07:47:00</t>
+          <t>2026-09-18 11:53:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3740,24 +3740,24 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-04 13:27:59</t>
+          <t>2026-09-29 07:47:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3772,79 +3772,79 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-10-04 13:27:59</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3885,12 +3885,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3931,12 +3931,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3977,12 +3977,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4023,12 +4023,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4048,12 +4048,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4069,22 +4069,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4094,104 +4094,104 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-05 07:56:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-17 16:36:00</t>
+          <t>2026-10-05 07:56:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4200,24 +4200,24 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-17 16:36:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4232,43 +4232,43 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4278,38 +4278,38 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4334,23 +4334,23 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4380,33 +4380,33 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-15 16:45:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4416,63 +4416,63 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SCRUM-28</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-15 16:45:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-28</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -4483,73 +4483,73 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10880</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-21 13:00:00</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SCRUM-18</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-21 13:00:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4564,48 +4564,48 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-18</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4614,24 +4614,24 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4667,12 +4667,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4706,24 +4706,24 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4738,48 +4738,48 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4794,28 +4794,28 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4840,23 +4840,23 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4876,38 +4876,38 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-11 09:42:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4936,19 +4936,19 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-10 19:29:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4978,88 +4978,84 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-12</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-10 20:22:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-11</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-29 07:44:17</t>
+          <t>2026-09-18 09:14:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5074,105 +5070,155 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-10</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J85" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-16 19:56:00</t>
+          <t>2026-09-29 07:44:17</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-9</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>10437</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>2026-09-10 11:00:00</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>2026-W37</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I87" t="n">
+      <c r="I88" t="n">
         <v>5</v>
       </c>
-      <c r="J87" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5417,7 +5463,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-10 21:33:49</t>
+          <t>2026-10-12 17:23:17</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="30">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="inlineStr"/>
     </row>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-12 17:23:17</t>
+          <t>2026-10-12 17:25:27</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="27">
@@ -899,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,11 +927,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -942,7 +942,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -957,26 +957,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
@@ -987,11 +987,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="7">
@@ -1002,11 +1002,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="8">
@@ -1017,11 +1017,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="9">
@@ -1032,11 +1032,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1057,16 +1057,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="12">
@@ -1077,11 +1077,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="13">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1107,11 +1107,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1122,11 +1122,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="16">
@@ -1137,10 +1137,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Seleman Hassan</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C17" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1155,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1489,17 +1504,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>10986</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-07 10:22:37</t>
+          <t>2026-10-09 08:28:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1514,33 +1529,33 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SCRUM-83</t>
+          <t>SCRUM-84</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-07 10:52:19</t>
+          <t>2026-10-07 10:22:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1560,12 +1575,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1581,7 +1596,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1606,12 +1621,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1627,12 +1642,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-07 10:52:40</t>
+          <t>2026-10-07 10:52:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1652,12 +1667,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1673,12 +1688,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-07 11:00:00</t>
+          <t>2026-10-07 10:52:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1698,12 +1713,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1719,22 +1734,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 07:20:10</t>
+          <t>2026-10-07 11:00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1744,94 +1759,94 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SCRUM-82</t>
+          <t>SCRUM-83</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-21 19:00:00</t>
+          <t>2026-09-29 07:20:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SCRUM-80</t>
+          <t>SCRUM-82</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-28 17:56:13</t>
+          <t>2026-09-21 19:00:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1846,33 +1861,33 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SCRUM-79</t>
+          <t>SCRUM-80</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-09 00:45:44</t>
+          <t>2026-09-28 17:56:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1882,17 +1897,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SCRUM-78</t>
+          <t>SCRUM-79</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1903,12 +1918,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-09 01:45:26</t>
+          <t>2026-10-09 00:45:44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1938,33 +1953,33 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SCRUM-77</t>
+          <t>SCRUM-78</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:24</t>
+          <t>2026-10-09 01:45:26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1984,23 +1999,23 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SCRUM-75</t>
+          <t>SCRUM-77</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:25</t>
+          <t>2026-09-28 11:00:24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2020,12 +2035,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2041,12 +2056,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:30</t>
+          <t>2026-09-28 11:00:25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2066,12 +2081,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2087,12 +2102,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:28</t>
+          <t>2026-09-28 11:00:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2112,12 +2127,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2133,12 +2148,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-28 11:00:00</t>
+          <t>2026-09-28 11:00:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2158,12 +2173,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2179,7 +2194,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2204,12 +2219,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2218,95 +2233,95 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-10 19:30:00</t>
+          <t>2026-09-28 11:00:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SCRUM-74</t>
+          <t>SCRUM-75</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-07 11:22:56</t>
+          <t>2026-09-10 19:30:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SCRUM-73</t>
+          <t>SCRUM-74</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -2317,17 +2332,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-05 13:00:00</t>
+          <t>2026-10-07 11:22:56</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2342,17 +2357,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SCRUM-71</t>
+          <t>SCRUM-73</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2363,7 +2378,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10846</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2388,12 +2403,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2409,7 +2424,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2434,17 +2449,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SCRUM-70</t>
+          <t>SCRUM-71</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2455,27 +2470,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-23 12:00:00</t>
+          <t>2026-10-05 13:00:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2490,38 +2505,38 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SCRUM-68</t>
+          <t>SCRUM-70</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-01 09:00:00</t>
+          <t>2026-09-23 12:00:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2536,7 +2551,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SCRUM-67</t>
+          <t>SCRUM-68</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2547,22 +2562,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-05 07:49:53</t>
+          <t>2026-10-01 09:00:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2586,29 +2601,29 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 11:40:00</t>
+          <t>2026-10-05 07:49:53</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2618,12 +2633,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2632,29 +2647,29 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-07 09:42:30</t>
+          <t>2026-10-02 11:40:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2678,24 +2693,24 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 08:20:00</t>
+          <t>2026-10-07 09:42:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2720,33 +2735,33 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SCRUM-66</t>
+          <t>SCRUM-67</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 07:54:00</t>
+          <t>2026-10-08 08:20:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2756,12 +2771,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2770,29 +2785,29 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-09 07:24:00</t>
+          <t>2026-10-02 07:54:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2816,60 +2831,60 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:09</t>
+          <t>2026-10-09 07:24:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SCRUM-64</t>
+          <t>SCRUM-66</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2894,12 +2909,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2915,12 +2930,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:15</t>
+          <t>2026-09-24 11:13:09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2940,12 +2955,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2961,12 +2976,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-24 11:13:10</t>
+          <t>2026-09-24 11:13:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2986,12 +3001,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3007,12 +3022,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:22</t>
+          <t>2026-09-24 11:13:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3032,12 +3047,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3053,12 +3068,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-24 10:53:00</t>
+          <t>2026-09-24 11:14:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3078,12 +3093,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3099,17 +3114,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:01</t>
+          <t>2026-09-24 10:53:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3124,33 +3139,33 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SCRUM-58</t>
+          <t>SCRUM-64</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:04</t>
+          <t>2026-09-21 11:00:01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3170,12 +3185,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3191,12 +3206,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-21 12:29:25</t>
+          <t>2026-09-21 11:00:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3216,12 +3231,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3237,12 +3252,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:29:25</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3262,12 +3277,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3278,21 +3293,17 @@
       <c r="I46" t="n">
         <v>1.5</v>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Team Meeting</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:29</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3312,12 +3323,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3328,17 +3339,21 @@
       <c r="I47" t="n">
         <v>1.5</v>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Team Meeting</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 11:00:29</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,12 +3373,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3379,22 +3394,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 08:37:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3404,43 +3419,43 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SCRUM-55</t>
+          <t>SCRUM-58</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-23 10:41:54</t>
+          <t>2026-09-15 08:37:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3450,33 +3465,33 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>SCRUM-55</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-23 20:15:50</t>
+          <t>2026-09-23 10:41:54</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3496,12 +3511,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3510,19 +3525,19 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-23 11:08:00</t>
+          <t>2026-09-23 20:15:50</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3542,12 +3557,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3563,37 +3578,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-11 17:24:00</t>
+          <t>2026-09-23 11:08:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3602,65 +3617,65 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-16 18:19:00</t>
+          <t>2026-09-11 17:24:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SCRUM-53</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>10883</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-16 16:49:00</t>
+          <t>2026-09-16 18:19:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3690,28 +3705,28 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SCRUM-52</t>
+          <t>SCRUM-53</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-18 11:53:00</t>
+          <t>2026-09-16 16:49:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3726,48 +3741,48 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SCRUM-50</t>
+          <t>SCRUM-52</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-29 07:47:00</t>
+          <t>2026-09-18 11:53:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3786,24 +3801,24 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-04 13:27:59</t>
+          <t>2026-09-29 07:47:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3818,79 +3833,79 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SCRUM-49</t>
+          <t>SCRUM-50</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-16 07:44:48</t>
+          <t>2026-10-04 13:27:59</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SCRUM-48</t>
+          <t>SCRUM-49</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-16 07:54:24</t>
+          <t>2026-09-16 07:44:48</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3910,12 +3925,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3931,12 +3946,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-16 05:54:42</t>
+          <t>2026-09-16 07:54:24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3956,12 +3971,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3977,12 +3992,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-16 08:14:29</t>
+          <t>2026-09-16 05:54:42</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4002,12 +4017,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4023,12 +4038,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-16 08:18:46</t>
+          <t>2026-09-16 08:14:29</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4048,12 +4063,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4069,12 +4084,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-16 08:00:00</t>
+          <t>2026-09-16 08:18:46</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4094,12 +4109,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4115,22 +4130,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-21 08:29:54</t>
+          <t>2026-09-16 08:00:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4140,104 +4155,104 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SCRUM-47</t>
+          <t>SCRUM-48</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-05 07:56:00</t>
+          <t>2026-09-21 08:29:54</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-W41</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SCRUM-46</t>
+          <t>SCRUM-47</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-17 16:36:00</t>
+          <t>2026-10-05 07:56:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W41</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4246,24 +4261,24 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17:00</t>
+          <t>2026-09-17 16:36:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4278,43 +4293,43 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SCRUM-38</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-27 17:42:22</t>
+          <t>2026-09-17 07:53:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4334,33 +4349,33 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SCRUM-35</t>
+          <t>SCRUM-46</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00:19</t>
+          <t>2026-09-14 09:17:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4370,43 +4385,43 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Anton Hedlund</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>SCRUM-34</t>
+          <t>SCRUM-38</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10984</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15:02</t>
+          <t>2026-09-14 10:30:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4426,7 +4441,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SCRUM-33</t>
+          <t>SCRUM-37</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4437,22 +4452,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-15 16:45:00</t>
+          <t>2026-09-27 17:42:22</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4462,84 +4477,84 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SCRUM-28</t>
+          <t>SCRUM-35</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-11 09:14:00</t>
+          <t>2026-09-25 15:00:19</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SCRUM-27</t>
+          <t>SCRUM-34</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10880</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-21 13:00:00</t>
+          <t>2026-09-25 14:15:02</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4554,17 +4569,17 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Einar Eriksson Wahlin</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>SCRUM-18</t>
+          <t>SCRUM-33</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -4575,27 +4590,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-28 08:36:42</t>
+          <t>2026-09-15 16:45:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4610,125 +4625,125 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-28</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-27 19:00:00</t>
+          <t>2026-09-11 06:50:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Klas Widebeck</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-28</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-26 06:56:00</t>
+          <t>2026-09-11 09:14:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Seleman Hassan</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-27</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-26 15:23:00</t>
+          <t>2026-09-14 11:00:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4738,43 +4753,43 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>SCRUM-17</t>
+          <t>SCRUM-20</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-24 19:34:00</t>
+          <t>2026-09-17 08:00:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-W39</t>
+          <t>2026-W38</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4784,17 +4799,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Anton Hedlund</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>SCRUM-16</t>
+          <t>SCRUM-20</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -4805,252 +4820,252 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-07 19:57:00</t>
+          <t>2026-09-21 13:00:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>SCRUM-15</t>
+          <t>SCRUM-18</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-11 18:54:00</t>
+          <t>2026-09-28 08:36:42</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W40</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 3</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Einar Eriksson Wahlin</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:873506cb-9f09-47b4-8689-67e320ded9be</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>SCRUM-13</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-11 09:42:00</t>
+          <t>2026-09-27 19:00:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Klas Widebeck</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-10 19:29:00</t>
+          <t>2026-09-26 06:56:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Seleman Hassan</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7e8593ee-4747-44a1-89c2-28e81af19f99</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>SCRUM-12</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-10 20:22:00</t>
+          <t>2026-09-26 15:23:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-W37</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 1</t>
+          <t>SCRUM Sprint 2</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Calvin Koch</t>
+          <t>Sai Suchith Kurra</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>SCRUM-11</t>
+          <t>SCRUM-17</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-18 09:14:00</t>
+          <t>2026-09-24 19:34:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W39</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5060,98 +5075,94 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>SCRUM-10</t>
+          <t>SCRUM-16</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>The issue has been resolved.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-29 07:44:17</t>
+          <t>2026-09-07 19:57:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-W40</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 3</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sai Suchith Kurra</t>
+          <t>Calvin Koch</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>SCRUM-9</t>
+          <t>SCRUM-15</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-16 19:56:00</t>
+          <t>2026-09-11 18:54:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-W38</t>
+          <t>2026-W37</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SCRUM Sprint 2</t>
+          <t>SCRUM Sprint 1</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5166,59 +5177,385 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>SCRUM-7</t>
+          <t>SCRUM-13</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>10213</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:42:00</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>SCRUM-12</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>10362</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:29:00</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>SCRUM-12</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>10989</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-11 07:57:00</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Anton Hedlund</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>712020:991ea2e9-c055-4d6e-a6b7-a44bccafe0a6</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>SCRUM-12</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>10366</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-10 20:22:00</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-W37</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 1</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>SCRUM-11</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>10071</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:14:00</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>SCRUM-10</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>The issue has been resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:44:17</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-W40</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 3</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Sai Suchith Kurra</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>712020:7a155d42-06e0-4222-9d4e-f39dede68758</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>SCRUM-9</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:56:00</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>SCRUM Sprint 2</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Calvin Koch</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>712020:1793fffe-a3b4-4b8b-b162-77b2e79e19da</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>SCRUM-7</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>10437</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>2026-09-10 11:00:00</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>2026-W37</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>SCRUM Sprint 1</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Klas Widebeck</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>712020:ba6fc434-9839-4353-a732-a8f4b60b9695</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>SCRUM-7</t>
         </is>
       </c>
-      <c r="I88" t="n">
+      <c r="I95" t="n">
         <v>5</v>
       </c>
-      <c r="J88" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5694,7 +6031,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -5703,7 +6040,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-12 17:20:32</t>
+          <t>2026-10-13 10:31:22</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7174,7 +7511,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -7183,7 +7520,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-10-10 21:37:18</t>
+          <t>2026-10-13 10:53:46</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7534,7 +7871,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7543,7 +7880,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-14 18:26:25</t>
+          <t>2026-10-13 10:25:19</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7894,7 +8231,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7903,7 +8240,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-11 20:46:33</t>
+          <t>2026-10-13 10:51:31</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8014,7 +8351,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8023,7 +8360,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-14 14:08:16</t>
+          <t>2026-10-13 11:00:42</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8334,7 +8671,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8343,7 +8680,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-09-28 22:30:22</t>
+          <t>2026-10-13 10:57:22</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-10 21:39:01</t>
+          <t>2026-10-15 14:37:53</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-07 14:23:25</t>
+          <t>2026-10-15 14:37:55</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-28 13:53:59</t>
+          <t>2026-10-15 14:38:09</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -6267,7 +6267,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-09 05:45:46</t>
+          <t>2026-10-15 18:29:16</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-09 05:45:31</t>
+          <t>2026-10-15 18:29:14</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-28 13:42:36</t>
+          <t>2026-10-15 18:29:18</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -5787,7 +5787,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-12 17:25:27</t>
+          <t>2026-10-16 19:04:30</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-12 11:20:45</t>
+          <t>2026-10-16 19:04:38</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">

--- a/sprint_worklog_report.xlsx
+++ b/sprint_worklog_report.xlsx
@@ -5689,7 +5689,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
